--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mo 1.00%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4 drill hole(s) nearby · 1966 · Georgia Lake Mines Ltd</t>
+          <t>3 drill hole(s) nearby · 1955–1956 · Glagoma Copper Mines Ltd</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -630,23 +630,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U2" t="n">
         <v>66</v>
       </c>
       <c r="V2" t="n">
-        <v>44.99932</v>
+        <v>46.28991</v>
       </c>
       <c r="W2" t="n">
-        <v>-78.32907</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -656,21 +656,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1955–1956 · Glagoma Copper Mines Ltd</t>
+          <t>5 drill hole(s) nearby · 1988 · Corona Corporation, Corona/Lacana Exploration (1981) Inc · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -716,23 +716,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>66</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -742,30 +742,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>5 drill hole(s) nearby · 1988 · Corona Corporation, Corona/Lacana Exploration (1981) Inc · tested Gold, Copper</t>
+          <t>9 drill hole(s) nearby · 1955 · Goldyke Mines Ltd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -811,14 +811,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -828,21 +828,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Mo 1.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>9 drill hole(s) nearby · 1955 · Goldyke Mines Ltd</t>
+          <t>4 drill hole(s) nearby · 1966 · Georgia Lake Mines Ltd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -894,17 +894,17 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V5" t="n">
-        <v>45.39062</v>
+        <v>44.99932</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.70397</v>
+        <v>-78.32907</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1258,35 +1258,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>McManus Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI41P09NW00043</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Mo 2.00%</t>
+          <t>Ag 171g/t</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Mead Mining Corp · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1999–2008 · Garfield Pinkerton, Temex Resc Corp · tested Copper</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1318,23 +1318,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="V10" t="n">
-        <v>49.69198</v>
+        <v>47.72286</v>
       </c>
       <c r="W10" t="n">
-        <v>-88.04716999999999</v>
+        <v>-80.28064000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
         </is>
       </c>
     </row>
@@ -1344,35 +1344,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>McManus Group</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41P09NW00043</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cobalt, Copper, Nickel, Silver</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1388,12 +1388,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ag 171g/t</t>
+          <t>Mo 2.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1999–2008 · Garfield Pinkerton, Temex Resc Corp · tested Copper</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Mead Mining Corp · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1404,23 +1404,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U11" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V11" t="n">
-        <v>47.72286</v>
+        <v>49.69198</v>
       </c>
       <c r="W11" t="n">
-        <v>-80.28064000000001</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ontario" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ontario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,21 +570,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -612,47 +612,41 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>$582k</t>
-        </is>
-      </c>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Mag Copper Ltd, Trelawney Mining and Exploration Inc, Citadel Gold Mines Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>46.23809</v>
+        <v>44.55039</v>
       </c>
       <c r="W2" t="n">
-        <v>-82.11991</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -662,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -706,12 +700,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -731,14 +725,14 @@
         <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -748,93 +742,83 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shoot Zone Deposit</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI42A10SE00065</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>670 kt (indicated)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 5.5g/t</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>$6.4M</t>
-        </is>
-      </c>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>11</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>St Andrew Goldfields Ltd, Goldcorp Canada Ltd, Goldcorp Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V4" t="n">
-        <v>48.56426</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-80.63866</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -844,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -889,25 +873,15 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>$24k</t>
-        </is>
-      </c>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2010</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Carol Christine Cook, Golden Jaguar Explorations Ltd, D Dmitrovic</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>13</v>
@@ -916,17 +890,17 @@
         <v>325</v>
       </c>
       <c r="U5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.49976</v>
+        <v>44.85917</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.15956</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -936,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -981,44 +955,34 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>$13k</t>
-        </is>
-      </c>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1997</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Robert J Ross</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.51686</v>
+        <v>45.28947</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.62098</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1028,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1073,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1084,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55104</v>
+        <v>45.30338</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1110,93 +1074,79 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Band-Ore Mattagami Zone 4</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI52B09SE00024</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shebandowan</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>616 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Au 4.83g/t</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>33 drill hole(s) nearby · 1981–2022 · Golden Share Mining Corporation, Mattagami Lake Expl Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>$3.0M</t>
-        </is>
-      </c>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>21</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Golden Share Mining Corp, E2 Gold Inc, Band-Ore Resources Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>48.62462</v>
+        <v>45.29002</v>
       </c>
       <c r="W8" t="n">
-        <v>-90.12229000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1206,35 +1156,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1245,50 +1195,40 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>225 kt (possible)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>$215k</t>
-        </is>
-      </c>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Crown William Mining Corp, Madoc Mining Company Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.63956</v>
+        <v>46.23809</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.55477999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1298,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1321,12 +1261,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1337,50 +1277,40 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>681 kt (probable)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>$118k</t>
-        </is>
-      </c>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>14</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2013</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Graphite Mountain Inc, Cardinal Explorations Inc, Oakridge Environmental Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>45.21442</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-77.8742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1390,30 +1320,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ore Chimney</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C14SE00142</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bishop Corners</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1422,7 +1352,7 @@
         </is>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1435,44 +1365,34 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>$259k</t>
-        </is>
-      </c>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2011</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Willwin International Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>44.77617</v>
+        <v>44.55104</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.15194</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1482,30 +1402,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Golden Arrow - West</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI42A08NW00004</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Vimy Ridge</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1514,61 +1434,47 @@
         </is>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>493 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Au 22.63g/t</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>77 drill hole(s) nearby · 1937–2015 · Victoria Gold Mines Ltd, Murgor Resources Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>$661k</t>
-        </is>
-      </c>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>12</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Victoria Gold Mines Ltd, Victoria Gold Mines (Etl)/Murgor Resourc, Teddy Bear Valley Mines Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>48.45691</v>
+        <v>48.24876</v>
       </c>
       <c r="W12" t="n">
-        <v>-80.40869000000001</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A08NW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1578,89 +1484,79 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI42A09SW00163</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Holtyre</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.9</v>
+        <v>71.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>558 kt (indicated)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>91 drill hole(s) nearby · 1946–2021 · G E Parsons , Armco-Geddes Resc Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>$7.9M</t>
-        </is>
-      </c>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>12</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>St Andrew Goldfields Ltd, Goldcorp Canada Ltd, Goldcorp Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>48.50619</v>
+        <v>54.51539</v>
       </c>
       <c r="W13" t="n">
-        <v>-80.31543000000001</v>
+        <v>-91.40791</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1670,89 +1566,83 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>95-2</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31M12SW00017</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diamond, Kimberlite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20.2 Mt (inferred)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>29 drill hole(s) nearby · 1995–2005 · Contact Diamond Corp, Sudbury Contact Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>$3.9M</t>
-        </is>
-      </c>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Contact Diamond Corp, Sudbury Contact Mines Ltd, MPH Consulting Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="V14" t="n">
-        <v>47.52342</v>
+        <v>44.99932</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.89148</v>
+        <v>-78.32907</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1762,35 +1652,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1801,13 +1691,13 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>227 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1818,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>44.47438</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.51861</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1844,21 +1734,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jardun Mine - No 3 Zone</t>
+          <t>Temagami Copper Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41K09NE00090</t>
+          <t>MDI41I16NE00004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Northland</t>
+          <t>Adanac</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9.6</v>
+        <v>1.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1867,7 +1757,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver, Zinc, Gold</t>
+          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1883,54 +1773,44 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Pb 4.78%, Zn 4.78%</t>
+          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>137 drill hole(s) nearby · 1951–1984 · Longbow Exploration Inc/Watson Lake Mines Ltd, Jardun Mines Ltd · tested Copper, Lead, Silver, Zinc, Gold</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>$244k</t>
-        </is>
-      </c>
+          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>13369871 Canada Inc, Gold Diamet Resources Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
         <v>54</v>
       </c>
       <c r="V16" t="n">
-        <v>46.63751</v>
+        <v>46.96233</v>
       </c>
       <c r="W16" t="n">
-        <v>-84.14293000000001</v>
+        <v>-80.03716</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
         </is>
       </c>
     </row>
@@ -1940,35 +1820,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI31C10NW00016</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1979,54 +1859,44 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>72 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mo 2.00%</t>
+          <t>Zn 11.60%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Roxmark Mines Ltd, Candore Expl Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>$710k</t>
-        </is>
-      </c>
+          <t>42 drill hole(s) nearby · 1950–1975 · Cons Rochette Mines Ltd, W H Douglas</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>15</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Roxmark Mines Ltd, Goldstone Resources Inc, Steven Siemieniuk</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U17" t="n">
         <v>52</v>
       </c>
       <c r="V17" t="n">
-        <v>49.69198</v>
+        <v>44.6895</v>
       </c>
       <c r="W17" t="n">
-        <v>-88.04716999999999</v>
+        <v>-76.77161</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
         </is>
       </c>
     </row>
@@ -2036,35 +1906,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Macassa</t>
+          <t>Sand River Gold Mine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C13SE00099</t>
+          <t>MDI52H09SE00005</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ormsby</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
+          <t>Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2075,50 +1945,44 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4.7 Mt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>W 0.23%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>$571k</t>
-        </is>
-      </c>
+          <t>12 drill hole(s) nearby · 1987–1988 · Cryderman Gold Inc · tested Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Douglas Garrie, First Nickel Inc, Limerick Mines Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U18" t="n">
         <v>52</v>
       </c>
       <c r="V18" t="n">
-        <v>44.868</v>
+        <v>49.62195</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.72254</v>
+        <v>-88.04667000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09SE00005</t>
         </is>
       </c>
     </row>
@@ -2128,30 +1992,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Ogema</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI52A15SE00006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Dorion</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Lead, Zinc, Amethyst, Barite, Copper, Fluorite, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2160,61 +2024,47 @@
         </is>
       </c>
       <c r="I19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8 kt produced</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Mo 5.00%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>$12k</t>
-        </is>
-      </c>
+          <t>2 drill hole(s) nearby · 1961 · Sogemines Dev Co Ltd · tested Zinc</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2009</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Douglas Lalonde</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U19" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V19" t="n">
-        <v>45.39062</v>
+        <v>48.76995</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.70397</v>
+        <v>-88.73446</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A15SE00006</t>
         </is>
       </c>
     </row>
@@ -2224,52 +2074,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Rabbit Mountain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI52A05SE00008</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Harstone</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>86 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2280,23 +2130,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V20" t="n">
-        <v>46.29559</v>
+        <v>48.30674</v>
       </c>
       <c r="W20" t="n">
-        <v>-83.20277</v>
+        <v>-89.60534</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
         </is>
       </c>
     </row>
@@ -2306,35 +2156,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Simon Copper Property</t>
+          <t>Beaver</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31F03NW00044</t>
+          <t>MDI52A05SE00009</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Slate Falls</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Iron, Selenium</t>
+          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2345,35 +2195,21 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>230 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Cu 1.09%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>$1.1M</t>
-        </is>
-      </c>
+          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, Honey Badger Exploration Inc · tested Silver, Zinc</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>11</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Adroit Resources Inc, Pelangio Mines Inc, CJP Exploration Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
         <v>1</v>
@@ -2382,17 +2218,17 @@
         <v>25</v>
       </c>
       <c r="U21" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>45.20807</v>
+        <v>48.31944</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.31331</v>
+        <v>-89.63952999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
         </is>
       </c>
     </row>
@@ -2402,30 +2238,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sand River Gold Mine</t>
+          <t>Silver Mountain West</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI52H09SE00005</t>
+          <t>MDI52A04NW00003</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2441,54 +2277,40 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>W 0.23%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1987–1988 · Cryderman Gold Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>$1.0M</t>
-        </is>
-      </c>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Kodiak Exploration Ltd, Herb Garry Goodman, Dianne J Cote</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
+        <v>150</v>
+      </c>
+      <c r="U22" t="n">
         <v>50</v>
       </c>
-      <c r="U22" t="n">
-        <v>51</v>
-      </c>
       <c r="V22" t="n">
-        <v>49.62195</v>
+        <v>48.24757</v>
       </c>
       <c r="W22" t="n">
-        <v>-88.04667000000001</v>
+        <v>-89.8866</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
         </is>
       </c>
     </row>
@@ -2498,89 +2320,83 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Scadding Gold Property</t>
+          <t>Office Shaft</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI41I10NE00012</t>
+          <t>MDI41N13SW00013</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Basin Mines</t>
+          <t>Quebec Harbour</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5.2</v>
+        <v>11.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I23" t="b">
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>$3.7M</t>
-        </is>
-      </c>
+          <t>9 drill hole(s) nearby · 1942–1955 · M J O'Brien Ltd(Burrage Copper)Jones, The American Metal Co Ltd · tested Copper</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>19</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Trueclaim Exploration Inc, Currie Rose Resources Inc, John Gregory Brady</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
         <v>50</v>
       </c>
       <c r="V23" t="n">
-        <v>46.65087</v>
+        <v>47.76366</v>
       </c>
       <c r="W23" t="n">
-        <v>-80.61375</v>
+        <v>-85.91361000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00013</t>
         </is>
       </c>
     </row>
@@ -2590,35 +2406,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ethel Copper Property</t>
+          <t>Quirke No. 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI41P09NW00014</t>
+          <t>MDI41J10SE00007</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Elk Lake</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Uranium, Rare Earth Elements, Thorium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2629,35 +2445,21 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Cu 2.64%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>$1.7M</t>
-        </is>
-      </c>
+          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>16</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Temex Resources Corp, Contact Diamond Corp, Battery Mineral Resources Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>1</v>
@@ -2669,14 +2471,14 @@
         <v>50</v>
       </c>
       <c r="V24" t="n">
-        <v>47.7491</v>
+        <v>46.51253</v>
       </c>
       <c r="W24" t="n">
-        <v>-80.27547</v>
+        <v>-82.64662</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
         </is>
       </c>
     </row>
@@ -2686,35 +2488,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kyle Lake No. 1</t>
+          <t>Buckles Mine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI43C06NW00002</t>
+          <t>MDI41J07NE00004</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ogoki</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>99.59999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Diamond, Kimberlite</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2725,31 +2527,21 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>14.5 Mt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1995 · Kwg Resc Inc</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>$396k</t>
-        </is>
-      </c>
+          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2008</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>KWG Resources Inc, Spider Resources Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
         <v>1</v>
@@ -2761,14 +2553,14 @@
         <v>50</v>
       </c>
       <c r="V25" t="n">
-        <v>52.46062</v>
+        <v>46.37605</v>
       </c>
       <c r="W25" t="n">
-        <v>-85.40002</v>
+        <v>-82.58892</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI43C06NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
         </is>
       </c>
     </row>
@@ -2778,21 +2570,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bannockburn Gold Project</t>
+          <t>Crystal-Comstock Property</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MDI31C12NE00195</t>
+          <t>MDI41I15SE00006</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Cryderman Subdivision</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.8</v>
+        <v>12.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2801,12 +2593,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2817,54 +2609,40 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.7 Mt (indicated)</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Au 1.64g/t</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>$221k</t>
-        </is>
-      </c>
+          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Crown William Mining Corp, Canadian Mono Mines Inc, Madoc Mining Company Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U26" t="n">
         <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>44.64988</v>
+        <v>46.75321</v>
       </c>
       <c r="W26" t="n">
-        <v>-77.54698</v>
+        <v>-80.62255</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
         </is>
       </c>
     </row>
@@ -2874,42 +2652,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Office Shaft</t>
+          <t>Nordic Mine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MDI41N13SW00013</t>
+          <t>MDI41J07NE00009</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Quebec Harbour</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>11.2</v>
+        <v>0.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium, Thorium, Yttrium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I27" t="b">
         <v>0</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2919,7 +2697,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9 drill hole(s) nearby · 1942–1955 · M J O'Brien Ltd(Burrage Copper)Jones, The American Metal Co Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2928,11 +2706,7 @@
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>1</v>
       </c>
@@ -2943,14 +2717,14 @@
         <v>50</v>
       </c>
       <c r="V27" t="n">
-        <v>47.76366</v>
+        <v>46.37802</v>
       </c>
       <c r="W27" t="n">
-        <v>-85.91361000000001</v>
+        <v>-82.58893</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
         </is>
       </c>
     </row>
@@ -2960,35 +2734,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Moneta Mine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI42A06NW00003</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Schumacher</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -3005,7 +2779,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
+          <t>The average grade of the ore in leucoxene andesite was approximately 0.60 oz/t and the average in the pillowed metavolcanics was 0.30 oz/t.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3016,23 +2790,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U28" t="n">
         <v>50</v>
       </c>
       <c r="V28" t="n">
-        <v>44.72488</v>
+        <v>48.47006</v>
       </c>
       <c r="W28" t="n">
-        <v>-78.80319</v>
+        <v>-81.32491</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A06NW00003</t>
         </is>
       </c>
     </row>
@@ -3042,30 +2816,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Contact Bay</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI000000000779</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3074,24 +2848,20 @@
         </is>
       </c>
       <c r="I29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>192 t produced</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3102,23 +2872,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V29" t="n">
-        <v>46.28991</v>
+        <v>49.69695</v>
       </c>
       <c r="W29" t="n">
-        <v>-83.20480999999999</v>
+        <v>-92.82165999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
         </is>
       </c>
     </row>
@@ -3128,35 +2898,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reserve Creek Occurrences</t>
+          <t>Net Lake Occurrence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDI42M12SE00008</t>
+          <t>MDI31M04SW00099</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Eabametoong First Nation</t>
+          <t>Temagami North</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
+          <t>Bismuth, Copper, Molybdenum, Nickel, Silver, Gold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -3167,54 +2937,40 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>272 kt (indicated)</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Mo 0.45%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>136 drill hole(s) nearby · 1942–2011 · Slam Exploration Ltd, Pricemore Resources Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>$3.5M</t>
-        </is>
-      </c>
+          <t>A grab sample of breccia collected by Myteque Mines assayed 1.35% Cu, 0.54% MoS2 and 0.34 oz/t Ag with a trace of gold. Hazelton assayed 2.45% Mo. Ciglen in 1956 returned best assays of 014% Ni, 0.23% Cu over 11 ft, and 0.47% Cu, 0.21% Pb and 0.03% Zn over 10.5 feet. An assay from an unspecified location and assayed by the Mines Branch, Ottawa returned 4.67% Mi, 0.10% Cu and 0.002 oz/t Au.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>7</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Slam Exploration Ltd, Eastmain Resources Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U30" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V30" t="n">
-        <v>51.57743</v>
+        <v>47.11985</v>
       </c>
       <c r="W30" t="n">
-        <v>-87.73681999999999</v>
+        <v>-79.78539000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SW00099</t>
         </is>
       </c>
     </row>
@@ -3224,21 +2980,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>McCoy Property</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31F03NW00055</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3247,16 +3003,16 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3269,7 +3025,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3280,23 +3036,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U31" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V31" t="n">
-        <v>46.30402</v>
+        <v>45.20254</v>
       </c>
       <c r="W31" t="n">
-        <v>-81.53989</v>
+        <v>-77.38281000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
         </is>
       </c>
     </row>
@@ -3306,21 +3062,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scramble Mine</t>
+          <t>Addington Mine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDI52E16SW00091</t>
+          <t>MDI31C11NE00010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pelletier Bridge</t>
+          <t>Flinton Corner</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,12 +3085,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -3345,50 +3101,40 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>150 kt (possible)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>$413k</t>
-        </is>
-      </c>
+          <t>3 drill hole(s) nearby · 1983–1984 · C Longmuir/ C. Roger Young, C R Young/ R. C. Longmuir</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Canstar Resources Inc, Pioneer Construction Inc, Alexander J R Pleson</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V32" t="n">
-        <v>49.78399</v>
+        <v>44.71386</v>
       </c>
       <c r="W32" t="n">
-        <v>-94.37701</v>
+        <v>-77.18101</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
         </is>
       </c>
     </row>
@@ -3398,35 +3144,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Geneva Lake Mine</t>
+          <t>Ogistoh Mine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MDI41I13SE00002</t>
+          <t>MDI31M04SE00026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Buffalo Rock</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
+          <t>Cobalt, Copper, Gold, Nickel, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -3437,50 +3183,40 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>103 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>$267k</t>
-        </is>
-      </c>
+          <t>Beland (1913) reported that an assay of 92 oz/t Ag over 6 feet was obtained at one place in the shaft. Miron in 1991 assayed 0.002 oz/t Au and a grab sample collected from the old dump site assayed 0.425% Cu, 0.794% Ni and 0.028 oz/t Au. A grab sample collected by the OGS from a sulphide rich zone within the gabbro/diorite assayed 0.46% Cu and 0.89% Ni. Ruttan assayed 0.64% Cu.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>16</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2014</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Green Swan Capital Corp, Champion Bear Resources Ltd, High-Sense Geophysics Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="U33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V33" t="n">
-        <v>46.7905</v>
+        <v>47.05917</v>
       </c>
       <c r="W33" t="n">
-        <v>-81.51521</v>
+        <v>-79.52840999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SE00026</t>
         </is>
       </c>
     </row>
@@ -3490,35 +3226,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Empire B Zone</t>
+          <t>Ore Chimney</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MDI31D16NE00146</t>
+          <t>MDI31C14SE00142</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>South Wilberforce</t>
+          <t>Bishop Corners</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uranium, Yttrium, Fluorite, Thorium</t>
+          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -3529,50 +3265,40 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.0 Mt (possible)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>$213k</t>
-        </is>
-      </c>
+          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>23</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>El Nino Ventures Inc, Frederick T Archibald, Republic Goldfields Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T34" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U34" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V34" t="n">
-        <v>44.99427</v>
+        <v>44.77617</v>
       </c>
       <c r="W34" t="n">
-        <v>-78.19589999999999</v>
+        <v>-77.15194</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
         </is>
       </c>
     </row>
@@ -3582,93 +3308,83 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Batlers Shaft</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41N13SW00012</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Quebec Harbour</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.7</v>
+        <v>11.1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
         <v>1</v>
       </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>934 kt (measured)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Gra 3.52%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>$254k</t>
-        </is>
-      </c>
+          <t>4 drill hole(s) nearby · 1942 · M J O'Brien Ltd(Burrage Copper)Jones</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>11</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2013</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Graphite Mountain Inc, Cardinal Explorations Inc, Mega Graphite Inc</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S35" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T35" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="V35" t="n">
-        <v>44.62168</v>
+        <v>47.76629</v>
       </c>
       <c r="W35" t="n">
-        <v>-76.56963</v>
+        <v>-85.91061999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00012</t>
         </is>
       </c>
     </row>
@@ -3678,35 +3394,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rutter Nepheline</t>
+          <t>Ethel Copper Property</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDI41I02SE00005</t>
+          <t>MDI41P09NW00014</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rutter</t>
+          <t>Elk Lake</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nepheline Syenite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I36" t="b">
@@ -3717,50 +3433,40 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>50.0 Mt (proven + probable)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1982 · Steep Rock Iron Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>$6k</t>
-        </is>
-      </c>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>5051318 Ontario Corp</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U36" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="V36" t="n">
-        <v>46.09664</v>
+        <v>47.7491</v>
       </c>
       <c r="W36" t="n">
-        <v>-80.67718000000001</v>
+        <v>-80.27547</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I02SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
         </is>
       </c>
     </row>
@@ -3770,35 +3476,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tashota-Nipigon</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDI42L04SE00005</t>
+          <t>MDI52A10NE00008</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Auden</t>
+          <t>Pearl</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>29.3</v>
+        <v>2.8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Bismuth, Copper, Silver</t>
+          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3809,54 +3515,40 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>45 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Au 2g/t</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>$1.7M</t>
-        </is>
-      </c>
+          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>10</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Kenorland Minerals Ltd, Sage Gold Inc, Willa Suzanne Nelson</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U37" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="V37" t="n">
-        <v>50.04735</v>
+        <v>48.67856</v>
       </c>
       <c r="W37" t="n">
-        <v>-87.58936</v>
+        <v>-88.62576</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
         </is>
       </c>
     </row>
@@ -3866,30 +3558,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C11SW00028</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Queensborough</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3898,24 +3590,20 @@
         </is>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>106 t produced</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3926,23 +3614,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T38" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U38" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V38" t="n">
-        <v>44.99932</v>
+        <v>44.58796</v>
       </c>
       <c r="W38" t="n">
-        <v>-78.32907</v>
+        <v>-77.43434000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3640,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hermina</t>
+          <t>Massey Mine No. 4 Shaft</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MDI41J01NE00007</t>
+          <t>MDI41J01NE00023</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3966,7 +3654,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3980,7 +3668,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I39" t="b">
@@ -3997,44 +3685,34 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>$561k</t>
-        </is>
-      </c>
+          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>9</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Mag Copper Ltd, Trelawney Mining and Exploration Inc, Citadel Gold Mines Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
+        <v>150</v>
+      </c>
+      <c r="U39" t="n">
         <v>50</v>
       </c>
-      <c r="U39" t="n">
-        <v>42</v>
-      </c>
       <c r="V39" t="n">
-        <v>46.23918</v>
+        <v>46.2376</v>
       </c>
       <c r="W39" t="n">
-        <v>-82.15586</v>
+        <v>-82.12882</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
         </is>
       </c>
     </row>
@@ -4044,97 +3722,79 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bridget Lake Occurrence</t>
+          <t>Pater Mine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MDI41N15NW00007</t>
+          <t>MDI41J02NE00002</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Michipicoten River</t>
+          <t>Spragge</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I40" t="b">
         <v>0</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>30 kt (possible)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Au 12.4g/t</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>$146k</t>
-        </is>
-      </c>
+          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>14</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2008</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Bridget Lake Resources Inc, Finneth Expl Inc, Ursula Konig</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T40" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V40" t="n">
-        <v>47.8998</v>
+        <v>46.20698</v>
       </c>
       <c r="W40" t="n">
-        <v>-84.85621</v>
+        <v>-82.6491</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
         </is>
       </c>
     </row>
@@ -4144,35 +3804,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lakemount Property</t>
+          <t>Golden Arrow - West</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MDI42C02SE00090</t>
+          <t>MDI42A08NW00004</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Vimy Ridge</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
+          <t>Gold, Copper, Lead</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -4183,13 +3843,13 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2.3 Mt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>98 drill hole(s) nearby · 1952–1982 · Kelore Mines Ltd, Firespur Expl Ltd · tested Copper, Nickel</t>
+          <t>77 drill hole(s) nearby · 1937–2015 · Golden Arrow Mines Ltd, Pamour Porcupine Mines · tested Gold</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4200,23 +3860,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U41" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="V41" t="n">
-        <v>48.06318</v>
+        <v>48.45691</v>
       </c>
       <c r="W41" t="n">
-        <v>-84.62636999999999</v>
+        <v>-80.40869000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A08NW00004</t>
         </is>
       </c>
     </row>
@@ -4226,30 +3886,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Black Lake Occurrence</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI41J01NW00026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4258,61 +3918,47 @@
         </is>
       </c>
       <c r="I42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>37 kt (indicated)</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Mo .52%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>$39k</t>
-        </is>
-      </c>
+          <t>13 drill hole(s) nearby · 1956–1966 · Gradore Mines Ltd, Sam Linton (Unknown) · tested Copper, Gold</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>2</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2009</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Douglas Lalonde, Douglas Joseph Lalonde</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U42" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="V42" t="n">
-        <v>45.30338</v>
+        <v>46.24374</v>
       </c>
       <c r="W42" t="n">
-        <v>-76.90682</v>
+        <v>-82.39867</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
         </is>
       </c>
     </row>
@@ -4322,30 +3968,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4354,38 +4000,28 @@
         </is>
       </c>
       <c r="I43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>80 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>$349k</t>
-        </is>
-      </c>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Douglas Garrie, First Nickel Inc</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
         <v>9</v>
@@ -4394,17 +4030,17 @@
         <v>225</v>
       </c>
       <c r="U43" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="V43" t="n">
-        <v>44.52895</v>
+        <v>44.72488</v>
       </c>
       <c r="W43" t="n">
-        <v>-77.78169</v>
+        <v>-78.80319</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -4414,17 +4050,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4432,12 +4068,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4453,35 +4089,21 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.5 Mt (probable)</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Gra 9.49%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>$36k</t>
-        </is>
-      </c>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>3</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2006</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Chris R Christensen, Judith Christensen, Rasmus H Christensen</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
         <v>13</v>
@@ -4490,17 +4112,17 @@
         <v>325</v>
       </c>
       <c r="U44" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>44.55883</v>
+        <v>46.30402</v>
       </c>
       <c r="W44" t="n">
-        <v>-76.57349000000001</v>
+        <v>-81.53989</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -4510,30 +4132,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4549,35 +4171,21 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>603 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Cal 77.93%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>$20k</t>
-        </is>
-      </c>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>2</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2009</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>1500448 Ontario Corp, Rock Brook Resources Corp, George O Gagnon</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>13</v>
@@ -4586,17 +4194,17 @@
         <v>325</v>
       </c>
       <c r="U45" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>45.58868</v>
+        <v>44.63956</v>
       </c>
       <c r="W45" t="n">
-        <v>-79.70944</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -4606,30 +4214,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Springer-Lavergne Rare Earth Project</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDI31L05NW00002</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Crystal Falls</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5.1</v>
+        <v>1.9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4638,61 +4246,47 @@
         </is>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4.2 Mt (indicated)</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Rar 1.139%, Tho 0.016%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>$1.3M</t>
-        </is>
-      </c>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>6</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Alcide Lavergne, Aldebert Lavergne, Annette Quenneville</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T46" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U46" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>46.44231</v>
+        <v>46.29559</v>
       </c>
       <c r="W46" t="n">
-        <v>-79.94853999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -4702,35 +4296,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -4741,50 +4335,40 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>136 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>$200k</t>
-        </is>
-      </c>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2014</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Big North Graphite, MPH Consulting Ltd, Douglas Lalonde</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U47" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="V47" t="n">
-        <v>45.29002</v>
+        <v>44.73856</v>
       </c>
       <c r="W47" t="n">
-        <v>-76.94167</v>
+        <v>-76.32056</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -4794,35 +4378,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4833,31 +4417,21 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2 kt (possible)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>$200k</t>
-        </is>
-      </c>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>3</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2014</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Big North Graphite, MPH Consulting Ltd, Douglas Lalonde</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
         <v>13</v>
@@ -4866,17 +4440,17 @@
         <v>325</v>
       </c>
       <c r="U48" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="V48" t="n">
-        <v>45.28947</v>
+        <v>44.55883</v>
       </c>
       <c r="W48" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -4886,30 +4460,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Abbican</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MDI41J06NE00044</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10.3</v>
+        <v>0.7</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4918,65 +4492,47 @@
         </is>
       </c>
       <c r="I49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>96 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Cu 1.08%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>30 drill hole(s) nearby · 1955–1968 · Milgate Mines Ltd, Abbican Mines Ltd · tested Copper, Gold</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>$23k</t>
-        </is>
-      </c>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>4</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2016</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Ashley Gold Mines Ltd, CJP Exploration Inc, Scott Woolhead</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="V49" t="n">
-        <v>46.47973</v>
+        <v>44.62168</v>
       </c>
       <c r="W49" t="n">
-        <v>-83.15055</v>
+        <v>-76.56963</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -4986,21 +4542,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Victoria Mine</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MDI41K09NE00019</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>French Bay</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>9.6</v>
+        <v>2.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5009,70 +4565,56 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>145 kt (unclassified)</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Zn 5.28%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1 Zone 1957 Unclassified 145150 160,000 tons averaging 5.28% combined lead and zinc and 1.73 ounces of silver per ton.</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>$244k</t>
-        </is>
-      </c>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>6</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2025</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>13369871 Canada Inc, Gold Diamet Resources Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="V50" t="n">
-        <v>46.63596</v>
+        <v>44.47438</v>
       </c>
       <c r="W50" t="n">
-        <v>-84.1369</v>
+        <v>-76.51861</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -5082,35 +4624,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eagle Copper Mine</t>
+          <t>Holdsworth Prospect</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MDI41K16SW00002</t>
+          <t>MDI42C02SE00011</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bourdages Corner</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -5124,51 +4666,37 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Cu 1.15%</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>$101k</t>
-        </is>
-      </c>
+          <t>68 drill hole(s) nearby · 1918–1989 · Soocana Mining, Algoma Steel Corp Ltd · tested Gold, Zinc</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>10</v>
-      </c>
-      <c r="P51" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Canadian Arrow Mines Ltd, John Alexander Rae, Clifford Hicks</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U51" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>46.75901</v>
+        <v>48.10921</v>
       </c>
       <c r="W51" t="n">
-        <v>-84.26090000000001</v>
+        <v>-84.58408</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00011</t>
         </is>
       </c>
     </row>
@@ -5178,35 +4706,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>Victoria Mine</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MDI31C10NW00016</t>
+          <t>MDI41K09NE00019</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>French Bay</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7</v>
+        <v>9.6</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
+          <t>Lead, Silver, Zinc, Copper, Gold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -5217,17 +4745,13 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>90 kt produced</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Zn 11.60%</t>
-        </is>
-      </c>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>42 drill hole(s) nearby · 1950–1975 · W H Douglas, Cons Rochette Mines Ltd</t>
+          <t>1 Zone 1957 Unclassified 145150 160,000 tons averaging 5.28% combined lead and zinc and 1.73 ounces of silver per ton.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5238,23 +4762,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U52" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="V52" t="n">
-        <v>44.6895</v>
+        <v>46.63596</v>
       </c>
       <c r="W52" t="n">
-        <v>-76.77161</v>
+        <v>-84.1369</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00019</t>
         </is>
       </c>
     </row>
@@ -5264,30 +4788,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Rock Lake</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J05NE00002</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Ophir</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5296,57 +4820,47 @@
         </is>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>907 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>$24k</t>
-        </is>
-      </c>
+          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>2</v>
-      </c>
-      <c r="P53" t="n">
-        <v>2010</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Carol Christine Cook, Golden Jaguar Explorations Ltd, D Dmitrovic</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U53" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="V53" t="n">
-        <v>44.5021</v>
+        <v>46.44114</v>
       </c>
       <c r="W53" t="n">
-        <v>-77.61301</v>
+        <v>-83.73430999999999</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
         </is>
       </c>
     </row>
@@ -5356,21 +4870,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Quebec Mine - Main Shaft</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41N13SW00003</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Quebec Harbour</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6.5</v>
+        <v>11.1</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5379,7 +4893,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5388,20 +4902,20 @@
         </is>
       </c>
       <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
         <v>1</v>
       </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>in 1955 was 0.11% Cu over 5 ft. Grades of mineralization reportedly exceeded 2.5% Cu over 3 to 6 feet underground.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5410,25 +4924,29 @@
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T54" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="U54" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="V54" t="n">
-        <v>48.69799</v>
+        <v>47.76464</v>
       </c>
       <c r="W54" t="n">
-        <v>-93.27513999999999</v>
+        <v>-85.91225</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00003</t>
         </is>
       </c>
     </row>
@@ -5438,30 +4956,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Jardun Mine - No 3 Zone</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI41K09NE00090</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Northland</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>71.8</v>
+        <v>9.6</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5470,20 +4988,20 @@
         </is>
       </c>
       <c r="I55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>5 kt (possible)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>137 drill hole(s) nearby · 1951–1984 · Longbow Exploration Inc/Watson Lake Mines Ltd, Jardun Mines Ltd · tested Copper, Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5494,23 +5012,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U55" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="V55" t="n">
-        <v>54.51539</v>
+        <v>46.63751</v>
       </c>
       <c r="W55" t="n">
-        <v>-91.40791</v>
+        <v>-84.14293000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00090</t>
         </is>
       </c>
     </row>
@@ -5520,35 +5038,35 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I56" t="b">
@@ -5559,13 +5077,13 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -5582,17 +5100,17 @@
         <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="V56" t="n">
-        <v>45.21442</v>
+        <v>45.58868</v>
       </c>
       <c r="W56" t="n">
-        <v>-77.8742</v>
+        <v>-79.70944</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -5602,21 +5120,21 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Contact Bay</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDI000000000779</t>
+          <t>MDI31C12SE00039</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5625,12 +5143,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -5641,50 +5159,40 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>118 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>$2.7M</t>
-        </is>
-      </c>
+          <t>15 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>7</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>KG Exploration (Canada) Inc, Pure Gold Mining Inc, Heritage Mining Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T57" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U57" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="V57" t="n">
-        <v>49.69695</v>
+        <v>44.51231</v>
       </c>
       <c r="W57" t="n">
-        <v>-92.82165999999999</v>
+        <v>-77.62011</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
         </is>
       </c>
     </row>
@@ -5694,21 +5202,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crystal-Comstock Property</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MDI41I15SE00006</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cryderman Subdivision</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>12.9</v>
+        <v>0.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5717,7 +5225,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5733,50 +5241,40 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>741 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>$1.7M</t>
-        </is>
-      </c>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
-        <v>17</v>
-      </c>
-      <c r="P58" t="n">
-        <v>2023</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Inventus Mining Corp, North American Palladium Ltd, Flag Resources (1985) Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T58" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U58" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="V58" t="n">
-        <v>46.75321</v>
+        <v>44.5143</v>
       </c>
       <c r="W58" t="n">
-        <v>-80.62255</v>
+        <v>-77.61444</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -5786,35 +5284,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Worthington Mine</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDI41I06NW00005</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Worthington</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4</v>
+        <v>5.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -5825,50 +5323,40 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>23 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>A sample taken from the Worthington Shaft by Wallbridge Mining Company assayed 0.219% Cu, and 0.0388% Ni. Shipments averaged 8% Ni;</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>$1.3M</t>
-        </is>
-      </c>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>8</v>
-      </c>
-      <c r="P59" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Vale Canada Ltd, Wallbridge Mining Company Ltd, Inco Ltd</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U59" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="V59" t="n">
-        <v>46.38402</v>
+        <v>49.71016</v>
       </c>
       <c r="W59" t="n">
-        <v>-81.44789</v>
+        <v>-94.40097</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -5878,56 +5366,56 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>45 kt (unclassified)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Gra 7%</t>
+          <t>Mo 2.00%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Nortoba Mines, B C Lamble · tested Gold</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5938,23 +5426,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U60" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="V60" t="n">
-        <v>44.85917</v>
+        <v>49.69198</v>
       </c>
       <c r="W60" t="n">
-        <v>-76.15956</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>
@@ -5964,30 +5452,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stanleyville Vermiculite</t>
+          <t>Band-Ore Mattagami Zone 4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MDI31C16SW00030</t>
+          <t>MDI52B09SE00024</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Shebandowan</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Vermiculite</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6009,7 +5497,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6020,23 +5508,23 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U61" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V61" t="n">
-        <v>44.79726</v>
+        <v>48.62462</v>
       </c>
       <c r="W61" t="n">
-        <v>-76.32017999999999</v>
+        <v>-90.12229000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
         </is>
       </c>
     </row>
@@ -6046,21 +5534,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>McCoy Property</t>
+          <t>Abbican</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MDI31F03NW00055</t>
+          <t>MDI41J06NE00044</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6069,48 +5557,42 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I62" t="b">
         <v>0</v>
       </c>
       <c r="J62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>$588k</t>
-        </is>
-      </c>
+          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62" t="n">
-        <v>2011</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>First Nickel Inc, Ralph V Stewart, Glenn George Crawford</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S62" t="n">
         <v>1</v>
       </c>
@@ -6118,17 +5600,17 @@
         <v>25</v>
       </c>
       <c r="U62" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>45.20254</v>
+        <v>46.47973</v>
       </c>
       <c r="W62" t="n">
-        <v>-77.38281000000001</v>
+        <v>-83.15055</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
         </is>
       </c>
     </row>
@@ -6138,35 +5620,35 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Climax</t>
+          <t>Scramble Mine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MDI52A05SE00016</t>
+          <t>MDI52E16SW00091</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Pelletier Bridge</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -6177,50 +5659,40 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>$525k</t>
-        </is>
-      </c>
+          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>7</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2022</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Honey Badger Exploration Inc, Honey Badger Silver Inc, Allan Edward Hietapakka</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U63" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="V63" t="n">
-        <v>48.31312</v>
+        <v>49.78399</v>
       </c>
       <c r="W63" t="n">
-        <v>-89.66484</v>
+        <v>-94.37701</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
         </is>
       </c>
     </row>
@@ -6230,75 +5702,61 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Lakemount Property</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MDI41I04NE00004</t>
+          <t>MDI42C02SE00090</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>McGregor Bay</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I64" t="b">
         <v>0</v>
       </c>
       <c r="J64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1979 · Curtin Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>$157k</t>
-        </is>
-      </c>
+          <t>98 drill hole(s) nearby · 1952–1982 · Kelore Mines Ltd, New Kelore Mines Ltd · tested Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>6</v>
-      </c>
-      <c r="P64" t="n">
-        <v>2008</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Dan A Brunne, Roger Stringer, Dan Brunne</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>abuts Killarney Lakelands And Headwaters Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
         <v>1</v>
       </c>
@@ -6306,17 +5764,17 @@
         <v>25</v>
       </c>
       <c r="U64" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>46.14902</v>
+        <v>48.06318</v>
       </c>
       <c r="W64" t="n">
-        <v>-81.62088</v>
+        <v>-84.62636999999999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I04NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
         </is>
       </c>
     </row>
@@ -6326,35 +5784,35 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MDI31C12SE00033</t>
+          <t>MDI42A09SW00163</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Holtyre</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -6365,50 +5823,40 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>489 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>$24k</t>
-        </is>
-      </c>
+          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons Ltd · tested Gold</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="n">
-        <v>2</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2010</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Carol Christine Cook, Golden Jaguar Explorations Ltd, D Dmitrovic</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U65" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V65" t="n">
-        <v>44.50806</v>
+        <v>48.50619</v>
       </c>
       <c r="W65" t="n">
-        <v>-77.61564</v>
+        <v>-80.31543000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
         </is>
       </c>
     </row>
@@ -6418,35 +5866,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Springer-Lavergne Rare Earth Project</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31L05NW00002</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Crystal Falls</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -6457,50 +5905,40 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>$22k</t>
-        </is>
-      </c>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1997</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Robert J Ross, D Dmitrovic</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U66" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>44.5143</v>
+        <v>46.44231</v>
       </c>
       <c r="W66" t="n">
-        <v>-77.61444</v>
+        <v>-79.94853999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
         </is>
       </c>
     </row>
@@ -6510,35 +5948,35 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vermor Gold Mine</t>
+          <t>Simon Copper Property</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MDI52K01SW00004</t>
+          <t>MDI31F03NW00044</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Slate Falls</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10.9</v>
+        <v>4.6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Zinc, Iron, Selenium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -6549,50 +5987,40 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>39 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>$22k</t>
-        </is>
-      </c>
+          <t>49 drill hole(s) nearby · 1956–2008 · Malcolm Property, Noranda Exploration Co Ltd · tested Copper, Zinc, Gold, Nickel</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="n">
-        <v>4</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Ivar Joseph Riives, Gossan Resources Ltd, Alexander Glatz</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U67" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V67" t="n">
-        <v>50.01111</v>
+        <v>45.20807</v>
       </c>
       <c r="W67" t="n">
-        <v>-92.2621</v>
+        <v>-77.31331</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
         </is>
       </c>
     </row>
@@ -6602,35 +6030,35 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Moneta Mine</t>
+          <t>Macassa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MDI42A06NW00003</t>
+          <t>MDI31C13SE00099</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Schumacher</t>
+          <t>Ormsby</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -6641,50 +6069,40 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>346 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>The average grade of the ore in leucoxene andesite was approximately 0.60 oz/t and the average in the pillowed metavolcanics was 0.30 oz/t.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>$14k</t>
-        </is>
-      </c>
+          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2019</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Hermann Daxl</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T68" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U68" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V68" t="n">
-        <v>48.47006</v>
+        <v>44.868</v>
       </c>
       <c r="W68" t="n">
-        <v>-81.32491</v>
+        <v>-77.72254</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A06NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
         </is>
       </c>
     </row>
@@ -6694,35 +6112,35 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nordic Mine</t>
+          <t>Hermina</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDI41J07NE00009</t>
+          <t>MDI41J01NE00007</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Yttrium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -6733,50 +6151,40 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>754 kt (proven)</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>$12k</t>
-        </is>
-      </c>
+          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>2</v>
-      </c>
-      <c r="P69" t="n">
-        <v>2008</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Abitibi Mining Corp</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U69" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V69" t="n">
-        <v>46.37802</v>
+        <v>46.23918</v>
       </c>
       <c r="W69" t="n">
-        <v>-82.58893</v>
+        <v>-82.15586</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
         </is>
       </c>
     </row>
@@ -6786,35 +6194,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Buckles Mine</t>
+          <t>Shoot Zone Deposit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MDI41J07NE00004</t>
+          <t>MDI42A10SE00065</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -6825,50 +6233,40 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>250 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>$12k</t>
-        </is>
-      </c>
+          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>2</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2008</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Abitibi Mining Corp</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V70" t="n">
-        <v>46.37605</v>
+        <v>48.56426</v>
       </c>
       <c r="W70" t="n">
-        <v>-82.58892</v>
+        <v>-80.63866</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
         </is>
       </c>
     </row>
@@ -6878,35 +6276,35 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Empire B Zone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MDI31C11SW00028</t>
+          <t>MDI31D16NE00146</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Queensborough</t>
+          <t>South Wilberforce</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Uranium, Yttrium, Fluorite, Thorium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -6917,50 +6315,40 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>$12k</t>
-        </is>
-      </c>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" t="n">
-        <v>1996</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>W J Brown</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V71" t="n">
-        <v>44.58796</v>
+        <v>44.99427</v>
       </c>
       <c r="W71" t="n">
-        <v>-77.43434000000001</v>
+        <v>-78.19589999999999</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
         </is>
       </c>
     </row>
@@ -6970,21 +6358,21 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bannockburn Gold Project</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MDI31C12SE00039</t>
+          <t>MDI31C12NE00195</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6993,12 +6381,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I72" t="b">
@@ -7009,50 +6397,40 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>36 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Gold, Copper</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>$10k</t>
-        </is>
-      </c>
+          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="P72" t="n">
-        <v>1995</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>D Dmitrovic</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T72" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U72" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="V72" t="n">
-        <v>44.51231</v>
+        <v>44.64988</v>
       </c>
       <c r="W72" t="n">
-        <v>-77.62011</v>
+        <v>-77.54698</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
         </is>
       </c>
     </row>
@@ -7062,35 +6440,35 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pater Mine</t>
+          <t>Reserve Creek Occurrences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MDI41J02NE00002</t>
+          <t>MDI42M12SE00008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Spragge</t>
+          <t>Eabametoong First Nation</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I73" t="b">
@@ -7101,13 +6479,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1.8 Mt produced</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Mo 0.45%</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Goldpost Resources Inc · tested Gold</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -7118,23 +6500,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U73" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V73" t="n">
-        <v>46.20698</v>
+        <v>51.57743</v>
       </c>
       <c r="W73" t="n">
-        <v>-82.6491</v>
+        <v>-87.73681999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
         </is>
       </c>
     </row>
@@ -7144,35 +6526,35 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Quirke No. 1</t>
+          <t>Eagle Copper Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MDI41J10SE00007</t>
+          <t>MDI41K16SW00002</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Bourdages Corner</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uranium, Rare Earth Elements, Thorium</t>
+          <t>Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I74" t="b">
@@ -7183,13 +6565,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>8.0 Mt produced</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Cu 1.15%</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -7206,17 +6592,17 @@
         <v>25</v>
       </c>
       <c r="U74" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="V74" t="n">
-        <v>46.51253</v>
+        <v>46.75901</v>
       </c>
       <c r="W74" t="n">
-        <v>-82.64662</v>
+        <v>-84.26090000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
         </is>
       </c>
     </row>
@@ -7226,35 +6612,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Gatling Five Acre</t>
+          <t>Shawmere Anorthosite</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MDI31C12SE00028</t>
+          <t>MDI42B02NW00001</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Foleyet</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.4</v>
+        <v>28.7</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Aluminum, Feldspar (Nonmetals), Silica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I75" t="b">
@@ -7265,13 +6651,13 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>4 kt produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd · tested Copper</t>
+          <t>11 drill hole(s) nearby · 1994 · Purchem Ltd</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -7282,23 +6668,23 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U75" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="V75" t="n">
-        <v>44.51496</v>
+        <v>48.13236</v>
       </c>
       <c r="W75" t="n">
-        <v>-77.62126000000001</v>
+        <v>-82.78859</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42B02NW00001</t>
         </is>
       </c>
     </row>
@@ -7308,35 +6694,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Holdsworth Prospect</t>
+          <t>95-2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MDI42C02SE00011</t>
+          <t>MDI31M12SW00017</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Diamond, Kimberlite</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I76" t="b">
@@ -7347,13 +6733,13 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>60 t produced</t>
+          <t>no tonnage on record</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>68 drill hole(s) nearby · 1918–1989 · Algoma Steel Corp Ltd, Reed Lake Expl Ltd · tested Gold, Zinc</t>
+          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -7370,17 +6756,431 @@
         <v>25</v>
       </c>
       <c r="U76" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="V76" t="n">
-        <v>48.10921</v>
+        <v>47.52342</v>
       </c>
       <c r="W76" t="n">
-        <v>-84.58408</v>
+        <v>-79.89148</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Stanleyville Vermiculite</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MDI31C16SW00030</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Stanleyville</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Vermiculite</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="n">
+        <v>125</v>
+      </c>
+      <c r="U77" t="n">
+        <v>27</v>
+      </c>
+      <c r="V77" t="n">
+        <v>44.79726</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-76.32017999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Rutter Nepheline</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MDI41I02SE00005</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Rutter</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nepheline Syenite</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>3 drill hole(s) nearby · 1982 · Steep Rock Iron Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
+        <v>75</v>
+      </c>
+      <c r="U78" t="n">
+        <v>27</v>
+      </c>
+      <c r="V78" t="n">
+        <v>46.09664</v>
+      </c>
+      <c r="W78" t="n">
+        <v>-80.67718000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I02SE00005</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kyle Lake No. 1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MDI43C06NW00002</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Ogoki</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Diamond, Kimberlite</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1995 · Kwg Resc Inc</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>25</v>
+      </c>
+      <c r="U79" t="n">
+        <v>27</v>
+      </c>
+      <c r="V79" t="n">
+        <v>52.46062</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-85.40002</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI43C06NW00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Jayfran-Pipawa</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MDI31F04SE00036</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Vardy</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nepheline Syenite, Uranium</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>150</v>
+      </c>
+      <c r="U80" t="n">
+        <v>27</v>
+      </c>
+      <c r="V80" t="n">
+        <v>45.09484</v>
+      </c>
+      <c r="W80" t="n">
+        <v>-77.76734999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Northern Kyanite</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MDI41I10SE00004</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wahnapitae</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>3</v>
+      </c>
+      <c r="T81" t="n">
+        <v>75</v>
+      </c>
+      <c r="U81" t="n">
+        <v>27</v>
+      </c>
+      <c r="V81" t="n">
+        <v>46.50103</v>
+      </c>
+      <c r="W81" t="n">
+        <v>-80.73585</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:X74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -828,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -893,14 +893,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.85917</v>
+        <v>45.28947</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.15956</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -910,21 +910,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -975,14 +975,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.28947</v>
+        <v>45.30338</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -992,21 +992,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1057,14 +1057,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.30338</v>
+        <v>45.29002</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.90682</v>
+        <v>-76.94167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1139,14 +1139,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.29002</v>
+        <v>44.85917</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94167</v>
+        <v>-76.15956</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1212,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="U9" t="n">
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>46.23809</v>
+        <v>44.55104</v>
       </c>
       <c r="W9" t="n">
-        <v>-82.11991</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1238,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1303,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>45.21442</v>
+        <v>48.24876</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.8742</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>44.55104</v>
+        <v>45.21442</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.8742</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1402,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U12" t="n">
         <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>48.24876</v>
+        <v>44.72488</v>
       </c>
       <c r="W12" t="n">
-        <v>-89.86754000000001</v>
+        <v>-78.80319</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71.8</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1526,10 +1526,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1546,17 +1550,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="V13" t="n">
-        <v>54.51539</v>
+        <v>44.99932</v>
       </c>
       <c r="W13" t="n">
-        <v>-91.40791</v>
+        <v>-78.32907</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1566,30 +1570,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1608,14 +1612,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>44.99932</v>
+        <v>44.5143</v>
       </c>
       <c r="W14" t="n">
-        <v>-78.32907</v>
+        <v>-77.61444</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1652,21 +1652,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1697,7 +1697,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1734,30 +1734,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Temagami Copper Mine</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41I16NE00004</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Adanac</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1776,14 +1776,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1794,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>46.96233</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-80.03716</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1820,30 +1816,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>Kristina</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C10NW00016</t>
+          <t>MDI41K16NE00002</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>Wabos</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7</v>
+        <v>7.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1864,12 +1860,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Zn 11.60%</t>
+          <t>Cu 6.21%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>42 drill hole(s) nearby · 1950–1975 · Cons Rochette Mines Ltd, W H Douglas</t>
+          <t>An average grade might be 2.7% copper.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1880,23 +1876,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V17" t="n">
-        <v>44.6895</v>
+        <v>46.88544</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.77161</v>
+        <v>-84.09032000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16NE00002</t>
         </is>
       </c>
     </row>
@@ -1906,30 +1902,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sand River Gold Mine</t>
+          <t>Temagami Copper Mine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52H09SE00005</t>
+          <t>MDI41I16NE00004</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Adanac</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten</t>
+          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1950,12 +1946,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>W 0.23%</t>
+          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1987–1988 · Cryderman Gold Inc · tested Gold</t>
+          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1966,23 +1962,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V18" t="n">
-        <v>49.62195</v>
+        <v>46.96233</v>
       </c>
       <c r="W18" t="n">
-        <v>-88.04667000000001</v>
+        <v>-80.03716</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
         </is>
       </c>
     </row>
@@ -1992,35 +1988,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ogema</t>
+          <t>Sand River Gold Mine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52A15SE00006</t>
+          <t>MDI52H09SE00005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dorion</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Amethyst, Barite, Copper, Fluorite, Silver</t>
+          <t>Gold, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2034,10 +2030,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>W 0.23%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1961 · Sogemines Dev Co Ltd · tested Zinc</t>
+          <t>12 drill hole(s) nearby · 1987–1988 · Cryderman Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2048,23 +2048,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V19" t="n">
-        <v>48.76995</v>
+        <v>49.62195</v>
       </c>
       <c r="W19" t="n">
-        <v>-88.73446</v>
+        <v>-88.04667000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A15SE00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09SE00005</t>
         </is>
       </c>
     </row>
@@ -2074,30 +2074,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rabbit Mountain</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI52A05SE00008</t>
+          <t>MDI31C12SE00033</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Harstone</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2119,7 +2119,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
+          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2130,23 +2130,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U20" t="n">
         <v>50</v>
       </c>
       <c r="V20" t="n">
-        <v>48.30674</v>
+        <v>44.50806</v>
       </c>
       <c r="W20" t="n">
-        <v>-89.60534</v>
+        <v>-77.61564</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
         </is>
       </c>
     </row>
@@ -2156,35 +2156,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Beaver</t>
+          <t>Rabbit Mountain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI52A05SE00009</t>
+          <t>MDI52A05SE00008</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Harstone</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2201,7 +2201,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, Honey Badger Exploration Inc · tested Silver, Zinc</t>
+          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2221,14 +2221,14 @@
         <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>48.31944</v>
+        <v>48.30674</v>
       </c>
       <c r="W21" t="n">
-        <v>-89.63952999999999</v>
+        <v>-89.60534</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
         </is>
       </c>
     </row>
@@ -2238,30 +2238,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Silver Mountain West</t>
+          <t>Beaver</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI52A04NW00003</t>
+          <t>MDI52A05SE00009</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2283,7 +2283,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
+          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, Honey Badger Exploration Inc · tested Silver, Zinc</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2294,23 +2294,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U22" t="n">
         <v>50</v>
       </c>
       <c r="V22" t="n">
-        <v>48.24757</v>
+        <v>48.31944</v>
       </c>
       <c r="W22" t="n">
-        <v>-89.8866</v>
+        <v>-89.63952999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
         </is>
       </c>
     </row>
@@ -2406,30 +2406,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quirke No. 1</t>
+          <t>Pater Mine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI41J10SE00007</t>
+          <t>MDI41J02NE00002</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Spragge</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>0.8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Uranium, Rare Earth Elements, Thorium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2451,7 +2451,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2462,23 +2462,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U24" t="n">
         <v>50</v>
       </c>
       <c r="V24" t="n">
-        <v>46.51253</v>
+        <v>46.20698</v>
       </c>
       <c r="W24" t="n">
-        <v>-82.64662</v>
+        <v>-82.6491</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
         </is>
       </c>
     </row>
@@ -2488,35 +2488,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buckles Mine</t>
+          <t>Contact Bay</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI41J07NE00004</t>
+          <t>MDI000000000779</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2533,7 +2533,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2553,14 +2553,14 @@
         <v>50</v>
       </c>
       <c r="V25" t="n">
-        <v>46.37605</v>
+        <v>49.69695</v>
       </c>
       <c r="W25" t="n">
-        <v>-82.58892</v>
+        <v>-92.82165999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nordic Mine</t>
+          <t>Quirke No. 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MDI41J07NE00009</t>
+          <t>MDI41J10SE00007</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9</v>
+        <v>16</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Yttrium</t>
+          <t>Uranium, Rare Earth Elements, Thorium</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2697,7 +2697,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
+          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2717,14 +2717,14 @@
         <v>50</v>
       </c>
       <c r="V27" t="n">
-        <v>46.37802</v>
+        <v>46.51253</v>
       </c>
       <c r="W27" t="n">
-        <v>-82.58893</v>
+        <v>-82.64662</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
         </is>
       </c>
     </row>
@@ -2734,35 +2734,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Moneta Mine</t>
+          <t>Massey Mine No. 4 Shaft</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDI42A06NW00003</t>
+          <t>MDI41J01NE00023</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Schumacher</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -2779,7 +2779,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>The average grade of the ore in leucoxene andesite was approximately 0.60 oz/t and the average in the pillowed metavolcanics was 0.30 oz/t.</t>
+          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2790,23 +2790,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U28" t="n">
         <v>50</v>
       </c>
       <c r="V28" t="n">
-        <v>48.47006</v>
+        <v>46.2376</v>
       </c>
       <c r="W28" t="n">
-        <v>-81.32491</v>
+        <v>-82.12882</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A06NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
         </is>
       </c>
     </row>
@@ -2816,30 +2816,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Contact Bay</t>
+          <t>McCoy Property</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDI000000000779</t>
+          <t>MDI31F03NW00055</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2861,7 +2861,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
+          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2881,14 +2881,14 @@
         <v>50</v>
       </c>
       <c r="V29" t="n">
-        <v>49.69695</v>
+        <v>45.20254</v>
       </c>
       <c r="W29" t="n">
-        <v>-92.82165999999999</v>
+        <v>-77.38281000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Net Lake Occurrence</t>
+          <t>Buckles Mine</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDI31M04SW00099</t>
+          <t>MDI41J07NE00004</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Temagami North</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bismuth, Copper, Molybdenum, Nickel, Silver, Gold</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -2943,7 +2943,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>A grab sample of breccia collected by Myteque Mines assayed 1.35% Cu, 0.54% MoS2 and 0.34 oz/t Ag with a trace of gold. Hazelton assayed 2.45% Mo. Ciglen in 1956 returned best assays of 014% Ni, 0.23% Cu over 11 ft, and 0.47% Cu, 0.21% Pb and 0.03% Zn over 10.5 feet. An assay from an unspecified location and assayed by the Mines Branch, Ottawa returned 4.67% Mi, 0.10% Cu and 0.002 oz/t Au.</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2954,23 +2954,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U30" t="n">
         <v>50</v>
       </c>
       <c r="V30" t="n">
-        <v>47.11985</v>
+        <v>46.37605</v>
       </c>
       <c r="W30" t="n">
-        <v>-79.78539000000001</v>
+        <v>-82.58892</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SW00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
         </is>
       </c>
     </row>
@@ -2980,35 +2980,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>McCoy Property</t>
+          <t>Nordic Mine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDI31F03NW00055</t>
+          <t>MDI41J07NE00009</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum</t>
+          <t>Uranium, Thorium, Yttrium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -3025,7 +3025,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3045,14 +3045,14 @@
         <v>50</v>
       </c>
       <c r="V31" t="n">
-        <v>45.20254</v>
+        <v>46.37802</v>
       </c>
       <c r="W31" t="n">
-        <v>-77.38281000000001</v>
+        <v>-82.58893</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
         </is>
       </c>
     </row>
@@ -3062,30 +3062,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Addington Mine</t>
+          <t>Net Lake Occurrence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDI31C11NE00010</t>
+          <t>MDI31M04SW00099</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Flinton Corner</t>
+          <t>Temagami North</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Bismuth</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Tungsten</t>
+          <t>Bismuth, Copper, Molybdenum, Nickel, Silver, Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3107,7 +3107,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1983–1984 · C Longmuir/ C. Roger Young, C R Young/ R. C. Longmuir</t>
+          <t>A grab sample of breccia collected by Myteque Mines assayed 1.35% Cu, 0.54% MoS2 and 0.34 oz/t Ag with a trace of gold. Hazelton assayed 2.45% Mo. Ciglen in 1956 returned best assays of 014% Ni, 0.23% Cu over 11 ft, and 0.47% Cu, 0.21% Pb and 0.03% Zn over 10.5 feet. An assay from an unspecified location and assayed by the Mines Branch, Ottawa returned 4.67% Mi, 0.10% Cu and 0.002 oz/t Au.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3118,23 +3118,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="U32" t="n">
         <v>50</v>
       </c>
       <c r="V32" t="n">
-        <v>44.71386</v>
+        <v>47.11985</v>
       </c>
       <c r="W32" t="n">
-        <v>-77.18101</v>
+        <v>-79.78539000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SW00099</t>
         </is>
       </c>
     </row>
@@ -3226,30 +3226,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ore Chimney</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MDI31C14SE00142</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bishop Corners</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3271,7 +3271,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3291,14 +3291,14 @@
         <v>50</v>
       </c>
       <c r="V34" t="n">
-        <v>44.77617</v>
+        <v>46.23809</v>
       </c>
       <c r="W34" t="n">
-        <v>-77.15194</v>
+        <v>-82.11991</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -3308,30 +3308,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Batlers Shaft</t>
+          <t>Ogema</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDI41N13SW00012</t>
+          <t>MDI52A15SE00006</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Quebec Harbour</t>
+          <t>Dorion</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>11.1</v>
+        <v>6.2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc, Amethyst, Barite, Copper, Fluorite, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>4 drill hole(s) nearby · 1942 · M J O'Brien Ltd(Burrage Copper)Jones</t>
+          <t>2 drill hole(s) nearby · 1961 · Sogemines Dev Co Ltd · tested Zinc</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3362,29 +3362,25 @@
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="U35" t="n">
         <v>50</v>
       </c>
       <c r="V35" t="n">
-        <v>47.76629</v>
+        <v>48.76995</v>
       </c>
       <c r="W35" t="n">
-        <v>-85.91061999999999</v>
+        <v>-88.73446</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00012</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A15SE00006</t>
         </is>
       </c>
     </row>
@@ -3394,21 +3390,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ethel Copper Property</t>
+          <t>Worthington Mine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDI41P09NW00014</t>
+          <t>MDI41I06NW00005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Elk Lake</t>
+          <t>Worthington</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3417,7 +3413,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3439,7 +3435,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
+          <t>A sample taken from the Worthington Shaft by Wallbridge Mining Company assayed 0.219% Cu, and 0.0388% Ni. Shipments averaged 8% Ni;</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3459,14 +3455,14 @@
         <v>50</v>
       </c>
       <c r="V36" t="n">
-        <v>47.7491</v>
+        <v>46.38402</v>
       </c>
       <c r="W36" t="n">
-        <v>-80.27547</v>
+        <v>-81.44789</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00005</t>
         </is>
       </c>
     </row>
@@ -3476,30 +3472,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Vermor Gold Mine</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDI52A10NE00008</t>
+          <t>MDI52K01SW00004</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pearl</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.8</v>
+        <v>10.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3521,7 +3517,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
+          <t>19 drill hole(s) nearby · 1951–1989 · Denree Cons Mines Ltd, D E Smith</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3532,23 +3528,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="U37" t="n">
         <v>50</v>
       </c>
       <c r="V37" t="n">
-        <v>48.67856</v>
+        <v>50.01111</v>
       </c>
       <c r="W37" t="n">
-        <v>-88.62576</v>
+        <v>-92.26211000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
         </is>
       </c>
     </row>
@@ -3558,30 +3554,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Ethel Copper Property</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDI31C11SW00028</t>
+          <t>MDI41P09NW00014</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Queensborough</t>
+          <t>Elk Lake</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3603,7 +3599,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3614,23 +3610,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U38" t="n">
         <v>50</v>
       </c>
       <c r="V38" t="n">
-        <v>44.58796</v>
+        <v>47.7491</v>
       </c>
       <c r="W38" t="n">
-        <v>-77.43434000000001</v>
+        <v>-80.27547</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
         </is>
       </c>
     </row>
@@ -3640,30 +3636,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Massey Mine No. 4 Shaft</t>
+          <t>Climax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MDI41J01NE00023</t>
+          <t>MDI52A05SE00016</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3685,7 +3681,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
+          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3696,23 +3692,23 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U39" t="n">
         <v>50</v>
       </c>
       <c r="V39" t="n">
-        <v>46.2376</v>
+        <v>48.31312</v>
       </c>
       <c r="W39" t="n">
-        <v>-82.12882</v>
+        <v>-89.66484</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
         </is>
       </c>
     </row>
@@ -3722,21 +3718,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pater Mine</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MDI41J02NE00002</t>
+          <t>MDI52A10NE00008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Spragge</t>
+          <t>Pearl</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3745,12 +3741,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I40" t="b">
@@ -3767,7 +3763,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3778,23 +3774,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="U40" t="n">
         <v>50</v>
       </c>
       <c r="V40" t="n">
-        <v>46.20698</v>
+        <v>48.67856</v>
       </c>
       <c r="W40" t="n">
-        <v>-82.6491</v>
+        <v>-88.62576</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
         </is>
       </c>
     </row>
@@ -3804,21 +3800,21 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Golden Arrow - West</t>
+          <t>Addington Mine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MDI42A08NW00004</t>
+          <t>MDI31C11NE00010</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vimy Ridge</t>
+          <t>Flinton Corner</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3827,12 +3823,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Copper, Lead</t>
+          <t>Gold, Copper, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I41" t="b">
@@ -3849,7 +3845,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>77 drill hole(s) nearby · 1937–2015 · Golden Arrow Mines Ltd, Pamour Porcupine Mines · tested Gold</t>
+          <t>3 drill hole(s) nearby · 1983–1984 · C Longmuir/ C. Roger Young, C R Young/ R. C. Longmuir</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3860,23 +3856,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U41" t="n">
         <v>50</v>
       </c>
       <c r="V41" t="n">
-        <v>48.45691</v>
+        <v>44.71386</v>
       </c>
       <c r="W41" t="n">
-        <v>-80.40869000000001</v>
+        <v>-77.18101</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A08NW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
         </is>
       </c>
     </row>
@@ -3886,30 +3882,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Black Lake Occurrence</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MDI41J01NW00026</t>
+          <t>MDI31C11SW00028</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Queensborough</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3931,7 +3927,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1956–1966 · Gradore Mines Ltd, Sam Linton (Unknown) · tested Copper, Gold</t>
+          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3942,23 +3938,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T42" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U42" t="n">
         <v>50</v>
       </c>
       <c r="V42" t="n">
-        <v>46.24374</v>
+        <v>44.58796</v>
       </c>
       <c r="W42" t="n">
-        <v>-82.39867</v>
+        <v>-77.43434000000001</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
         </is>
       </c>
     </row>
@@ -3968,39 +3964,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -4013,7 +4009,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4024,23 +4020,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V43" t="n">
-        <v>44.72488</v>
+        <v>44.62168</v>
       </c>
       <c r="W43" t="n">
-        <v>-78.80319</v>
+        <v>-76.56963</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -4050,30 +4046,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4095,7 +4091,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4115,14 +4111,14 @@
         <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W44" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -4132,30 +4128,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4177,7 +4173,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4188,23 +4184,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U45" t="n">
         <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>44.63956</v>
+        <v>44.73856</v>
       </c>
       <c r="W45" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.32056</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -4214,21 +4210,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4237,7 +4233,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4259,7 +4255,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4270,23 +4266,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U46" t="n">
         <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W46" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -4296,30 +4292,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4341,7 +4337,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4352,23 +4348,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U47" t="n">
         <v>48</v>
       </c>
       <c r="V47" t="n">
-        <v>44.73856</v>
+        <v>46.29559</v>
       </c>
       <c r="W47" t="n">
-        <v>-76.32056</v>
+        <v>-83.20277</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -4460,30 +4456,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4505,7 +4501,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -4525,14 +4521,14 @@
         <v>48</v>
       </c>
       <c r="V49" t="n">
-        <v>44.62168</v>
+        <v>44.47438</v>
       </c>
       <c r="W49" t="n">
-        <v>-76.56963</v>
+        <v>-76.51861</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -4542,42 +4538,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Quebec Mine - Main Shaft</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41N13SW00003</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Quebec Harbour</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2.3</v>
+        <v>11.1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
         <v>1</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4587,7 +4583,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>in 1955 was 0.11% Cu over 5 ft. Grades of mineralization reportedly exceeded 2.5% Cu over 3 to 6 feet underground.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4596,25 +4592,29 @@
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U50" t="n">
         <v>48</v>
       </c>
       <c r="V50" t="n">
-        <v>44.47438</v>
+        <v>47.76464</v>
       </c>
       <c r="W50" t="n">
-        <v>-76.51861</v>
+        <v>-85.91225</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00003</t>
         </is>
       </c>
     </row>
@@ -4624,30 +4624,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Holdsworth Prospect</t>
+          <t>Rock Lake</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MDI42C02SE00011</t>
+          <t>MDI41J05NE00002</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Ophir</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4669,7 +4669,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>68 drill hole(s) nearby · 1918–1989 · Soocana Mining, Algoma Steel Corp Ltd · tested Gold, Zinc</t>
+          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -4680,23 +4680,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U51" t="n">
         <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>48.10921</v>
+        <v>46.44114</v>
       </c>
       <c r="W51" t="n">
-        <v>-84.58408</v>
+        <v>-83.73430999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
         </is>
       </c>
     </row>
@@ -4706,35 +4706,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Victoria Mine</t>
+          <t>Holdsworth Prospect</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MDI41K09NE00019</t>
+          <t>MDI42C02SE00011</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>French Bay</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4751,7 +4751,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>1 Zone 1957 Unclassified 145150 160,000 tons averaging 5.28% combined lead and zinc and 1.73 ounces of silver per ton.</t>
+          <t>68 drill hole(s) nearby · 1918–1989 · Soocana Mining, Algoma Steel Corp Ltd · tested Gold, Zinc</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4771,14 +4771,14 @@
         <v>48</v>
       </c>
       <c r="V52" t="n">
-        <v>46.63596</v>
+        <v>48.10921</v>
       </c>
       <c r="W52" t="n">
-        <v>-84.1369</v>
+        <v>-84.58408</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00011</t>
         </is>
       </c>
     </row>
@@ -4788,39 +4788,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rock Lake</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MDI41J05NE00002</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ophir</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -4833,7 +4833,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4844,23 +4844,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V53" t="n">
-        <v>46.44114</v>
+        <v>45.58868</v>
       </c>
       <c r="W53" t="n">
-        <v>-83.73430999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -4870,52 +4870,56 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quebec Mine - Main Shaft</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MDI41N13SW00003</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Quebec Harbour</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I54" t="b">
         <v>0</v>
       </c>
       <c r="J54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Mo 2.00%</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>in 1955 was 0.11% Cu over 5 ft. Grades of mineralization reportedly exceeded 2.5% Cu over 3 to 6 feet underground.</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Nortoba Mines, B C Lamble · tested Gold</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4924,29 +4928,25 @@
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U54" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="V54" t="n">
-        <v>47.76464</v>
+        <v>49.69198</v>
       </c>
       <c r="W54" t="n">
-        <v>-85.91225</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>
@@ -4956,35 +4956,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jardun Mine - No 3 Zone</t>
+          <t>Shoot Zone Deposit</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MDI41K09NE00090</t>
+          <t>MDI42A10SE00065</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Northland</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver, Zinc, Gold</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -5001,7 +5001,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>137 drill hole(s) nearby · 1951–1984 · Longbow Exploration Inc/Watson Lake Mines Ltd, Jardun Mines Ltd · tested Copper, Lead, Silver, Zinc, Gold</t>
+          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5012,23 +5012,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T55" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="V55" t="n">
-        <v>46.63751</v>
+        <v>48.56426</v>
       </c>
       <c r="W55" t="n">
-        <v>-84.14293000000001</v>
+        <v>-80.63866</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
         </is>
       </c>
     </row>
@@ -5038,30 +5038,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Scramble Mine</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52E16SW00091</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Pelletier Bridge</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="I56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -5083,7 +5083,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -5094,23 +5094,23 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U56" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="V56" t="n">
-        <v>45.58868</v>
+        <v>49.78399</v>
       </c>
       <c r="W56" t="n">
-        <v>-79.70944</v>
+        <v>-94.37701</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
         </is>
       </c>
     </row>
@@ -5120,35 +5120,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Springer-Lavergne Rare Earth Project</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDI31C12SE00039</t>
+          <t>MDI31L05NW00002</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Crystal Falls</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.3</v>
+        <v>5.1</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -5165,7 +5165,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>15 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5176,23 +5176,23 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="V57" t="n">
-        <v>44.51231</v>
+        <v>46.44231</v>
       </c>
       <c r="W57" t="n">
-        <v>-77.62011</v>
+        <v>-79.94853999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
         </is>
       </c>
     </row>
@@ -5202,42 +5202,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Abbican</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI41J06NE00044</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8</v>
+        <v>10.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I58" t="b">
         <v>0</v>
       </c>
       <c r="J58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5256,25 +5256,29 @@
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U58" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>44.5143</v>
+        <v>46.47973</v>
       </c>
       <c r="W58" t="n">
-        <v>-77.61444</v>
+        <v>-83.15055</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
         </is>
       </c>
     </row>
@@ -5284,35 +5288,35 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Simon Copper Property</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31F03NW00044</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Slate Falls</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Zinc, Iron, Selenium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I59" t="b">
@@ -5329,7 +5333,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>49 drill hole(s) nearby · 1956–2008 · Malcolm Property, Noranda Exploration Co Ltd · tested Copper, Zinc, Gold, Nickel</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5340,23 +5344,23 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U59" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="V59" t="n">
-        <v>49.71016</v>
+        <v>45.20807</v>
       </c>
       <c r="W59" t="n">
-        <v>-94.40097</v>
+        <v>-77.31331</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
         </is>
       </c>
     </row>
@@ -5366,30 +5370,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>Band-Ore Mattagami Zone 4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI52B09SE00024</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Shebandowan</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5408,14 +5412,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Mo 2.00%</t>
-        </is>
-      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Nortoba Mines, B C Lamble · tested Gold</t>
+          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5432,17 +5432,17 @@
         <v>25</v>
       </c>
       <c r="U60" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="V60" t="n">
-        <v>49.69198</v>
+        <v>48.62462</v>
       </c>
       <c r="W60" t="n">
-        <v>-88.04716999999999</v>
+        <v>-90.12229000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
         </is>
       </c>
     </row>
@@ -5452,30 +5452,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Band-Ore Mattagami Zone 4</t>
+          <t>Lakemount Property</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MDI52B09SE00024</t>
+          <t>MDI42C02SE00090</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Shebandowan</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5497,7 +5497,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
+          <t>98 drill hole(s) nearby · 1952–1982 · Kelore Mines Ltd, New Kelore Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5517,14 +5517,14 @@
         <v>32</v>
       </c>
       <c r="V61" t="n">
-        <v>48.62462</v>
+        <v>48.06318</v>
       </c>
       <c r="W61" t="n">
-        <v>-90.12229000000001</v>
+        <v>-84.62636999999999</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
         </is>
       </c>
     </row>
@@ -5534,21 +5534,21 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Abbican</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MDI41J06NE00044</t>
+          <t>MDI42A09SW00163</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Holtyre</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10.3</v>
+        <v>4.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5569,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
+          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5588,11 +5588,7 @@
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="n">
         <v>1</v>
       </c>
@@ -5603,14 +5599,14 @@
         <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>46.47973</v>
+        <v>48.50619</v>
       </c>
       <c r="W62" t="n">
-        <v>-83.15055</v>
+        <v>-80.31543000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
         </is>
       </c>
     </row>
@@ -5620,30 +5616,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scramble Mine</t>
+          <t>Macassa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MDI52E16SW00091</t>
+          <t>MDI31C13SE00099</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Pelletier Bridge</t>
+          <t>Ormsby</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5665,7 +5661,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -5676,23 +5672,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T63" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U63" t="n">
         <v>32</v>
       </c>
       <c r="V63" t="n">
-        <v>49.78399</v>
+        <v>44.868</v>
       </c>
       <c r="W63" t="n">
-        <v>-94.37701</v>
+        <v>-77.72254</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
         </is>
       </c>
     </row>
@@ -5702,21 +5698,21 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lakemount Property</t>
+          <t>Hermina</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MDI42C02SE00090</t>
+          <t>MDI41J01NE00007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5725,7 +5721,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5747,7 +5743,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>98 drill hole(s) nearby · 1952–1982 · Kelore Mines Ltd, New Kelore Mines Ltd · tested Copper, Nickel</t>
+          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5758,23 +5754,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U64" t="n">
         <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>48.06318</v>
+        <v>46.23918</v>
       </c>
       <c r="W64" t="n">
-        <v>-84.62636999999999</v>
+        <v>-82.15586</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
         </is>
       </c>
     </row>
@@ -5784,30 +5780,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Bannockburn Gold Project</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MDI42A09SW00163</t>
+          <t>MDI31C12NE00195</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Holtyre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5829,7 +5825,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons Ltd · tested Gold</t>
+          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5840,23 +5836,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T65" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="U65" t="n">
         <v>32</v>
       </c>
       <c r="V65" t="n">
-        <v>48.50619</v>
+        <v>44.64988</v>
       </c>
       <c r="W65" t="n">
-        <v>-80.31543000000001</v>
+        <v>-77.54698</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
         </is>
       </c>
     </row>
@@ -5866,30 +5862,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Springer-Lavergne Rare Earth Project</t>
+          <t>Empire B Zone</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MDI31L05NW00002</t>
+          <t>MDI31D16NE00146</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Crystal Falls</t>
+          <t>South Wilberforce</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
+          <t>Uranium, Yttrium, Fluorite, Thorium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5911,7 +5907,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5931,14 +5927,14 @@
         <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>46.44231</v>
+        <v>44.99427</v>
       </c>
       <c r="W66" t="n">
-        <v>-79.94853999999999</v>
+        <v>-78.19589999999999</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
         </is>
       </c>
     </row>
@@ -5948,30 +5944,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Simon Copper Property</t>
+          <t>Reserve Creek Occurrences</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MDI31F03NW00044</t>
+          <t>MDI42M12SE00008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Slate Falls</t>
+          <t>Eabametoong First Nation</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Iron, Selenium</t>
+          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5990,10 +5986,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Mo 0.45%</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>49 drill hole(s) nearby · 1956–2008 · Malcolm Property, Noranda Exploration Co Ltd · tested Copper, Zinc, Gold, Nickel</t>
+          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Goldpost Resources Inc · tested Gold</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -6010,17 +6010,17 @@
         <v>25</v>
       </c>
       <c r="U67" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="V67" t="n">
-        <v>45.20807</v>
+        <v>51.57743</v>
       </c>
       <c r="W67" t="n">
-        <v>-77.31331</v>
+        <v>-87.73681999999999</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
         </is>
       </c>
     </row>
@@ -6030,21 +6030,21 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Macassa</t>
+          <t>Eagle Copper Mine</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MDI31C13SE00099</t>
+          <t>MDI41K16SW00002</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ormsby</t>
+          <t>Bourdages Corner</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
+          <t>Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6072,10 +6072,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Cu 1.15%</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -6086,23 +6090,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U68" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="V68" t="n">
-        <v>44.868</v>
+        <v>46.75901</v>
       </c>
       <c r="W68" t="n">
-        <v>-77.72254</v>
+        <v>-84.26090000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
         </is>
       </c>
     </row>
@@ -6112,30 +6116,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hermina</t>
+          <t>Northern Kyanite</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDI41J01NE00007</t>
+          <t>MDI41I10SE00004</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Wahnapitae</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6157,7 +6161,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
+          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -6168,23 +6172,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U69" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V69" t="n">
-        <v>46.23918</v>
+        <v>46.50103</v>
       </c>
       <c r="W69" t="n">
-        <v>-82.15586</v>
+        <v>-80.73585</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
         </is>
       </c>
     </row>
@@ -6194,30 +6198,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shoot Zone Deposit</t>
+          <t>Stanleyville Vermiculite</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MDI42A10SE00065</t>
+          <t>MDI31C16SW00030</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Vermiculite</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6239,7 +6243,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
+          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -6250,23 +6254,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="U70" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V70" t="n">
-        <v>48.56426</v>
+        <v>44.79726</v>
       </c>
       <c r="W70" t="n">
-        <v>-80.63866</v>
+        <v>-76.32017999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
         </is>
       </c>
     </row>
@@ -6276,30 +6280,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Empire B Zone</t>
+          <t>95-2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MDI31D16NE00146</t>
+          <t>MDI31M12SW00017</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>South Wilberforce</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Uranium, Yttrium, Fluorite, Thorium</t>
+          <t>Diamond, Kimberlite</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6321,7 +6325,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
+          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -6338,17 +6342,17 @@
         <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V71" t="n">
-        <v>44.99427</v>
+        <v>47.52342</v>
       </c>
       <c r="W71" t="n">
-        <v>-78.19589999999999</v>
+        <v>-79.89148</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
         </is>
       </c>
     </row>
@@ -6358,30 +6362,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bannockburn Gold Project</t>
+          <t>Rutter Nepheline</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MDI31C12NE00195</t>
+          <t>MDI41I02SE00005</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Rutter</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
+          <t>Nepheline Syenite</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6403,7 +6407,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
+          <t>3 drill hole(s) nearby · 1982 · Steep Rock Iron Mines Ltd</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -6414,23 +6418,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T72" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="U72" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V72" t="n">
-        <v>44.64988</v>
+        <v>46.09664</v>
       </c>
       <c r="W72" t="n">
-        <v>-77.54698</v>
+        <v>-80.67718000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I02SE00005</t>
         </is>
       </c>
     </row>
@@ -6440,30 +6444,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reserve Creek Occurrences</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MDI42M12SE00008</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Eabametoong First Nation</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>1.6</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6475,21 +6479,17 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Mo 0.45%</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Goldpost Resources Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -6498,25 +6498,29 @@
       </c>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T73" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V73" t="n">
-        <v>51.57743</v>
+        <v>45.09484</v>
       </c>
       <c r="W73" t="n">
-        <v>-87.73681999999999</v>
+        <v>-77.76734999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
         </is>
       </c>
     </row>
@@ -6526,21 +6530,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Eagle Copper Mine</t>
+          <t>West Graham</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MDI41K16SW00002</t>
+          <t>MDI41I06NW00072</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bourdages Corner</t>
+          <t>Crean Hill</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6549,7 +6553,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver</t>
+          <t>Copper, Nickel, Cobalt, Gold, Palladium, Platinum, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6570,12 +6574,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Cu 1.15%</t>
+          <t>Ni 0.30%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
+          <t>6 drill hole(s) nearby · 1960–1961 · Mcvittie-Graham Mining Co Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6592,595 +6596,17 @@
         <v>25</v>
       </c>
       <c r="U74" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="V74" t="n">
-        <v>46.75901</v>
+        <v>46.43504</v>
       </c>
       <c r="W74" t="n">
-        <v>-84.26090000000001</v>
+        <v>-81.30689</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Shawmere Anorthosite</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>MDI42B02NW00001</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Foleyet</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Aluminum, Feldspar (Nonmetals), Silica</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I75" t="b">
-        <v>0</v>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>11 drill hole(s) nearby · 1994 · Purchem Ltd</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="n">
-        <v>1</v>
-      </c>
-      <c r="T75" t="n">
-        <v>25</v>
-      </c>
-      <c r="U75" t="n">
-        <v>27</v>
-      </c>
-      <c r="V75" t="n">
-        <v>48.13236</v>
-      </c>
-      <c r="W75" t="n">
-        <v>-82.78859</v>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42B02NW00001</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>95-2</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>MDI31M12SW00017</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Hudson</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Diamond, Kimberlite</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>25</v>
-      </c>
-      <c r="U76" t="n">
-        <v>27</v>
-      </c>
-      <c r="V76" t="n">
-        <v>47.52342</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-79.89148</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Stanleyville Vermiculite</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>MDI31C16SW00030</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Stanleyville</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Vermiculite</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>5</v>
-      </c>
-      <c r="T77" t="n">
-        <v>125</v>
-      </c>
-      <c r="U77" t="n">
-        <v>27</v>
-      </c>
-      <c r="V77" t="n">
-        <v>44.79726</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-76.32017999999999</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Rutter Nepheline</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>MDI41I02SE00005</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Rutter</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Nepheline Syenite</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>3 drill hole(s) nearby · 1982 · Steep Rock Iron Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>3</v>
-      </c>
-      <c r="T78" t="n">
-        <v>75</v>
-      </c>
-      <c r="U78" t="n">
-        <v>27</v>
-      </c>
-      <c r="V78" t="n">
-        <v>46.09664</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-80.67718000000001</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I02SE00005</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Kyle Lake No. 1</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>MDI43C06NW00002</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Ogoki</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Diamond, Kimberlite</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I79" t="b">
-        <v>0</v>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1995 · Kwg Resc Inc</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="n">
-        <v>1</v>
-      </c>
-      <c r="T79" t="n">
-        <v>25</v>
-      </c>
-      <c r="U79" t="n">
-        <v>27</v>
-      </c>
-      <c r="V79" t="n">
-        <v>52.46062</v>
-      </c>
-      <c r="W79" t="n">
-        <v>-85.40002</v>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI43C06NW00002</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Jayfran-Pipawa</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MDI31F04SE00036</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Vardy</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Nepheline Syenite, Uranium</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I80" t="b">
-        <v>0</v>
-      </c>
-      <c r="J80" t="b">
-        <v>1</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
-      <c r="S80" t="n">
-        <v>6</v>
-      </c>
-      <c r="T80" t="n">
-        <v>150</v>
-      </c>
-      <c r="U80" t="n">
-        <v>27</v>
-      </c>
-      <c r="V80" t="n">
-        <v>45.09484</v>
-      </c>
-      <c r="W80" t="n">
-        <v>-77.76734999999999</v>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Northern Kyanite</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>MDI41I10SE00004</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Wahnapitae</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I81" t="b">
-        <v>0</v>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="n">
-        <v>3</v>
-      </c>
-      <c r="T81" t="n">
-        <v>75</v>
-      </c>
-      <c r="U81" t="n">
-        <v>27</v>
-      </c>
-      <c r="V81" t="n">
-        <v>46.50103</v>
-      </c>
-      <c r="W81" t="n">
-        <v>-80.73585</v>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00072</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -656,21 +656,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,14 +698,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Mo 5.00%</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -722,17 +718,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
-        <v>45.39062</v>
+        <v>45.30338</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.70397</v>
+        <v>-76.90682</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -742,30 +738,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -784,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -802,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>45.29002</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-76.94167</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -828,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -893,14 +885,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.28947</v>
+        <v>44.85917</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -910,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.30338</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.90682</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -992,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1057,14 +1049,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.29002</v>
+        <v>45.21442</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.94167</v>
+        <v>-77.8742</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.85917</v>
+        <v>44.49976</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.15956</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1148,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55104</v>
+        <v>44.5021</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.61301</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V10" t="n">
-        <v>48.24876</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-89.86754000000001</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>45.21442</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.8742</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1402,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Windy Hill</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI41P09SE00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Cane</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Cobalt, Silver, Uranium, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1434,7 +1426,7 @@
         </is>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1444,10 +1436,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ni 0.07%, Co 0.72%, U 34.98%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Silver Economic Ore 2 Niccolite Economic Ore 1 Chalcopyrite Economic Gangue 2 Pitchblende Economic Gangue 3 Argentite Economic Gangue 6 Smaltite Economic Gangue Mineralization Comments Jun 24, 2024 (Nazha Sabiri) - Selected grab samples from pitchblende assayed as high as 34.98% uranium as U3O8 (MDC09). Sample (CAN05) taken from a dibase waste rock, in a historical trench, assayed 7240 ppm cobalt and 737 ppm nickel (File 2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="V12" t="n">
-        <v>44.72488</v>
+        <v>47.60521</v>
       </c>
       <c r="W12" t="n">
-        <v>-78.80319</v>
+        <v>-80.03053</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09SE00007</t>
         </is>
       </c>
     </row>
@@ -1484,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1516,7 +1512,7 @@
         </is>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1528,12 +1524,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Mo 1.00%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1544,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U13" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="V13" t="n">
-        <v>44.99932</v>
+        <v>46.28991</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.32907</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -1570,30 +1566,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31C10NW00016</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1602,7 +1598,7 @@
         </is>
       </c>
       <c r="I14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1612,10 +1608,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Zn 11.60%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>42 drill hole(s) nearby · 1950–1975 · Cons Rochette Mines Ltd, W H Douglas</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>175</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5143</v>
+        <v>44.6895</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61444</v>
+        <v>-76.77161</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
         </is>
       </c>
     </row>
@@ -1652,30 +1652,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ethel Copper Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41P09NW00014</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Elk Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1697,7 +1697,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V15" t="n">
-        <v>44.5021</v>
+        <v>47.7491</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61301</v>
+        <v>-80.27547</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
         </is>
       </c>
     </row>
@@ -1734,30 +1734,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Pater Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J02NE00002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Spragge</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1779,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1796,17 +1796,17 @@
         <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>46.20698</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-82.6491</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
         </is>
       </c>
     </row>
@@ -1816,21 +1816,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kristina</t>
+          <t>McCoy Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41K16NE00002</t>
+          <t>MDI31F03NW00055</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wabos</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1858,14 +1858,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Cu 6.21%</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>An average grade might be 2.7% copper.</t>
+          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1882,17 +1878,17 @@
         <v>25</v>
       </c>
       <c r="U17" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="V17" t="n">
-        <v>46.88544</v>
+        <v>45.20254</v>
       </c>
       <c r="W17" t="n">
-        <v>-84.09032000000001</v>
+        <v>-77.38281000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
         </is>
       </c>
     </row>
@@ -1902,35 +1898,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Temagami Copper Mine</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41I16NE00004</t>
+          <t>MDI31C11SW00028</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Adanac</t>
+          <t>Queensborough</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1944,14 +1940,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
+          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1962,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
+        <v>200</v>
+      </c>
+      <c r="U18" t="n">
         <v>50</v>
       </c>
-      <c r="U18" t="n">
-        <v>54</v>
-      </c>
       <c r="V18" t="n">
-        <v>46.96233</v>
+        <v>44.58796</v>
       </c>
       <c r="W18" t="n">
-        <v>-80.03716</v>
+        <v>-77.43434000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
         </is>
       </c>
     </row>
@@ -1988,35 +1980,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sand River Gold Mine</t>
+          <t>Rabbit Mountain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52H09SE00005</t>
+          <t>MDI52A05SE00008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Harstone</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold, Silver, Tungsten</t>
+          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2030,14 +2022,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>W 0.23%</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1987–1988 · Cryderman Gold Inc · tested Gold</t>
+          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2048,23 +2036,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
+        <v>25</v>
+      </c>
+      <c r="U19" t="n">
         <v>50</v>
       </c>
-      <c r="U19" t="n">
-        <v>52</v>
-      </c>
       <c r="V19" t="n">
-        <v>49.62195</v>
+        <v>48.30674</v>
       </c>
       <c r="W19" t="n">
-        <v>-88.04667000000001</v>
+        <v>-89.60534</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
         </is>
       </c>
     </row>
@@ -2074,35 +2062,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Beaver</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C12SE00033</t>
+          <t>MDI52A05SE00009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2119,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
+          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, D B Mcwilliams · tested Silver, Zinc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2130,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
         <v>50</v>
       </c>
       <c r="V20" t="n">
-        <v>44.50806</v>
+        <v>48.31944</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.61564</v>
+        <v>-89.63952999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
         </is>
       </c>
     </row>
@@ -2156,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rabbit Mountain</t>
+          <t>Ore Chimney</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI52A05SE00008</t>
+          <t>MDI31C14SE00142</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Harstone</t>
+          <t>Bishop Corners</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
+          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2201,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
+          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2212,23 +2200,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="U21" t="n">
         <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>48.30674</v>
+        <v>44.77617</v>
       </c>
       <c r="W21" t="n">
-        <v>-89.60534</v>
+        <v>-77.15194</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
         </is>
       </c>
     </row>
@@ -2238,35 +2226,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Beaver</t>
+          <t>Black Lake Occurrence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI52A05SE00009</t>
+          <t>MDI41J01NW00026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2283,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, Honey Badger Exploration Inc · tested Silver, Zinc</t>
+          <t>13 drill hole(s) nearby · 1956–1966 · Sam Linton (Unknown), Gradore Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2294,23 +2282,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U22" t="n">
         <v>50</v>
       </c>
       <c r="V22" t="n">
-        <v>48.31944</v>
+        <v>46.24374</v>
       </c>
       <c r="W22" t="n">
-        <v>-89.63952999999999</v>
+        <v>-82.39867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
         </is>
       </c>
     </row>
@@ -2320,30 +2308,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Office Shaft</t>
+          <t>Ogema</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI41N13SW00013</t>
+          <t>MDI52A15SE00006</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quebec Harbour</t>
+          <t>Dorion</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>6.2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead, Zinc, Amethyst, Barite, Copper, Fluorite, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2355,7 +2343,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2365,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9 drill hole(s) nearby · 1942–1955 · M J O'Brien Ltd(Burrage Copper)Jones, The American Metal Co Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1961 · Sogemines Dev Co Ltd · tested Zinc</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2374,29 +2362,25 @@
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U23" t="n">
         <v>50</v>
       </c>
       <c r="V23" t="n">
-        <v>47.76366</v>
+        <v>48.76995</v>
       </c>
       <c r="W23" t="n">
-        <v>-85.91361000000001</v>
+        <v>-88.73446</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A15SE00006</t>
         </is>
       </c>
     </row>
@@ -2406,35 +2390,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pater Mine</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI41J02NE00002</t>
+          <t>MDI31C12SE00033</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Spragge</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2451,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2462,23 +2446,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U24" t="n">
         <v>50</v>
       </c>
       <c r="V24" t="n">
-        <v>46.20698</v>
+        <v>44.50806</v>
       </c>
       <c r="W24" t="n">
-        <v>-82.6491</v>
+        <v>-77.61564</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
         </is>
       </c>
     </row>
@@ -2488,30 +2472,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Contact Bay</t>
+          <t>Climax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI000000000779</t>
+          <t>MDI52A05SE00016</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2533,7 +2517,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
+          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2544,23 +2528,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
         <v>50</v>
       </c>
       <c r="V25" t="n">
-        <v>49.69695</v>
+        <v>48.31312</v>
       </c>
       <c r="W25" t="n">
-        <v>-92.82165999999999</v>
+        <v>-89.66484</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
         </is>
       </c>
     </row>
@@ -2570,30 +2554,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Crystal-Comstock Property</t>
+          <t>Hermenia Mine, No. 3 Shaft</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MDI41I15SE00006</t>
+          <t>MDI41J01NE00022</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cryderman Subdivision</t>
+          <t>Walford</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12.9</v>
+        <v>6.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2615,7 +2599,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
+          <t>40 drill hole(s) nearby · 1951–2005 · East Sullivan Mines Ltd, Mcvittie, Jerome&amp;Doyon/ East Sullivan Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2635,14 +2619,14 @@
         <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>46.75321</v>
+        <v>46.24928</v>
       </c>
       <c r="W26" t="n">
-        <v>-80.62255</v>
+        <v>-82.17301999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00022</t>
         </is>
       </c>
     </row>
@@ -2652,35 +2636,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quirke No. 1</t>
+          <t>Vermor Gold Mine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MDI41J10SE00007</t>
+          <t>MDI52K01SW00004</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Uranium, Rare Earth Elements, Thorium</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2697,7 +2681,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2708,23 +2692,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U27" t="n">
         <v>50</v>
       </c>
       <c r="V27" t="n">
-        <v>46.51253</v>
+        <v>50.01111</v>
       </c>
       <c r="W27" t="n">
-        <v>-82.64662</v>
+        <v>-92.26211000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
         </is>
       </c>
     </row>
@@ -2734,35 +2718,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Massey Mine No. 4 Shaft</t>
+          <t>Nordic Mine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDI41J01NE00023</t>
+          <t>MDI41J07NE00009</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium, Thorium, Yttrium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -2779,7 +2763,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2790,23 +2774,23 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U28" t="n">
         <v>50</v>
       </c>
       <c r="V28" t="n">
-        <v>46.2376</v>
+        <v>46.37802</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.12882</v>
+        <v>-82.58893</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
         </is>
       </c>
     </row>
@@ -2816,21 +2800,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McCoy Property</t>
+          <t>Reuben McKee Property</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDI31F03NW00055</t>
+          <t>MDI41J11SW00058</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Dunns Valley</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1.4</v>
+        <v>16.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2839,7 +2823,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2861,7 +2845,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
+          <t>Two samples taken from the Resident Geologist Staff in 2012 each returned assays of 1.4% Cu.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2881,14 +2865,14 @@
         <v>50</v>
       </c>
       <c r="V29" t="n">
-        <v>45.20254</v>
+        <v>46.56806</v>
       </c>
       <c r="W29" t="n">
-        <v>-77.38281000000001</v>
+        <v>-83.46539</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J11SW00058</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2882,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Buckles Mine</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDI41J07NE00004</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2916,17 +2900,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -2943,7 +2927,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, Rio Canadian Expl Ltd/Knight-Adair</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2954,23 +2938,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T30" t="n">
-        <v>25</v>
+        <v>275</v>
       </c>
       <c r="U30" t="n">
         <v>50</v>
       </c>
       <c r="V30" t="n">
-        <v>46.37605</v>
+        <v>44.72488</v>
       </c>
       <c r="W30" t="n">
-        <v>-82.58892</v>
+        <v>-78.80319</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -2980,35 +2964,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nordic Mine</t>
+          <t>Massey Mine No. 4 Shaft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDI41J07NE00009</t>
+          <t>MDI41J01NE00023</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Yttrium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -3025,7 +3009,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd, Geneva Lake Mines Ltd</t>
+          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3036,23 +3020,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U31" t="n">
         <v>50</v>
       </c>
       <c r="V31" t="n">
-        <v>46.37802</v>
+        <v>46.2376</v>
       </c>
       <c r="W31" t="n">
-        <v>-82.58893</v>
+        <v>-82.12882</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
         </is>
       </c>
     </row>
@@ -3062,35 +3046,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Net Lake Occurrence</t>
+          <t>Quirke No. 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDI31M04SW00099</t>
+          <t>MDI41J10SE00007</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Temagami North</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>16</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bismuth, Copper, Molybdenum, Nickel, Silver, Gold</t>
+          <t>Uranium, Rare Earth Elements, Thorium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -3107,7 +3091,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>A grab sample of breccia collected by Myteque Mines assayed 1.35% Cu, 0.54% MoS2 and 0.34 oz/t Ag with a trace of gold. Hazelton assayed 2.45% Mo. Ciglen in 1956 returned best assays of 014% Ni, 0.23% Cu over 11 ft, and 0.47% Cu, 0.21% Pb and 0.03% Zn over 10.5 feet. An assay from an unspecified location and assayed by the Mines Branch, Ottawa returned 4.67% Mi, 0.10% Cu and 0.002 oz/t Au.</t>
+          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3118,23 +3102,23 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U32" t="n">
         <v>50</v>
       </c>
       <c r="V32" t="n">
-        <v>47.11985</v>
+        <v>46.51253</v>
       </c>
       <c r="W32" t="n">
-        <v>-79.78539000000001</v>
+        <v>-82.64662</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SW00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
         </is>
       </c>
     </row>
@@ -3144,35 +3128,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ogistoh Mine</t>
+          <t>Buckles Mine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MDI31M04SE00026</t>
+          <t>MDI41J07NE00004</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Buffalo Rock</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13.3</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cobalt, Copper, Gold, Nickel, Silver</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -3189,7 +3173,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Beland (1913) reported that an assay of 92 oz/t Ag over 6 feet was obtained at one place in the shaft. Miron in 1991 assayed 0.002 oz/t Au and a grab sample collected from the old dump site assayed 0.425% Cu, 0.794% Ni and 0.028 oz/t Au. A grab sample collected by the OGS from a sulphide rich zone within the gabbro/diorite assayed 0.46% Cu and 0.89% Ni. Ruttan assayed 0.64% Cu.</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3200,23 +3184,23 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="U33" t="n">
         <v>50</v>
       </c>
       <c r="V33" t="n">
-        <v>47.05917</v>
+        <v>46.37605</v>
       </c>
       <c r="W33" t="n">
-        <v>-79.52840999999999</v>
+        <v>-82.58892</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M04SE00026</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
         </is>
       </c>
     </row>
@@ -3226,30 +3210,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Contact Bay</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI000000000779</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3271,7 +3255,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3282,23 +3266,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U34" t="n">
         <v>50</v>
       </c>
       <c r="V34" t="n">
-        <v>46.23809</v>
+        <v>49.69695</v>
       </c>
       <c r="W34" t="n">
-        <v>-82.11991</v>
+        <v>-92.82165999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
         </is>
       </c>
     </row>
@@ -3308,30 +3292,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ogema</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDI52A15SE00006</t>
+          <t>MDI52A10NE00008</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dorion</t>
+          <t>Pearl</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Amethyst, Barite, Copper, Fluorite, Silver</t>
+          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3353,7 +3337,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1961 · Sogemines Dev Co Ltd · tested Zinc</t>
+          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3364,23 +3348,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T35" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U35" t="n">
         <v>50</v>
       </c>
       <c r="V35" t="n">
-        <v>48.76995</v>
+        <v>48.67856</v>
       </c>
       <c r="W35" t="n">
-        <v>-88.73446</v>
+        <v>-88.62576</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A15SE00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
         </is>
       </c>
     </row>
@@ -3390,30 +3374,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Worthington Mine</t>
+          <t>Crystal-Comstock Property</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDI41I06NW00005</t>
+          <t>MDI41I15SE00006</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Worthington</t>
+          <t>Cryderman Subdivision</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.4</v>
+        <v>12.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3435,7 +3419,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>A sample taken from the Worthington Shaft by Wallbridge Mining Company assayed 0.219% Cu, and 0.0388% Ni. Shipments averaged 8% Ni;</t>
+          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3455,14 +3439,14 @@
         <v>50</v>
       </c>
       <c r="V36" t="n">
-        <v>46.38402</v>
+        <v>46.75321</v>
       </c>
       <c r="W36" t="n">
-        <v>-81.44789</v>
+        <v>-80.62255</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
         </is>
       </c>
     </row>
@@ -3472,30 +3456,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vermor Gold Mine</t>
+          <t>Kell Claims</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDI52K01SW00004</t>
+          <t>MDI41P10SE00002</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Gowganda</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10.9</v>
+        <v>18.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3517,7 +3501,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19 drill hole(s) nearby · 1951–1989 · Denree Cons Mines Ltd, D E Smith</t>
+          <t>A bulk sample of 253 pounds assayed 1703.8 oz/t Ag and yielded 180 lbs Co. A drill hole completed by Ourgold Mining Company returned 1.11% Cu, 0.56 oz/t Ag and 0.07% Co over 15 feet; 5.3% Cu, 1.2 oz/t Ag and 0.9% Co over 11.8 feet; and 25 feet averaging 2.23% Cu and 1.18 oz/t Ag.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3528,23 +3512,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U37" t="n">
         <v>50</v>
       </c>
       <c r="V37" t="n">
-        <v>50.01111</v>
+        <v>47.50538</v>
       </c>
       <c r="W37" t="n">
-        <v>-92.26211000000001</v>
+        <v>-80.64733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P10SE00002</t>
         </is>
       </c>
     </row>
@@ -3554,35 +3538,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ethel Copper Property</t>
+          <t>Silver Mountain West</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDI41P09NW00014</t>
+          <t>MDI52A04NW00003</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Elk Lake</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -3599,7 +3583,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3610,23 +3594,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="U38" t="n">
         <v>50</v>
       </c>
       <c r="V38" t="n">
-        <v>47.7491</v>
+        <v>48.24757</v>
       </c>
       <c r="W38" t="n">
-        <v>-80.27547</v>
+        <v>-89.8866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
         </is>
       </c>
     </row>
@@ -3636,30 +3620,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Climax</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MDI52A05SE00016</t>
+          <t>MDI41I04NE00004</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>McGregor Bay</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3.1</v>
+        <v>7.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3671,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3681,7 +3665,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
+          <t>2 drill hole(s) nearby · 1979 · Curtin Mines Ltd</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3690,25 +3674,29 @@
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>abuts Killarney Lakelands And Headwaters Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U39" t="n">
         <v>50</v>
       </c>
       <c r="V39" t="n">
-        <v>48.31312</v>
+        <v>46.14902</v>
       </c>
       <c r="W39" t="n">
-        <v>-89.66484</v>
+        <v>-81.62088</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I04NE00004</t>
         </is>
       </c>
     </row>
@@ -3718,39 +3706,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MDI52A10NE00008</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pearl</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -3763,7 +3751,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3774,23 +3762,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V40" t="n">
-        <v>48.67856</v>
+        <v>44.63956</v>
       </c>
       <c r="W40" t="n">
-        <v>-88.62576</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -3800,39 +3788,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Addington Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MDI31C11NE00010</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Flinton Corner</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Tungsten</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -3845,7 +3833,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1983–1984 · C Longmuir/ C. Roger Young, C R Young/ R. C. Longmuir</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3856,23 +3844,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V41" t="n">
-        <v>44.71386</v>
+        <v>46.30402</v>
       </c>
       <c r="W41" t="n">
-        <v>-77.18101</v>
+        <v>-81.53989</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -3882,39 +3870,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MDI31C11SW00028</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Queensborough</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -3927,7 +3915,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3944,17 +3932,17 @@
         <v>200</v>
       </c>
       <c r="U42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V42" t="n">
-        <v>44.58796</v>
+        <v>46.29559</v>
       </c>
       <c r="W42" t="n">
-        <v>-77.43434000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -3964,21 +3952,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3987,7 +3975,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4009,7 +3997,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4020,23 +4008,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U43" t="n">
         <v>48</v>
       </c>
       <c r="V43" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W43" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -4046,30 +4034,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4091,7 +4079,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4111,14 +4099,14 @@
         <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>44.63956</v>
+        <v>44.55883</v>
       </c>
       <c r="W44" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -4128,21 +4116,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4151,7 +4139,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4173,7 +4161,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4184,23 +4172,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W45" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -4210,30 +4198,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4255,7 +4243,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4275,14 +4263,14 @@
         <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>46.30402</v>
+        <v>44.47438</v>
       </c>
       <c r="W46" t="n">
-        <v>-81.53989</v>
+        <v>-76.51861</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -4292,21 +4280,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4315,12 +4303,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I47" t="b">
@@ -4337,7 +4325,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4348,23 +4336,23 @@
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>48</v>
       </c>
       <c r="V47" t="n">
-        <v>46.29559</v>
+        <v>48.69799</v>
       </c>
       <c r="W47" t="n">
-        <v>-83.20277</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -4374,39 +4362,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Rock Lake</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41J05NE00002</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Ophir</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -4419,7 +4407,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4430,23 +4418,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U48" t="n">
         <v>48</v>
       </c>
       <c r="V48" t="n">
-        <v>44.55883</v>
+        <v>46.44114</v>
       </c>
       <c r="W48" t="n">
-        <v>-76.57349000000001</v>
+        <v>-83.73430999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
         </is>
       </c>
     </row>
@@ -4456,42 +4444,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Bridget Lake Occurrence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41N15NW00007</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Michipicoten River</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
         <v>1</v>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4501,7 +4489,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -4510,25 +4498,29 @@
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
+        </is>
+      </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U49" t="n">
         <v>48</v>
       </c>
       <c r="V49" t="n">
-        <v>44.47438</v>
+        <v>47.8998</v>
       </c>
       <c r="W49" t="n">
-        <v>-76.51861</v>
+        <v>-84.85621</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
         </is>
       </c>
     </row>
@@ -4538,42 +4530,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quebec Mine - Main Shaft</t>
+          <t>Tashota-Nipigon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MDI41N13SW00003</t>
+          <t>MDI42L04SE00005</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Quebec Harbour</t>
+          <t>Auden</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11.1</v>
+        <v>29.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Bismuth, Copper, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I50" t="b">
         <v>0</v>
       </c>
       <c r="J50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4583,7 +4575,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>in 1955 was 0.11% Cu over 5 ft. Grades of mineralization reportedly exceeded 2.5% Cu over 3 to 6 feet underground.</t>
+          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4592,29 +4584,25 @@
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>abuts Michipicoten Island Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U50" t="n">
         <v>48</v>
       </c>
       <c r="V50" t="n">
-        <v>47.76464</v>
+        <v>50.04735</v>
       </c>
       <c r="W50" t="n">
-        <v>-85.91225</v>
+        <v>-87.58936</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N13SW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
         </is>
       </c>
     </row>
@@ -4624,30 +4612,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rock Lake</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MDI41J05NE00002</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ophir</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4669,7 +4657,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -4680,23 +4668,23 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T51" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U51" t="n">
         <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>46.44114</v>
+        <v>44.51686</v>
       </c>
       <c r="W51" t="n">
-        <v>-83.73430999999999</v>
+        <v>-77.62098</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -4706,17 +4694,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Holdsworth Prospect</t>
+          <t>McManus Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MDI42C02SE00011</t>
+          <t>MDI41P09NW00043</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -4724,12 +4712,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4748,10 +4736,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Ag 171g/t</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>68 drill hole(s) nearby · 1918–1989 · Soocana Mining, Algoma Steel Corp Ltd · tested Gold, Zinc</t>
+          <t>A 90 pound sample submitted in 1956 assayed: Cu-trace, Ni - 23.4%, Co - 4.45%, Fe - 1.35%, As-37.62%, S-2.52%, Ag-trace.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4762,23 +4754,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U52" t="n">
         <v>48</v>
       </c>
       <c r="V52" t="n">
-        <v>48.10921</v>
+        <v>47.72286</v>
       </c>
       <c r="W52" t="n">
-        <v>-84.58408</v>
+        <v>-80.28064000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
         </is>
       </c>
     </row>
@@ -4870,35 +4862,35 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>Gatling Five Acre</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI31C12SE00028</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7</v>
+        <v>0.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4912,14 +4904,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Mo 2.00%</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Nortoba Mines, B C Lamble · tested Gold</t>
+          <t>11 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4930,23 +4918,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U54" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V54" t="n">
-        <v>49.69198</v>
+        <v>44.51496</v>
       </c>
       <c r="W54" t="n">
-        <v>-88.04716999999999</v>
+        <v>-77.62126000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
         </is>
       </c>
     </row>
@@ -4956,21 +4944,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shoot Zone Deposit</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MDI42A10SE00065</t>
+          <t>MDI31C12SE00039</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4979,12 +4967,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -5001,7 +4989,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
+          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5012,23 +5000,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="V55" t="n">
-        <v>48.56426</v>
+        <v>44.51231</v>
       </c>
       <c r="W55" t="n">
-        <v>-80.63866</v>
+        <v>-77.62011</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
         </is>
       </c>
     </row>
@@ -5038,30 +5026,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scramble Mine</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MDI52E16SW00091</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pelletier Bridge</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5080,10 +5068,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Mo 2.00%</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Nortoba Mines · tested Gold</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -5100,17 +5092,17 @@
         <v>25</v>
       </c>
       <c r="U56" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="V56" t="n">
-        <v>49.78399</v>
+        <v>49.69198</v>
       </c>
       <c r="W56" t="n">
-        <v>-94.37701</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>
@@ -5120,35 +5112,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Springer-Lavergne Rare Earth Project</t>
+          <t>Kam Kotia Mine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDI31L05NW00002</t>
+          <t>MDI42A12SE00005</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Crystal Falls</t>
+          <t>Kamiskotia</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
+          <t>Copper, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -5162,10 +5154,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu 1.10%, Zn 1.17%</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
+          <t>8 drill hole(s) nearby · 1954–1993 · Falconbridge Ltd, Pleno Mines Ltd</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5182,17 +5178,17 @@
         <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="V57" t="n">
-        <v>46.44231</v>
+        <v>48.59125</v>
       </c>
       <c r="W57" t="n">
-        <v>-79.94853999999999</v>
+        <v>-81.60500999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A12SE00005</t>
         </is>
       </c>
     </row>
@@ -5202,21 +5198,21 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abbican</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MDI41J06NE00044</t>
+          <t>MDI42A09SW00163</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Holtyre</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>10.3</v>
+        <v>4.9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5225,7 +5221,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5237,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5247,7 +5243,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
+          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons  · tested Gold</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5256,11 +5252,7 @@
       </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
         <v>1</v>
       </c>
@@ -5271,14 +5263,14 @@
         <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>46.47973</v>
+        <v>48.50619</v>
       </c>
       <c r="W58" t="n">
-        <v>-83.15055</v>
+        <v>-80.31543000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
         </is>
       </c>
     </row>
@@ -5288,30 +5280,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simon Copper Property</t>
+          <t>Springer-Lavergne Rare Earth Project</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDI31F03NW00044</t>
+          <t>MDI31L05NW00002</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Slate Falls</t>
+          <t>Crystal Falls</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Iron, Selenium</t>
+          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5333,7 +5325,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>49 drill hole(s) nearby · 1956–2008 · Malcolm Property, Noranda Exploration Co Ltd · tested Copper, Zinc, Gold, Nickel</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5353,14 +5345,14 @@
         <v>32</v>
       </c>
       <c r="V59" t="n">
-        <v>45.20807</v>
+        <v>46.44231</v>
       </c>
       <c r="W59" t="n">
-        <v>-77.31331</v>
+        <v>-79.94853999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
         </is>
       </c>
     </row>
@@ -5370,30 +5362,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Band-Ore Mattagami Zone 4</t>
+          <t>Lakemount Property</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MDI52B09SE00024</t>
+          <t>MDI42C02SE00090</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Shebandowan</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5415,7 +5407,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
+          <t>98 drill hole(s) nearby · 1952–1982 · Firespur Expl Ltd, Kelore Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5435,14 +5427,14 @@
         <v>32</v>
       </c>
       <c r="V60" t="n">
-        <v>48.62462</v>
+        <v>48.06318</v>
       </c>
       <c r="W60" t="n">
-        <v>-90.12229000000001</v>
+        <v>-84.62636999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
         </is>
       </c>
     </row>
@@ -5452,21 +5444,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lakemount Property</t>
+          <t>Abbican</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MDI42C02SE00090</t>
+          <t>MDI41J06NE00044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5.7</v>
+        <v>10.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5475,7 +5467,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5487,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5497,7 +5489,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>98 drill hole(s) nearby · 1952–1982 · Kelore Mines Ltd, New Kelore Mines Ltd · tested Copper, Nickel</t>
+          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5506,7 +5498,11 @@
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
@@ -5517,14 +5513,14 @@
         <v>32</v>
       </c>
       <c r="V61" t="n">
-        <v>48.06318</v>
+        <v>46.47973</v>
       </c>
       <c r="W61" t="n">
-        <v>-84.62636999999999</v>
+        <v>-83.15055</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
         </is>
       </c>
     </row>
@@ -5534,30 +5530,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Empire B Zone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MDI42A09SW00163</t>
+          <t>MDI31D16NE00146</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Holtyre</t>
+          <t>South Wilberforce</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Uranium, Yttrium, Fluorite, Thorium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5579,7 +5575,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons Ltd · tested Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5599,14 +5595,14 @@
         <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>48.50619</v>
+        <v>44.99427</v>
       </c>
       <c r="W62" t="n">
-        <v>-80.31543000000001</v>
+        <v>-78.19589999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
         </is>
       </c>
     </row>
@@ -5672,10 +5668,10 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T63" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U63" t="n">
         <v>32</v>
@@ -5698,30 +5694,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hermina</t>
+          <t>Band-Ore Mattagami Zone 4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MDI41J01NE00007</t>
+          <t>MDI52B09SE00024</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Shebandowan</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5743,7 +5739,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
+          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5754,23 +5750,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U64" t="n">
         <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>46.23918</v>
+        <v>48.62462</v>
       </c>
       <c r="W64" t="n">
-        <v>-82.15586</v>
+        <v>-90.12229000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
         </is>
       </c>
     </row>
@@ -5862,30 +5858,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Empire B Zone</t>
+          <t>Scramble Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MDI31D16NE00146</t>
+          <t>MDI52E16SW00091</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>South Wilberforce</t>
+          <t>Pelletier Bridge</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Uranium, Yttrium, Fluorite, Thorium</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5907,7 +5903,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
+          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5927,14 +5923,14 @@
         <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>44.99427</v>
+        <v>49.78399</v>
       </c>
       <c r="W66" t="n">
-        <v>-78.19589999999999</v>
+        <v>-94.37701</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
         </is>
       </c>
     </row>
@@ -5944,30 +5940,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Reserve Creek Occurrences</t>
+          <t>Simon Copper Property</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MDI42M12SE00008</t>
+          <t>MDI31F03NW00044</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Eabametoong First Nation</t>
+          <t>Slate Falls</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
+          <t>Copper, Zinc, Iron, Selenium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5986,14 +5982,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Mo 0.45%</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Goldpost Resources Inc · tested Gold</t>
+          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -6010,17 +6002,17 @@
         <v>25</v>
       </c>
       <c r="U67" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V67" t="n">
-        <v>51.57743</v>
+        <v>45.20807</v>
       </c>
       <c r="W67" t="n">
-        <v>-87.73681999999999</v>
+        <v>-77.31331</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
         </is>
       </c>
     </row>
@@ -6030,17 +6022,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eagle Copper Mine</t>
+          <t>Shoot Zone Deposit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MDI41K16SW00002</t>
+          <t>MDI42A10SE00065</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bourdages Corner</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -6048,12 +6040,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6072,14 +6064,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Cu 1.15%</t>
-        </is>
-      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
+          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -6090,23 +6078,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U68" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V68" t="n">
-        <v>46.75901</v>
+        <v>48.56426</v>
       </c>
       <c r="W68" t="n">
-        <v>-84.26090000000001</v>
+        <v>-80.63866</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
         </is>
       </c>
     </row>
@@ -6116,30 +6104,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Northern Kyanite</t>
+          <t>Scadding Gold Property</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDI41I10SE00004</t>
+          <t>MDI41I10NE00012</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Wahnapitae</t>
+          <t>Basin Mines</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
+          <t>Gold, Palladium, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6161,7 +6149,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
+          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -6172,23 +6160,23 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U69" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V69" t="n">
-        <v>46.50103</v>
+        <v>46.65087</v>
       </c>
       <c r="W69" t="n">
-        <v>-80.73585</v>
+        <v>-80.61375</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
         </is>
       </c>
     </row>
@@ -6198,30 +6186,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stanleyville Vermiculite</t>
+          <t>Hermina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MDI31C16SW00030</t>
+          <t>MDI41J01NE00007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Vermiculite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6243,7 +6231,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -6254,23 +6242,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V70" t="n">
-        <v>44.79726</v>
+        <v>46.23918</v>
       </c>
       <c r="W70" t="n">
-        <v>-76.32017999999999</v>
+        <v>-82.15586</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
         </is>
       </c>
     </row>
@@ -6280,30 +6268,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>95-2</t>
+          <t>Methuen Township Ilmenite</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MDI31M12SW00017</t>
+          <t>MDI31C12NW00114</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Oak Lake</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Diamond, Kimberlite</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6325,7 +6313,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
+          <t>62 drill hole(s) nearby · 1969–2008 · Canadian Nickel Co Ltd, M R Tripp</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -6342,17 +6330,17 @@
         <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V71" t="n">
-        <v>47.52342</v>
+        <v>44.62955</v>
       </c>
       <c r="W71" t="n">
-        <v>-79.89148</v>
+        <v>-77.87374</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NW00114</t>
         </is>
       </c>
     </row>
@@ -6362,30 +6350,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rutter Nepheline</t>
+          <t>Geneva Lake Mine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MDI41I02SE00005</t>
+          <t>MDI41I13SE00002</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Rutter</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nepheline Syenite</t>
+          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6407,7 +6395,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1982 · Steep Rock Iron Mines Ltd</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -6418,23 +6406,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U72" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V72" t="n">
-        <v>46.09664</v>
+        <v>46.7905</v>
       </c>
       <c r="W72" t="n">
-        <v>-80.67718000000001</v>
+        <v>-81.51521</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I02SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
         </is>
       </c>
     </row>
@@ -6444,30 +6432,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jayfran-Pipawa</t>
+          <t>Reserve Creek Occurrences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MDI31F04SE00036</t>
+          <t>MDI42M12SE00008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Vardy</t>
+          <t>Eabametoong First Nation</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nepheline Syenite, Uranium</t>
+          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6479,17 +6467,21 @@
         <v>0</v>
       </c>
       <c r="J73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Mo 0.45%</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
+          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Pricemore Resources Inc · tested Gold</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -6498,29 +6490,25 @@
       </c>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V73" t="n">
-        <v>45.09484</v>
+        <v>51.57743</v>
       </c>
       <c r="W73" t="n">
-        <v>-77.76734999999999</v>
+        <v>-87.73681999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
         </is>
       </c>
     </row>
@@ -6530,21 +6518,21 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>West Graham</t>
+          <t>Eagle Copper Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MDI41I06NW00072</t>
+          <t>MDI41K16SW00002</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Crean Hill</t>
+          <t>Bourdages Corner</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6553,7 +6541,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Gold, Palladium, Platinum, Silver</t>
+          <t>Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6574,12 +6562,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Ni 0.30%</t>
+          <t>Cu 1.15%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1961 · Mcvittie-Graham Mining Co Ltd · tested Copper, Nickel</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6590,21 +6578,357 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="n">
+        <v>50</v>
+      </c>
+      <c r="U74" t="n">
+        <v>28</v>
+      </c>
+      <c r="V74" t="n">
+        <v>46.75901</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-84.26090000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Jayfran-Pipawa</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MDI31F04SE00036</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Vardy</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Nepheline Syenite, Uranium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
         <v>1</v>
       </c>
-      <c r="T74" t="n">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
+      <c r="S75" t="n">
+        <v>6</v>
+      </c>
+      <c r="T75" t="n">
+        <v>150</v>
+      </c>
+      <c r="U75" t="n">
+        <v>27</v>
+      </c>
+      <c r="V75" t="n">
+        <v>45.09484</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-77.76734999999999</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Northern Kyanite</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MDI41I10SE00004</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wahnapitae</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="n">
+        <v>50</v>
+      </c>
+      <c r="U76" t="n">
+        <v>27</v>
+      </c>
+      <c r="V76" t="n">
+        <v>46.50103</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-80.73585</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Stanleyville Vermiculite</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MDI31C16SW00030</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Stanleyville</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Vermiculite</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>100</v>
+      </c>
+      <c r="U77" t="n">
+        <v>27</v>
+      </c>
+      <c r="V77" t="n">
+        <v>44.79726</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-76.32017999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>West Graham</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MDI41I06NW00072</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Crean Hill</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Cobalt, Gold, Palladium, Platinum, Silver</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Ni 0.30%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1961 · Mcvittie-Graham Mining Co Ltd · tested Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>25</v>
       </c>
-      <c r="U74" t="n">
+      <c r="U78" t="n">
         <v>22</v>
       </c>
-      <c r="V74" t="n">
+      <c r="V78" t="n">
         <v>46.43504</v>
       </c>
-      <c r="W74" t="n">
+      <c r="W78" t="n">
         <v>-81.30689</v>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00072</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,10 +698,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +716,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V3" t="n">
-        <v>45.30338</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.90682</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -783,7 +787,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -803,14 +807,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>45.29002</v>
+        <v>48.24876</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.94167</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -885,14 +889,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.85917</v>
+        <v>45.28947</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.15956</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -902,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -925,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>44.85917</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1049,14 +1053,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.21442</v>
+        <v>45.30338</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.8742</v>
+        <v>-76.90682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1066,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.49976</v>
+        <v>45.29002</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.94167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1148,30 +1152,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U9" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.5021</v>
+        <v>44.55104</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.61301</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.52895</v>
+        <v>45.21442</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.78169</v>
+        <v>-77.8742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Windy Hill</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41P09SE00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cane</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cobalt, Silver, Uranium, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1426,7 +1430,7 @@
         </is>
       </c>
       <c r="I12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1436,14 +1440,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Ni 0.07%, Co 0.72%, U 34.98%</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Silver Economic Ore 2 Niccolite Economic Ore 1 Chalcopyrite Economic Gangue 2 Pitchblende Economic Gangue 3 Argentite Economic Gangue 6 Smaltite Economic Gangue Mineralization Comments Jun 24, 2024 (Nazha Sabiri) - Selected grab samples from pitchblende assayed as high as 34.98% uranium as U3O8 (MDC09). Sample (CAN05) taken from a dibase waste rock, in a historical trench, assayed 7240 ppm cobalt and 737 ppm nickel (File 2</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>47.60521</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-80.03053</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1522,14 +1522,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>46.28991</v>
+        <v>44.51686</v>
       </c>
       <c r="W13" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.62098</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1566,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C10NW00016</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Long Lake</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1610,12 +1606,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Zn 11.60%</t>
+          <t>Mo 1.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>42 drill hole(s) nearby · 1950–1975 · Cons Rochette Mines Ltd, W H Douglas</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="V14" t="n">
-        <v>44.6895</v>
+        <v>44.99932</v>
       </c>
       <c r="W14" t="n">
-        <v>-76.77161</v>
+        <v>-78.32907</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1652,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ethel Copper Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41P09NW00014</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Elk Lake</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1697,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>47.7491</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-80.27547</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1734,39 +1730,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pater Mine</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41J02NE00002</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Spragge</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1779,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1790,23 +1786,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>46.20698</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-82.6491</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1816,21 +1812,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McCoy Property</t>
+          <t>Temagami Copper Mine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31F03NW00055</t>
+          <t>MDI41I16NE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Adanac</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1839,12 +1835,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum</t>
+          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1858,10 +1854,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
+          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,23 +1872,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V17" t="n">
-        <v>45.20254</v>
+        <v>46.96233</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.38281000000001</v>
+        <v>-80.03716</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
         </is>
       </c>
     </row>
@@ -1898,30 +1898,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Windy Hill</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C11SW00028</t>
+          <t>MDI41P09SE00007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Queensborough</t>
+          <t>Cane</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Cobalt, Silver, Uranium, Nickel</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1940,10 +1940,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ni 0.07%, Co 0.72%, U 34.98%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Silver Economic Ore 2 Niccolite Economic Ore 1 Chalcopyrite Economic Gangue 2 Pitchblende Economic Gangue 3 Argentite Economic Gangue 6 Smaltite Economic Gangue Mineralization Comments Jun 24, 2024 (Nazha Sabiri) - Selected grab samples from pitchblende assayed as high as 34.98% uranium as U3O8 (MDC09). Sample (CAN05) taken from a dibase waste rock, in a historical trench, assayed 7240 ppm cobalt and 737 ppm nickel (File 2</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1954,23 +1958,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="V18" t="n">
-        <v>44.58796</v>
+        <v>47.60521</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.43434000000001</v>
+        <v>-80.03053</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09SE00007</t>
         </is>
       </c>
     </row>
@@ -1980,35 +1984,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Rabbit Mountain</t>
+          <t>Pater Mine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52A05SE00008</t>
+          <t>MDI41J02NE00002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Harstone</t>
+          <t>Spragge</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2025,7 +2029,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
+          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2036,23 +2040,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
         <v>50</v>
       </c>
       <c r="V19" t="n">
-        <v>48.30674</v>
+        <v>46.20698</v>
       </c>
       <c r="W19" t="n">
-        <v>-89.60534</v>
+        <v>-82.6491</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
         </is>
       </c>
     </row>
@@ -2062,35 +2066,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Beaver</t>
+          <t>Ore Chimney</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI52A05SE00009</t>
+          <t>MDI31C14SE00142</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Bishop Corners</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2107,7 +2111,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, D B Mcwilliams · tested Silver, Zinc</t>
+          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2122,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U20" t="n">
         <v>50</v>
       </c>
       <c r="V20" t="n">
-        <v>48.31944</v>
+        <v>44.77617</v>
       </c>
       <c r="W20" t="n">
-        <v>-89.63952999999999</v>
+        <v>-77.15194</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
         </is>
       </c>
     </row>
@@ -2144,30 +2148,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ore Chimney</t>
+          <t>Black Lake Occurrence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31C14SE00142</t>
+          <t>MDI41J01NW00026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bishop Corners</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2189,7 +2193,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
+          <t>13 drill hole(s) nearby · 1956–1966 · Sam Linton (Unknown), Gradore Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2209,14 +2213,14 @@
         <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>44.77617</v>
+        <v>46.24374</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.15194</v>
+        <v>-82.39867</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
         </is>
       </c>
     </row>
@@ -2226,30 +2230,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Black Lake Occurrence</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI41J01NW00026</t>
+          <t>MDI31C12SE00033</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2271,7 +2275,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1956–1966 · Sam Linton (Unknown), Gradore Mines Ltd · tested Copper, Gold</t>
+          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2291,14 +2295,14 @@
         <v>50</v>
       </c>
       <c r="V22" t="n">
-        <v>46.24374</v>
+        <v>44.50806</v>
       </c>
       <c r="W22" t="n">
-        <v>-82.39867</v>
+        <v>-77.61564</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
         </is>
       </c>
     </row>
@@ -2364,10 +2368,10 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U23" t="n">
         <v>50</v>
@@ -2390,30 +2394,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Climax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI31C12SE00033</t>
+          <t>MDI52A05SE00016</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2435,7 +2439,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
+          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2446,23 +2450,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T24" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="U24" t="n">
         <v>50</v>
       </c>
       <c r="V24" t="n">
-        <v>44.50806</v>
+        <v>48.31312</v>
       </c>
       <c r="W24" t="n">
-        <v>-77.61564</v>
+        <v>-89.66484</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
         </is>
       </c>
     </row>
@@ -2472,35 +2476,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Climax</t>
+          <t>Buckles Mine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI52A05SE00016</t>
+          <t>MDI41J07NE00004</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2517,7 +2521,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2528,23 +2532,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U25" t="n">
         <v>50</v>
       </c>
       <c r="V25" t="n">
-        <v>48.31312</v>
+        <v>46.37605</v>
       </c>
       <c r="W25" t="n">
-        <v>-89.66484</v>
+        <v>-82.58892</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
         </is>
       </c>
     </row>
@@ -2554,30 +2558,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hermenia Mine, No. 3 Shaft</t>
+          <t>Vermor Gold Mine</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MDI41J01NE00022</t>
+          <t>MDI52K01SW00004</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Walford</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.7</v>
+        <v>10.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2599,7 +2603,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>40 drill hole(s) nearby · 1951–2005 · East Sullivan Mines Ltd, Mcvittie, Jerome&amp;Doyon/ East Sullivan Mines Ltd · tested Copper</t>
+          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2610,23 +2614,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U26" t="n">
         <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>46.24928</v>
+        <v>50.01111</v>
       </c>
       <c r="W26" t="n">
-        <v>-82.17301999999999</v>
+        <v>-92.26211000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00022</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
         </is>
       </c>
     </row>
@@ -2636,30 +2640,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vermor Gold Mine</t>
+          <t>Massey Mine No. 4 Shaft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MDI52K01SW00004</t>
+          <t>MDI41J01NE00023</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10.9</v>
+        <v>4.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2681,7 +2685,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
+          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2692,23 +2696,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T27" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="U27" t="n">
         <v>50</v>
       </c>
       <c r="V27" t="n">
-        <v>50.01111</v>
+        <v>46.2376</v>
       </c>
       <c r="W27" t="n">
-        <v>-92.26211000000001</v>
+        <v>-82.12882</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2722,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nordic Mine</t>
+          <t>Quirke No. 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDI41J07NE00009</t>
+          <t>MDI41J10SE00007</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2732,7 +2736,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9</v>
+        <v>16</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2741,7 +2745,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Yttrium</t>
+          <t>Uranium, Rare Earth Elements, Thorium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2763,7 +2767,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
+          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2783,14 +2787,14 @@
         <v>50</v>
       </c>
       <c r="V28" t="n">
-        <v>46.37802</v>
+        <v>46.51253</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.58893</v>
+        <v>-82.64662</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
         </is>
       </c>
     </row>
@@ -2800,21 +2804,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Reuben McKee Property</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDI41J11SW00058</t>
+          <t>MDI52A10NE00008</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dunns Valley</t>
+          <t>Pearl</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>16.6</v>
+        <v>2.8</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2845,7 +2849,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Two samples taken from the Resident Geologist Staff in 2012 each returned assays of 1.4% Cu.</t>
+          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2856,23 +2860,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U29" t="n">
         <v>50</v>
       </c>
       <c r="V29" t="n">
-        <v>46.56806</v>
+        <v>48.67856</v>
       </c>
       <c r="W29" t="n">
-        <v>-83.46539</v>
+        <v>-88.62576</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J11SW00058</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
         </is>
       </c>
     </row>
@@ -2882,30 +2886,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Reuben McKee Property</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI41J11SW00058</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Dunns Valley</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9</v>
+        <v>16.6</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2927,7 +2931,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, Rio Canadian Expl Ltd/Knight-Adair</t>
+          <t>Two samples taken from the Resident Geologist Staff in 2012 each returned assays of 1.4% Cu.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2938,23 +2942,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="U30" t="n">
         <v>50</v>
       </c>
       <c r="V30" t="n">
-        <v>44.72488</v>
+        <v>46.56806</v>
       </c>
       <c r="W30" t="n">
-        <v>-78.80319</v>
+        <v>-83.46539</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J11SW00058</t>
         </is>
       </c>
     </row>
@@ -2964,35 +2968,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Massey Mine No. 4 Shaft</t>
+          <t>Silver Mountain West</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDI41J01NE00023</t>
+          <t>MDI52A04NW00003</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -3009,7 +3013,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3020,23 +3024,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="U31" t="n">
         <v>50</v>
       </c>
       <c r="V31" t="n">
-        <v>46.2376</v>
+        <v>48.24757</v>
       </c>
       <c r="W31" t="n">
-        <v>-82.12882</v>
+        <v>-89.8866</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3050,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quirke No. 1</t>
+          <t>Nordic Mine</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDI41J10SE00007</t>
+          <t>MDI41J07NE00009</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3060,7 +3064,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>16</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3069,7 +3073,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Uranium, Rare Earth Elements, Thorium</t>
+          <t>Uranium, Thorium, Yttrium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3091,7 +3095,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3111,14 +3115,14 @@
         <v>50</v>
       </c>
       <c r="V32" t="n">
-        <v>46.51253</v>
+        <v>46.37802</v>
       </c>
       <c r="W32" t="n">
-        <v>-82.64662</v>
+        <v>-82.58893</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
         </is>
       </c>
     </row>
@@ -3128,30 +3132,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Buckles Mine</t>
+          <t>Moneta Mine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MDI41J07NE00004</t>
+          <t>MDI42A06NW00003</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Schumacher</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3173,7 +3177,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
+          <t>The average grade of the ore in leucoxene andesite was approximately 0.60 oz/t and the average in the pillowed metavolcanics was 0.30 oz/t.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3193,14 +3197,14 @@
         <v>50</v>
       </c>
       <c r="V33" t="n">
-        <v>46.37605</v>
+        <v>48.47006</v>
       </c>
       <c r="W33" t="n">
-        <v>-82.58892</v>
+        <v>-81.32491</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A06NW00003</t>
         </is>
       </c>
     </row>
@@ -3210,30 +3214,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Contact Bay</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MDI000000000779</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3255,7 +3259,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, Rio Canadian Expl Ltd/Knight-Adair</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3266,23 +3270,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T34" t="n">
-        <v>25</v>
+        <v>275</v>
       </c>
       <c r="U34" t="n">
         <v>50</v>
       </c>
       <c r="V34" t="n">
-        <v>49.69695</v>
+        <v>44.72488</v>
       </c>
       <c r="W34" t="n">
-        <v>-92.82165999999999</v>
+        <v>-78.80319</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -3292,30 +3296,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Contact Bay</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDI52A10NE00008</t>
+          <t>MDI000000000779</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pearl</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3337,7 +3341,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
+          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3348,23 +3352,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U35" t="n">
         <v>50</v>
       </c>
       <c r="V35" t="n">
-        <v>48.67856</v>
+        <v>49.69695</v>
       </c>
       <c r="W35" t="n">
-        <v>-88.62576</v>
+        <v>-92.82165999999999</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
         </is>
       </c>
     </row>
@@ -3374,21 +3378,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Crystal-Comstock Property</t>
+          <t>Addington Mine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDI41I15SE00006</t>
+          <t>MDI31C11NE00010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cryderman Subdivision</t>
+          <t>Flinton Corner</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12.9</v>
+        <v>1.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3397,7 +3401,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Copper, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3419,7 +3423,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
+          <t>3 drill hole(s) nearby · 1983–1984 · R C Longmuir, C Longmuir/ C. Roger Young</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3430,23 +3434,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U36" t="n">
         <v>50</v>
       </c>
       <c r="V36" t="n">
-        <v>46.75321</v>
+        <v>44.71386</v>
       </c>
       <c r="W36" t="n">
-        <v>-80.62255</v>
+        <v>-77.18101</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
         </is>
       </c>
     </row>
@@ -3456,39 +3460,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kell Claims</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDI41P10SE00002</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Gowganda</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cobalt, Copper, Nickel, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3501,7 +3505,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>A bulk sample of 253 pounds assayed 1703.8 oz/t Ag and yielded 180 lbs Co. A drill hole completed by Ourgold Mining Company returned 1.11% Cu, 0.56 oz/t Ag and 0.07% Co over 15 feet; 5.3% Cu, 1.2 oz/t Ag and 0.9% Co over 11.8 feet; and 25 feet averaging 2.23% Cu and 1.18 oz/t Ag.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3512,23 +3516,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T37" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V37" t="n">
-        <v>47.50538</v>
+        <v>44.63956</v>
       </c>
       <c r="W37" t="n">
-        <v>-80.64733</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P10SE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -3538,39 +3542,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Silver Mountain West</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDI52A04NW00003</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3583,7 +3587,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3594,23 +3598,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T38" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V38" t="n">
-        <v>48.24757</v>
+        <v>46.29559</v>
       </c>
       <c r="W38" t="n">
-        <v>-89.8866</v>
+        <v>-83.20277</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -3620,42 +3624,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bousquet</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MDI41I04NE00004</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>McGregor Bay</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3665,7 +3669,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1979 · Curtin Mines Ltd</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3674,29 +3678,25 @@
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>abuts Killarney Lakelands And Headwaters Provincial Park (Natural Environment Class) boundary</t>
-        </is>
-      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U39" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V39" t="n">
-        <v>46.14902</v>
+        <v>46.30402</v>
       </c>
       <c r="W39" t="n">
-        <v>-81.62088</v>
+        <v>-81.53989</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I04NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -3706,30 +3706,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3751,7 +3751,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3762,23 +3762,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U40" t="n">
         <v>48</v>
       </c>
       <c r="V40" t="n">
-        <v>44.63956</v>
+        <v>44.55883</v>
       </c>
       <c r="W40" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -3788,30 +3788,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3833,7 +3833,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3844,23 +3844,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T41" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U41" t="n">
         <v>48</v>
       </c>
       <c r="V41" t="n">
-        <v>46.30402</v>
+        <v>44.73856</v>
       </c>
       <c r="W41" t="n">
-        <v>-81.53989</v>
+        <v>-76.32056</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -3870,30 +3870,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3915,7 +3915,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3926,23 +3926,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U42" t="n">
         <v>48</v>
       </c>
       <c r="V42" t="n">
-        <v>46.29559</v>
+        <v>44.47438</v>
       </c>
       <c r="W42" t="n">
-        <v>-83.20277</v>
+        <v>-76.51861</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -3952,21 +3952,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3997,7 +3997,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4008,23 +4008,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T43" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U43" t="n">
         <v>48</v>
       </c>
       <c r="V43" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W43" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -4034,35 +4034,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I44" t="b">
@@ -4079,7 +4079,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4090,23 +4090,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T44" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U44" t="n">
         <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>44.55883</v>
+        <v>48.69799</v>
       </c>
       <c r="W44" t="n">
-        <v>-76.57349000000001</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -4116,39 +4116,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>McManus Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41P09NW00043</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -4158,10 +4158,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Ag 171g/t</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>A 90 pound sample submitted in 1956 assayed: Cu-trace, Ni - 23.4%, Co - 4.45%, Fe - 1.35%, As-37.62%, S-2.52%, Ag-trace.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4172,23 +4176,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>325</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
         <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>44.62168</v>
+        <v>47.72286</v>
       </c>
       <c r="W45" t="n">
-        <v>-76.56963</v>
+        <v>-80.28064000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
         </is>
       </c>
     </row>
@@ -4198,39 +4202,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Rock Lake</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41J05NE00002</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Ophir</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -4243,7 +4247,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4254,23 +4258,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="U46" t="n">
         <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>44.47438</v>
+        <v>46.44114</v>
       </c>
       <c r="W46" t="n">
-        <v>-76.51861</v>
+        <v>-83.73430999999999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
         </is>
       </c>
     </row>
@@ -4280,30 +4284,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Bridget Lake Occurrence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41N15NW00007</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Michipicoten River</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4312,10 +4316,10 @@
         </is>
       </c>
       <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
         <v>1</v>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4325,7 +4329,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4334,25 +4338,29 @@
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
+        </is>
+      </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U47" t="n">
         <v>48</v>
       </c>
       <c r="V47" t="n">
-        <v>48.69799</v>
+        <v>47.8998</v>
       </c>
       <c r="W47" t="n">
-        <v>-93.27513999999999</v>
+        <v>-84.85621</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
         </is>
       </c>
     </row>
@@ -4362,35 +4370,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rock Lake</t>
+          <t>Tashota-Nipigon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MDI41J05NE00002</t>
+          <t>MDI42L04SE00005</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ophir</t>
+          <t>Auden</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.5</v>
+        <v>29.3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Bismuth, Copper, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4407,7 +4415,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
+          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4418,23 +4426,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U48" t="n">
         <v>48</v>
       </c>
       <c r="V48" t="n">
-        <v>46.44114</v>
+        <v>50.04735</v>
       </c>
       <c r="W48" t="n">
-        <v>-83.73430999999999</v>
+        <v>-87.58936</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
         </is>
       </c>
     </row>
@@ -4444,42 +4452,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bridget Lake Occurrence</t>
+          <t>Jardun Mine - No 3 Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MDI41N15NW00007</t>
+          <t>MDI41K09NE00090</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Michipicoten River</t>
+          <t>Northland</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4489,7 +4497,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
+          <t>137 drill hole(s) nearby · 1951–1984 · Longbow Exploration Inc/Watson Lake Mines Ltd, Jardun Mines Ltd · tested Copper, Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -4498,11 +4506,7 @@
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
-        </is>
-      </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
         <v>1</v>
       </c>
@@ -4513,14 +4517,14 @@
         <v>48</v>
       </c>
       <c r="V49" t="n">
-        <v>47.8998</v>
+        <v>46.63751</v>
       </c>
       <c r="W49" t="n">
-        <v>-84.85621</v>
+        <v>-84.14293000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00090</t>
         </is>
       </c>
     </row>
@@ -4530,39 +4534,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tashota-Nipigon</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MDI42L04SE00005</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Auden</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>29.3</v>
+        <v>0.9</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gold, Bismuth, Copper, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -4575,7 +4579,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4586,23 +4590,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U50" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V50" t="n">
-        <v>50.04735</v>
+        <v>45.58868</v>
       </c>
       <c r="W50" t="n">
-        <v>-87.58936</v>
+        <v>-79.70944</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4616,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Gatling Five Acre</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31C12SE00028</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4626,7 +4630,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4657,7 +4661,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>11 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -4674,17 +4678,17 @@
         <v>200</v>
       </c>
       <c r="U51" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="V51" t="n">
-        <v>44.51686</v>
+        <v>44.51496</v>
       </c>
       <c r="W51" t="n">
-        <v>-77.62098</v>
+        <v>-77.62126000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
         </is>
       </c>
     </row>
@@ -4694,35 +4698,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McManus Group</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MDI41P09NW00043</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cobalt, Copper, Nickel, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4736,14 +4740,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Ag 171g/t</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>A 90 pound sample submitted in 1956 assayed: Cu-trace, Ni - 23.4%, Co - 4.45%, Fe - 1.35%, As-37.62%, S-2.52%, Ag-trace.</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4754,23 +4754,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U52" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="V52" t="n">
-        <v>47.72286</v>
+        <v>49.71016</v>
       </c>
       <c r="W52" t="n">
-        <v>-80.28064000000001</v>
+        <v>-94.40097</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -4780,39 +4780,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -4825,7 +4825,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4836,23 +4836,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T53" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U53" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V53" t="n">
-        <v>45.58868</v>
+        <v>44.5143</v>
       </c>
       <c r="W53" t="n">
-        <v>-79.70944</v>
+        <v>-77.61444</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -4862,12 +4862,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Gatling Five Acre</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MDI31C12SE00028</t>
+          <t>MDI31C12SE00039</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4907,7 +4907,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper</t>
+          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4918,23 +4918,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T54" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U54" t="n">
         <v>41</v>
       </c>
       <c r="V54" t="n">
-        <v>44.51496</v>
+        <v>44.51231</v>
       </c>
       <c r="W54" t="n">
-        <v>-77.62126000000001</v>
+        <v>-77.62011</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
         </is>
       </c>
     </row>
@@ -4944,35 +4944,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MDI31C12SE00039</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.3</v>
+        <v>7</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4986,10 +4986,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Mo 2.00%</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper, Gold</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Nortoba Mines · tested Gold</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5000,23 +5004,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U55" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="V55" t="n">
-        <v>44.51231</v>
+        <v>49.69198</v>
       </c>
       <c r="W55" t="n">
-        <v>-77.62011</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>
@@ -5026,30 +5030,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>Springer-Lavergne Rare Earth Project</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI31L05NW00002</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Crystal Falls</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5068,14 +5072,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Mo 2.00%</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Nortoba Mines · tested Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -5092,17 +5092,17 @@
         <v>25</v>
       </c>
       <c r="U56" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="V56" t="n">
-        <v>49.69198</v>
+        <v>46.44231</v>
       </c>
       <c r="W56" t="n">
-        <v>-88.04716999999999</v>
+        <v>-79.94853999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
         </is>
       </c>
     </row>
@@ -5112,35 +5112,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kam Kotia Mine</t>
+          <t>Empire B Zone</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDI42A12SE00005</t>
+          <t>MDI31D16NE00146</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Kamiskotia</t>
+          <t>South Wilberforce</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Gold, Silver</t>
+          <t>Uranium, Yttrium, Fluorite, Thorium</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -5154,14 +5154,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Cu 1.10%, Zn 1.17%</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1954–1993 · Falconbridge Ltd, Pleno Mines Ltd</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5178,17 +5174,17 @@
         <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="V57" t="n">
-        <v>48.59125</v>
+        <v>44.99427</v>
       </c>
       <c r="W57" t="n">
-        <v>-81.60500999999999</v>
+        <v>-78.19589999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A12SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
         </is>
       </c>
     </row>
@@ -5198,30 +5194,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Bannockburn Gold Project</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MDI42A09SW00163</t>
+          <t>MDI31C12NE00195</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Holtyre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.9</v>
+        <v>0.8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5243,7 +5239,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons  · tested Gold</t>
+          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5254,23 +5250,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T58" t="n">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="U58" t="n">
         <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>48.50619</v>
+        <v>44.64988</v>
       </c>
       <c r="W58" t="n">
-        <v>-80.31543000000001</v>
+        <v>-77.54698</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
         </is>
       </c>
     </row>
@@ -5280,30 +5276,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Springer-Lavergne Rare Earth Project</t>
+          <t>Abbican</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDI31L05NW00002</t>
+          <t>MDI41J06NE00044</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Crystal Falls</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5.1</v>
+        <v>10.3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5315,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5325,7 +5321,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
+          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5334,7 +5330,11 @@
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S59" t="n">
         <v>1</v>
       </c>
@@ -5345,14 +5345,14 @@
         <v>32</v>
       </c>
       <c r="V59" t="n">
-        <v>46.44231</v>
+        <v>46.47973</v>
       </c>
       <c r="W59" t="n">
-        <v>-79.94853999999999</v>
+        <v>-83.15055</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
         </is>
       </c>
     </row>
@@ -5362,21 +5362,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lakemount Property</t>
+          <t>Macassa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MDI42C02SE00090</t>
+          <t>MDI31C13SE00099</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Ormsby</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
+          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5407,7 +5407,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>98 drill hole(s) nearby · 1952–1982 · Firespur Expl Ltd, Kelore Mines Ltd · tested Copper, Nickel</t>
+          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5418,23 +5418,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="U60" t="n">
         <v>32</v>
       </c>
       <c r="V60" t="n">
-        <v>48.06318</v>
+        <v>44.868</v>
       </c>
       <c r="W60" t="n">
-        <v>-84.62636999999999</v>
+        <v>-77.72254</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
         </is>
       </c>
     </row>
@@ -5444,30 +5444,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abbican</t>
+          <t>Band-Ore Mattagami Zone 4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MDI41J06NE00044</t>
+          <t>MDI52B09SE00024</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Shebandowan</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10.3</v>
+        <v>4.2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
+          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5498,11 +5498,7 @@
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="n">
         <v>1</v>
       </c>
@@ -5513,14 +5509,14 @@
         <v>32</v>
       </c>
       <c r="V61" t="n">
-        <v>46.47973</v>
+        <v>48.62462</v>
       </c>
       <c r="W61" t="n">
-        <v>-83.15055</v>
+        <v>-90.12229000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
         </is>
       </c>
     </row>
@@ -5530,30 +5526,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Empire B Zone</t>
+          <t>Scramble Mine</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MDI31D16NE00146</t>
+          <t>MDI52E16SW00091</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>South Wilberforce</t>
+          <t>Pelletier Bridge</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Uranium, Yttrium, Fluorite, Thorium</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5575,7 +5571,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
+          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5595,14 +5591,14 @@
         <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>44.99427</v>
+        <v>49.78399</v>
       </c>
       <c r="W62" t="n">
-        <v>-78.19589999999999</v>
+        <v>-94.37701</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
         </is>
       </c>
     </row>
@@ -5612,21 +5608,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Macassa</t>
+          <t>Simon Copper Property</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MDI31C13SE00099</t>
+          <t>MDI31F03NW00044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ormsby</t>
+          <t>Slate Falls</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5635,7 +5631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
+          <t>Copper, Zinc, Iron, Selenium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5657,7 +5653,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
+          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -5668,23 +5664,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U63" t="n">
         <v>32</v>
       </c>
       <c r="V63" t="n">
-        <v>44.868</v>
+        <v>45.20807</v>
       </c>
       <c r="W63" t="n">
-        <v>-77.72254</v>
+        <v>-77.31331</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
         </is>
       </c>
     </row>
@@ -5694,30 +5690,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Band-Ore Mattagami Zone 4</t>
+          <t>Hermina</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MDI52B09SE00024</t>
+          <t>MDI41J01NE00007</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Shebandowan</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5739,7 +5735,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
+          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5750,23 +5746,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T64" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U64" t="n">
         <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>48.62462</v>
+        <v>46.23918</v>
       </c>
       <c r="W64" t="n">
-        <v>-90.12229000000001</v>
+        <v>-82.15586</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
         </is>
       </c>
     </row>
@@ -5776,21 +5772,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bannockburn Gold Project</t>
+          <t>Shoot Zone Deposit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MDI31C12NE00195</t>
+          <t>MDI42A10SE00065</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5799,7 +5795,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5821,7 +5817,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
+          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5832,23 +5828,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T65" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="U65" t="n">
         <v>32</v>
       </c>
       <c r="V65" t="n">
-        <v>44.64988</v>
+        <v>48.56426</v>
       </c>
       <c r="W65" t="n">
-        <v>-77.54698</v>
+        <v>-80.63866</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
         </is>
       </c>
     </row>
@@ -5858,21 +5854,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scramble Mine</t>
+          <t>Scadding Gold Property</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MDI52E16SW00091</t>
+          <t>MDI41I10NE00012</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pelletier Bridge</t>
+          <t>Basin Mines</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5881,7 +5877,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Palladium, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5903,7 +5899,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
+          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5923,14 +5919,14 @@
         <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>49.78399</v>
+        <v>46.65087</v>
       </c>
       <c r="W66" t="n">
-        <v>-94.37701</v>
+        <v>-80.61375</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
         </is>
       </c>
     </row>
@@ -5940,30 +5936,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Simon Copper Property</t>
+          <t>Geneva Lake Mine</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MDI31F03NW00044</t>
+          <t>MDI41I13SE00002</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Slate Falls</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Iron, Selenium</t>
+          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5985,7 +5981,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -6005,14 +6001,14 @@
         <v>32</v>
       </c>
       <c r="V67" t="n">
-        <v>45.20807</v>
+        <v>46.7905</v>
       </c>
       <c r="W67" t="n">
-        <v>-77.31331</v>
+        <v>-81.51521</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
         </is>
       </c>
     </row>
@@ -6022,30 +6018,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shoot Zone Deposit</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MDI42A10SE00065</t>
+          <t>MDI42A09SW00163</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Holtyre</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6067,7 +6063,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
+          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons  · tested Gold</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -6078,23 +6074,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U68" t="n">
         <v>32</v>
       </c>
       <c r="V68" t="n">
-        <v>48.56426</v>
+        <v>48.50619</v>
       </c>
       <c r="W68" t="n">
-        <v>-80.63866</v>
+        <v>-80.31543000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
         </is>
       </c>
     </row>
@@ -6104,30 +6100,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scadding Gold Property</t>
+          <t>Lakemount Property</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDI41I10NE00012</t>
+          <t>MDI42C02SE00090</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Basin Mines</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Silver</t>
+          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6149,7 +6145,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
+          <t>98 drill hole(s) nearby · 1952–1982 · Firespur Expl Ltd, Kelore Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -6169,14 +6165,14 @@
         <v>32</v>
       </c>
       <c r="V69" t="n">
-        <v>46.65087</v>
+        <v>48.06318</v>
       </c>
       <c r="W69" t="n">
-        <v>-80.61375</v>
+        <v>-84.62636999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
         </is>
       </c>
     </row>
@@ -6186,30 +6182,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hermina</t>
+          <t>Reserve Creek Occurrences</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MDI41J01NE00007</t>
+          <t>MDI42M12SE00008</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Eabametoong First Nation</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6.7</v>
+        <v>12</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6228,10 +6224,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Mo 0.45%</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
+          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Pricemore Resources Inc · tested Gold</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -6242,23 +6242,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U70" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="V70" t="n">
-        <v>46.23918</v>
+        <v>51.57743</v>
       </c>
       <c r="W70" t="n">
-        <v>-82.15586</v>
+        <v>-87.73681999999999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
         </is>
       </c>
     </row>
@@ -6268,30 +6268,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Methuen Township Ilmenite</t>
+          <t>Eagle Copper Mine</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MDI31C12NW00114</t>
+          <t>MDI41K16SW00002</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Oak Lake</t>
+          <t>Bourdages Corner</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Titanium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6310,10 +6310,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Cu 1.15%</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>62 drill hole(s) nearby · 1969–2008 · Canadian Nickel Co Ltd, M R Tripp</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -6324,23 +6328,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="V71" t="n">
-        <v>44.62955</v>
+        <v>46.75901</v>
       </c>
       <c r="W71" t="n">
-        <v>-77.87374</v>
+        <v>-84.26090000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NW00114</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
         </is>
       </c>
     </row>
@@ -6350,30 +6354,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Geneva Lake Mine</t>
+          <t>Northern Kyanite</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MDI41I13SE00002</t>
+          <t>MDI41I10SE00004</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Wahnapitae</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
+          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6395,7 +6399,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
+          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -6406,23 +6410,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T72" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U72" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="V72" t="n">
-        <v>46.7905</v>
+        <v>46.50103</v>
       </c>
       <c r="W72" t="n">
-        <v>-81.51521</v>
+        <v>-80.73585</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
         </is>
       </c>
     </row>
@@ -6432,30 +6436,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Reserve Creek Occurrences</t>
+          <t>Stanleyville Vermiculite</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MDI42M12SE00008</t>
+          <t>MDI31C16SW00030</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Eabametoong First Nation</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>12</v>
+        <v>1.3</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
+          <t>Vermiculite</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6474,14 +6478,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Mo 0.45%</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Pricemore Resources Inc · tested Gold</t>
+          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -6492,23 +6492,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T73" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U73" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V73" t="n">
-        <v>51.57743</v>
+        <v>44.79726</v>
       </c>
       <c r="W73" t="n">
-        <v>-87.73681999999999</v>
+        <v>-76.32017999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
         </is>
       </c>
     </row>
@@ -6518,30 +6518,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Eagle Copper Mine</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MDI41K16SW00002</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Bourdages Corner</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6553,21 +6553,17 @@
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Cu 1.15%</t>
-        </is>
-      </c>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6576,25 +6572,29 @@
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T74" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U74" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V74" t="n">
-        <v>46.75901</v>
+        <v>45.09484</v>
       </c>
       <c r="W74" t="n">
-        <v>-84.26090000000001</v>
+        <v>-77.76734999999999</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
         </is>
       </c>
     </row>
@@ -6604,21 +6604,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jayfran-Pipawa</t>
+          <t>95-2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MDI31F04SE00036</t>
+          <t>MDI31M12SW00017</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Vardy</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nepheline Syenite, Uranium</t>
+          <t>Diamond, Kimberlite</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
+          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -6658,279 +6658,25 @@
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R75" t="inlineStr"/>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U75" t="n">
         <v>27</v>
       </c>
       <c r="V75" t="n">
-        <v>45.09484</v>
+        <v>47.52342</v>
       </c>
       <c r="W75" t="n">
-        <v>-77.76734999999999</v>
+        <v>-79.89148</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Northern Kyanite</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>MDI41I10SE00004</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Wahnapitae</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I76" t="b">
-        <v>0</v>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="n">
-        <v>2</v>
-      </c>
-      <c r="T76" t="n">
-        <v>50</v>
-      </c>
-      <c r="U76" t="n">
-        <v>27</v>
-      </c>
-      <c r="V76" t="n">
-        <v>46.50103</v>
-      </c>
-      <c r="W76" t="n">
-        <v>-80.73585</v>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Stanleyville Vermiculite</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>MDI31C16SW00030</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Stanleyville</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Vermiculite</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="n">
-        <v>4</v>
-      </c>
-      <c r="T77" t="n">
-        <v>100</v>
-      </c>
-      <c r="U77" t="n">
-        <v>27</v>
-      </c>
-      <c r="V77" t="n">
-        <v>44.79726</v>
-      </c>
-      <c r="W77" t="n">
-        <v>-76.32017999999999</v>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>West Graham</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>MDI41I06NW00072</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Crean Hill</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Copper, Nickel, Cobalt, Gold, Palladium, Platinum, Silver</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I78" t="b">
-        <v>0</v>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Ni 0.30%</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1961 · Mcvittie-Graham Mining Co Ltd · tested Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>25</v>
-      </c>
-      <c r="U78" t="n">
-        <v>22</v>
-      </c>
-      <c r="V78" t="n">
-        <v>46.43504</v>
-      </c>
-      <c r="W78" t="n">
-        <v>-81.30689</v>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00072</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>45.39062</v>
+        <v>44.55039</v>
       </c>
       <c r="W2" t="n">
-        <v>-76.70397</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,14 +698,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -716,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>45.30338</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-76.90682</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -742,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -787,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -807,14 +803,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>48.24876</v>
+        <v>45.29002</v>
       </c>
       <c r="W4" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -824,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +885,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.28947</v>
+        <v>44.85917</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -906,21 +902,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +925,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.85917</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.15956</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1049,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.30338</v>
+        <v>45.21442</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.90682</v>
+        <v>-77.8742</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.29002</v>
+        <v>44.49976</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94167</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1148,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55104</v>
+        <v>44.5021</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.61301</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V10" t="n">
-        <v>45.21442</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.8742</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Windy Hill</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI41P09SE00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cane</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt, Silver, Uranium, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1430,7 +1426,7 @@
         </is>
       </c>
       <c r="I12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1440,10 +1436,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ni 0.07%, Co 0.72%, U 34.98%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Silver Economic Ore 2 Niccolite Economic Ore 1 Chalcopyrite Economic Gangue 2 Pitchblende Economic Gangue 3 Argentite Economic Gangue 6 Smaltite Economic Gangue Mineralization Comments Jun 24, 2024 (Nazha Sabiri) - Selected grab samples from pitchblende assayed as high as 34.98% uranium as U3O8 (MDC09). Sample (CAN05) taken from a dibase waste rock, in a historical trench, assayed 7240 ppm cobalt and 737 ppm nickel (File 2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>47.60521</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-80.03053</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09SE00007</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1522,10 +1522,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="U13" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="V13" t="n">
-        <v>44.51686</v>
+        <v>46.28991</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.62098</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1566,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C10NW00016</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Long Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Zinc, Lead, Marble (Structural Material), Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1594,7 +1598,7 @@
         </is>
       </c>
       <c r="I14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1606,12 +1610,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Mo 1.00%</t>
+          <t>Zn 11.60%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>42 drill hole(s) nearby · 1950–1975 · Cons Rochette Mines Ltd, W H Douglas</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U14" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="V14" t="n">
-        <v>44.99932</v>
+        <v>44.6895</v>
       </c>
       <c r="W14" t="n">
-        <v>-78.32907</v>
+        <v>-76.77161</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10NW00016</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1652,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ethel Copper Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41P09NW00014</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Elk Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1680,7 +1684,7 @@
         </is>
       </c>
       <c r="I15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1693,7 +1697,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Bornite Economic Ore 1 Calcite Economic Gangue 2 Specularite Economic Gangue 3 Sphalerite Economic Gangue Mineralization Comments Oct 12, 2011 (A Wilson) - The grade of the ore was reportedly 3.15% Cu over 6.3 feet. Assays from the diamond drill logs showed variable values with the one of the better assays being 10.4% Cu over 2.8 feet.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>47.7491</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-80.27547</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00014</t>
         </is>
       </c>
     </row>
@@ -1730,39 +1734,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Pater Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J02NE00002</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Spragge</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1775,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1786,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>46.20698</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-82.6491</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
         </is>
       </c>
     </row>
@@ -1812,21 +1816,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Temagami Copper Mine</t>
+          <t>McCoy Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41I16NE00004</t>
+          <t>MDI31F03NW00055</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Adanac</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1835,12 +1839,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Nickel, Silver, Cobalt, Palladium, Platinum</t>
+          <t>Copper, Molybdenum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1854,14 +1858,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Au 110112g/t, Pd 45359g/t, Ni 0.00%</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>returned 0.108% Cu, 0.24% Ni, 0.08% Co over 25ft in DDH 5; 1.01% Cu, 0.25% Ni over 36.2 ft in DDH 9 and 1.85% cu, 0.05% Ni and 0.025% Co over 6.25 ft in DDH 8.</t>
+          <t>Assays from Lalonde DDH FNB24 returned 0.08% Cu over1.4 m and DDHFNB25 returned 0.05% Cu over 2.7 m.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,23 +1872,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
+        <v>25</v>
+      </c>
+      <c r="U17" t="n">
         <v>50</v>
       </c>
-      <c r="U17" t="n">
-        <v>54</v>
-      </c>
       <c r="V17" t="n">
-        <v>46.96233</v>
+        <v>45.20254</v>
       </c>
       <c r="W17" t="n">
-        <v>-80.03716</v>
+        <v>-77.38281000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I16NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00055</t>
         </is>
       </c>
     </row>
@@ -1898,30 +1898,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Windy Hill</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41P09SE00007</t>
+          <t>MDI31C11SW00028</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cane</t>
+          <t>Queensborough</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cobalt, Silver, Uranium, Nickel</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1940,14 +1940,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Ni 0.07%, Co 0.72%, U 34.98%</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Silver Economic Ore 2 Niccolite Economic Ore 1 Chalcopyrite Economic Gangue 2 Pitchblende Economic Gangue 3 Argentite Economic Gangue 6 Smaltite Economic Gangue Mineralization Comments Jun 24, 2024 (Nazha Sabiri) - Selected grab samples from pitchblende assayed as high as 34.98% uranium as U3O8 (MDC09). Sample (CAN05) taken from a dibase waste rock, in a historical trench, assayed 7240 ppm cobalt and 737 ppm nickel (File 2</t>
+          <t>best gold assays from this vein are: 2.7 oz/ton gold over 2.4 m in Shaft #1, 3.77 oz/ton over 3.0 m and 0.40 oz/ton over 1.80 m in Shaft #3. Vein #3, no dimension or orientation reported, veins assayed 0.15 oz/ton gold over 1.5 m and 0.31 oz/ton over 1.5 m. Vein #4 is 91.0 m long with best gold assay of 0.57 oz/ton over 2.9 m. Gold values range from 0.01 oz/ton to 0.05 oz/ton over 1.5 m to 5.5 m in Vein #5 and no significant values were encountered in Vein # 6 (File 31C11SW0020).</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1958,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T18" t="n">
+        <v>200</v>
+      </c>
+      <c r="U18" t="n">
         <v>50</v>
       </c>
-      <c r="U18" t="n">
-        <v>54</v>
-      </c>
       <c r="V18" t="n">
-        <v>47.60521</v>
+        <v>44.58796</v>
       </c>
       <c r="W18" t="n">
-        <v>-80.03053</v>
+        <v>-77.43434000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00028</t>
         </is>
       </c>
     </row>
@@ -1984,35 +1980,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pater Mine</t>
+          <t>Rabbit Mountain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI41J02NE00002</t>
+          <t>MDI52A05SE00008</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Spragge</t>
+          <t>Harstone</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Barite, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2029,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Diamond drilling in 1954 returned average assays of 1.6% Cu, plus a trace of Co over 5-6 feet.</t>
+          <t>The direct shipping ore contained over 1000 opt Ag and it is recorded that some of the material milled on the property contained about 80 opt Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2040,23 +2036,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U19" t="n">
         <v>50</v>
       </c>
       <c r="V19" t="n">
-        <v>46.20698</v>
+        <v>48.30674</v>
       </c>
       <c r="W19" t="n">
-        <v>-82.6491</v>
+        <v>-89.60534</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J02NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00008</t>
         </is>
       </c>
     </row>
@@ -2066,35 +2062,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ore Chimney</t>
+          <t>Beaver</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C14SE00142</t>
+          <t>MDI52A05SE00009</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bishop Corners</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
+          <t>Cobalt, Silver, Barite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2111,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
+          <t>11 drill hole(s) nearby · 1956–2018 · Cairngorm Mines Ltd, D B Mcwilliams · tested Silver, Zinc</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2122,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U20" t="n">
         <v>50</v>
       </c>
       <c r="V20" t="n">
-        <v>44.77617</v>
+        <v>48.31944</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.15194</v>
+        <v>-89.63952999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00009</t>
         </is>
       </c>
     </row>
@@ -2148,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Black Lake Occurrence</t>
+          <t>Ore Chimney</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI41J01NW00026</t>
+          <t>MDI31C14SE00142</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Bishop Corners</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Copper, Iron, Lead, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2193,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1956–1966 · Sam Linton (Unknown), Gradore Mines Ltd · tested Copper, Gold</t>
+          <t>Estimates of ore reserves in 1957 by Cavalier Mining Company include 11,000 tons grading 0.20 oz/ton Au and 5.64 oz/ton Ag from 50 feet above the 150-foot level to 50 feet below the 500-foot level.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2213,14 +2209,14 @@
         <v>50</v>
       </c>
       <c r="V21" t="n">
-        <v>46.24374</v>
+        <v>44.77617</v>
       </c>
       <c r="W21" t="n">
-        <v>-82.39867</v>
+        <v>-77.15194</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C14SE00142</t>
         </is>
       </c>
     </row>
@@ -2230,30 +2226,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pearce</t>
+          <t>Black Lake Occurrence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI31C12SE00033</t>
+          <t>MDI41J01NW00026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2275,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
+          <t>13 drill hole(s) nearby · 1956–1966 · Sam Linton (Unknown), Gradore Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2295,14 +2291,14 @@
         <v>50</v>
       </c>
       <c r="V22" t="n">
-        <v>44.50806</v>
+        <v>46.24374</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.61564</v>
+        <v>-82.39867</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NW00026</t>
         </is>
       </c>
     </row>
@@ -2368,10 +2364,10 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="U23" t="n">
         <v>50</v>
@@ -2394,30 +2390,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Climax</t>
+          <t>Pearce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI52A05SE00016</t>
+          <t>MDI31C12SE00033</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
+          <t>Gold, Arsenic, Silver</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2439,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
+          <t>The sample assayed 0.785 oz/ton Au, 0.05 oz/ton Ag, 2.17 percent As (OFR5537).</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2450,23 +2446,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="U24" t="n">
         <v>50</v>
       </c>
       <c r="V24" t="n">
-        <v>48.31312</v>
+        <v>44.50806</v>
       </c>
       <c r="W24" t="n">
-        <v>-89.66484</v>
+        <v>-77.61564</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00033</t>
         </is>
       </c>
     </row>
@@ -2476,35 +2472,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buckles Mine</t>
+          <t>Climax</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI41J07NE00004</t>
+          <t>MDI52A05SE00016</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nordic Townsite</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uranium, Copper</t>
+          <t>Silver, Fluorite, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2521,7 +2517,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
+          <t>Assays from 1968 returned 22.5 opt Ag across 0.7 m for a length of 76 m from the back of the W stope, first level, and 20.53 opt Ag across 0.7 m for a length of 42.7 m on the back of the E stope, first level.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2532,23 +2528,23 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
         <v>50</v>
       </c>
       <c r="V25" t="n">
-        <v>46.37605</v>
+        <v>48.31312</v>
       </c>
       <c r="W25" t="n">
-        <v>-82.58892</v>
+        <v>-89.66484</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A05SE00016</t>
         </is>
       </c>
     </row>
@@ -2558,30 +2554,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vermor Gold Mine</t>
+          <t>Hermenia Mine, No. 3 Shaft</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MDI52K01SW00004</t>
+          <t>MDI41J01NE00022</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Walford</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.9</v>
+        <v>6.7</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2603,7 +2599,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
+          <t>40 drill hole(s) nearby · 1951–2005 · East Sullivan Mines Ltd, Mcvittie, Jerome&amp;Doyon/ East Sullivan Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -2614,23 +2610,23 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U26" t="n">
         <v>50</v>
       </c>
       <c r="V26" t="n">
-        <v>50.01111</v>
+        <v>46.24928</v>
       </c>
       <c r="W26" t="n">
-        <v>-92.26211000000001</v>
+        <v>-82.17301999999999</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00022</t>
         </is>
       </c>
     </row>
@@ -2640,30 +2636,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Massey Mine No. 4 Shaft</t>
+          <t>Vermor Gold Mine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MDI41J01NE00023</t>
+          <t>MDI52K01SW00004</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.8</v>
+        <v>10.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2685,7 +2681,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
+          <t>19 drill hole(s) nearby · 1951–1989 · D E Smith, Denree Cons Mines Ltd</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -2696,23 +2692,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="U27" t="n">
         <v>50</v>
       </c>
       <c r="V27" t="n">
-        <v>46.2376</v>
+        <v>50.01111</v>
       </c>
       <c r="W27" t="n">
-        <v>-82.12882</v>
+        <v>-92.26211000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52K01SW00004</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2718,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quirke No. 1</t>
+          <t>Nordic Mine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MDI41J10SE00007</t>
+          <t>MDI41J07NE00009</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2736,7 +2732,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>0.9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2745,7 +2741,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uranium, Rare Earth Elements, Thorium</t>
+          <t>Uranium, Thorium, Yttrium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2767,7 +2763,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -2787,14 +2783,14 @@
         <v>50</v>
       </c>
       <c r="V28" t="n">
-        <v>46.51253</v>
+        <v>46.37802</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.64662</v>
+        <v>-82.58893</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
         </is>
       </c>
     </row>
@@ -2804,21 +2800,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Reuben McKee Property</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MDI52A10NE00008</t>
+          <t>MDI41J11SW00058</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pearl</t>
+          <t>Dunns Valley</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.8</v>
+        <v>16.6</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2827,7 +2823,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2849,7 +2845,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
+          <t>Two samples taken from the Resident Geologist Staff in 2012 each returned assays of 1.4% Cu.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -2860,23 +2856,23 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="U29" t="n">
         <v>50</v>
       </c>
       <c r="V29" t="n">
-        <v>48.67856</v>
+        <v>46.56806</v>
       </c>
       <c r="W29" t="n">
-        <v>-88.62576</v>
+        <v>-83.46539</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J11SW00058</t>
         </is>
       </c>
     </row>
@@ -2886,30 +2882,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reuben McKee Property</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDI41J11SW00058</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dunns Valley</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>16.6</v>
+        <v>0.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2931,7 +2927,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Two samples taken from the Resident Geologist Staff in 2012 each returned assays of 1.4% Cu.</t>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, Rio Canadian Expl Ltd/Knight-Adair</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2942,23 +2938,23 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="T30" t="n">
-        <v>25</v>
+        <v>275</v>
       </c>
       <c r="U30" t="n">
         <v>50</v>
       </c>
       <c r="V30" t="n">
-        <v>46.56806</v>
+        <v>44.72488</v>
       </c>
       <c r="W30" t="n">
-        <v>-83.46539</v>
+        <v>-78.80319</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J11SW00058</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -2968,35 +2964,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Silver Mountain West</t>
+          <t>Massey Mine No. 4 Shaft</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MDI52A04NW00003</t>
+          <t>MDI41J01NE00023</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -3013,7 +3009,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
+          <t>23 drill hole(s) nearby · 1954–2011 · Donalda Mines Ltd, Mag Copper Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3024,23 +3020,23 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="U31" t="n">
         <v>50</v>
       </c>
       <c r="V31" t="n">
-        <v>48.24757</v>
+        <v>46.2376</v>
       </c>
       <c r="W31" t="n">
-        <v>-89.8866</v>
+        <v>-82.12882</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00023</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3046,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nordic Mine</t>
+          <t>Quirke No. 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MDI41J07NE00009</t>
+          <t>MDI41J10SE00007</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3064,7 +3060,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9</v>
+        <v>16</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3073,7 +3069,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Uranium, Thorium, Yttrium</t>
+          <t>Uranium, Rare Earth Elements, Thorium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3095,7 +3091,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
+          <t>39 drill hole(s) nearby · 1953–1954 · Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3115,14 +3111,14 @@
         <v>50</v>
       </c>
       <c r="V32" t="n">
-        <v>46.37802</v>
+        <v>46.51253</v>
       </c>
       <c r="W32" t="n">
-        <v>-82.58893</v>
+        <v>-82.64662</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00009</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J10SE00007</t>
         </is>
       </c>
     </row>
@@ -3132,30 +3128,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moneta Mine</t>
+          <t>Buckles Mine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MDI42A06NW00003</t>
+          <t>MDI41J07NE00004</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Schumacher</t>
+          <t>Nordic Townsite</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Uranium, Copper</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3177,7 +3173,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>The average grade of the ore in leucoxene andesite was approximately 0.60 oz/t and the average in the pillowed metavolcanics was 0.30 oz/t.</t>
+          <t>22 drill hole(s) nearby · 1953–1954 · Geneva Lake Mines Ltd, Algom Uranium Mines Ltd</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3197,14 +3193,14 @@
         <v>50</v>
       </c>
       <c r="V33" t="n">
-        <v>48.47006</v>
+        <v>46.37605</v>
       </c>
       <c r="W33" t="n">
-        <v>-81.32491</v>
+        <v>-82.58892</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A06NW00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J07NE00004</t>
         </is>
       </c>
     </row>
@@ -3214,30 +3210,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Contact Bay</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI000000000779</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3259,7 +3255,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, Rio Canadian Expl Ltd/Knight-Adair</t>
+          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3270,23 +3266,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="U34" t="n">
         <v>50</v>
       </c>
       <c r="V34" t="n">
-        <v>44.72488</v>
+        <v>49.69695</v>
       </c>
       <c r="W34" t="n">
-        <v>-78.80319</v>
+        <v>-92.82165999999999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
         </is>
       </c>
     </row>
@@ -3296,30 +3292,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Contact Bay</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MDI000000000779</t>
+          <t>MDI52A10NE00008</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Pearl</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Lead, Silver, Uranium, Zinc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3341,7 +3337,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 2025–2026 · Heritage Mining Ltd</t>
+          <t>13 drill hole(s) nearby · 1990 · K Kukkee, Thurston Stone</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -3352,23 +3348,23 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T35" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U35" t="n">
         <v>50</v>
       </c>
       <c r="V35" t="n">
-        <v>49.69695</v>
+        <v>48.67856</v>
       </c>
       <c r="W35" t="n">
-        <v>-92.82165999999999</v>
+        <v>-88.62576</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI000000000779</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A10NE00008</t>
         </is>
       </c>
     </row>
@@ -3378,21 +3374,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Addington Mine</t>
+          <t>Crystal-Comstock Property</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MDI31C11NE00010</t>
+          <t>MDI41I15SE00006</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Flinton Corner</t>
+          <t>Cryderman Subdivision</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3401,7 +3397,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Tungsten</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3423,7 +3419,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3 drill hole(s) nearby · 1983–1984 · R C Longmuir, C Longmuir/ C. Roger Young</t>
+          <t>2 drill hole(s) nearby · 1999–2002 · Flag Resources (1985) Ltd</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -3434,23 +3430,23 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="U36" t="n">
         <v>50</v>
       </c>
       <c r="V36" t="n">
-        <v>44.71386</v>
+        <v>46.75321</v>
       </c>
       <c r="W36" t="n">
-        <v>-77.18101</v>
+        <v>-80.62255</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11NE00010</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I15SE00006</t>
         </is>
       </c>
     </row>
@@ -3460,39 +3456,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kell Claims</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41P10SE00002</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Gowganda</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5</v>
+        <v>18.4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3505,7 +3501,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>A bulk sample of 253 pounds assayed 1703.8 oz/t Ag and yielded 180 lbs Co. A drill hole completed by Ourgold Mining Company returned 1.11% Cu, 0.56 oz/t Ag and 0.07% Co over 15 feet; 5.3% Cu, 1.2 oz/t Ag and 0.9% Co over 11.8 feet; and 25 feet averaging 2.23% Cu and 1.18 oz/t Ag.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -3516,23 +3512,23 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U37" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V37" t="n">
-        <v>44.63956</v>
+        <v>47.50538</v>
       </c>
       <c r="W37" t="n">
-        <v>-77.55477999999999</v>
+        <v>-80.64733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P10SE00002</t>
         </is>
       </c>
     </row>
@@ -3542,39 +3538,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Silver Mountain West</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI52A04NW00003</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3587,7 +3583,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd · tested Silver</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -3598,23 +3594,23 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U38" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V38" t="n">
-        <v>46.29559</v>
+        <v>48.24757</v>
       </c>
       <c r="W38" t="n">
-        <v>-83.20277</v>
+        <v>-89.8866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00003</t>
         </is>
       </c>
     </row>
@@ -3624,42 +3620,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bousquet</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41I04NE00004</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>McGregor Bay</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
         <v>1</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3669,7 +3665,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1979 · Curtin Mines Ltd</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -3678,25 +3674,29 @@
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>abuts Killarney Lakelands And Headwaters Provincial Park (Natural Environment Class) boundary</t>
+        </is>
+      </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U39" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V39" t="n">
-        <v>46.30402</v>
+        <v>46.14902</v>
       </c>
       <c r="W39" t="n">
-        <v>-81.53989</v>
+        <v>-81.62088</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I04NE00004</t>
         </is>
       </c>
     </row>
@@ -3706,30 +3706,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3751,7 +3751,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -3762,23 +3762,23 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T40" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U40" t="n">
         <v>48</v>
       </c>
       <c r="V40" t="n">
-        <v>44.55883</v>
+        <v>44.63956</v>
       </c>
       <c r="W40" t="n">
-        <v>-76.57349000000001</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -3788,30 +3788,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3833,7 +3833,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -3844,23 +3844,23 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T41" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U41" t="n">
         <v>48</v>
       </c>
       <c r="V41" t="n">
-        <v>44.73856</v>
+        <v>46.30402</v>
       </c>
       <c r="W41" t="n">
-        <v>-76.32056</v>
+        <v>-81.53989</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -3870,30 +3870,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3915,7 +3915,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -3926,23 +3926,23 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T42" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U42" t="n">
         <v>48</v>
       </c>
       <c r="V42" t="n">
-        <v>44.47438</v>
+        <v>46.29559</v>
       </c>
       <c r="W42" t="n">
-        <v>-76.51861</v>
+        <v>-83.20277</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -3952,21 +3952,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3997,7 +3997,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4008,23 +4008,23 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T43" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U43" t="n">
         <v>48</v>
       </c>
       <c r="V43" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W43" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -4034,35 +4034,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I44" t="b">
@@ -4079,7 +4079,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -4090,23 +4090,23 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U44" t="n">
         <v>48</v>
       </c>
       <c r="V44" t="n">
-        <v>48.69799</v>
+        <v>44.55883</v>
       </c>
       <c r="W44" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -4116,39 +4116,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>McManus Group</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MDI41P09NW00043</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cobalt, Copper, Nickel, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -4158,14 +4158,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Ag 171g/t</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>A 90 pound sample submitted in 1956 assayed: Cu-trace, Ni - 23.4%, Co - 4.45%, Fe - 1.35%, As-37.62%, S-2.52%, Ag-trace.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -4176,23 +4172,23 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="T45" t="n">
-        <v>50</v>
+        <v>325</v>
       </c>
       <c r="U45" t="n">
         <v>48</v>
       </c>
       <c r="V45" t="n">
-        <v>47.72286</v>
+        <v>44.62168</v>
       </c>
       <c r="W45" t="n">
-        <v>-80.28064000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -4202,39 +4198,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rock Lake</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MDI41J05NE00002</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ophir</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -4247,7 +4243,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -4258,23 +4254,23 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T46" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U46" t="n">
         <v>48</v>
       </c>
       <c r="V46" t="n">
-        <v>46.44114</v>
+        <v>44.47438</v>
       </c>
       <c r="W46" t="n">
-        <v>-83.73430999999999</v>
+        <v>-76.51861</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -4284,30 +4280,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bridget Lake Occurrence</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MDI41N15NW00007</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Michipicoten River</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4316,10 +4312,10 @@
         </is>
       </c>
       <c r="I47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4329,7 +4325,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -4338,29 +4334,25 @@
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U47" t="n">
         <v>48</v>
       </c>
       <c r="V47" t="n">
-        <v>47.8998</v>
+        <v>48.69799</v>
       </c>
       <c r="W47" t="n">
-        <v>-84.85621</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -4370,35 +4362,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tashota-Nipigon</t>
+          <t>Rock Lake</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MDI42L04SE00005</t>
+          <t>MDI41J05NE00002</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Auden</t>
+          <t>Ophir</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>29.3</v>
+        <v>2.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gold, Bismuth, Copper, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I48" t="b">
@@ -4415,7 +4407,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
+          <t>Drilling in the vicinity of the old workings obtained copper values ranging from 0.11 to 0.51% Cu, traces Au and Ag, over core lengths ranging from 5 to 45 feet. Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 1 Quartz Economic Gangue 2 Carbonate Economic Gangue 3 Pyrite Economic Gangue 4 Specularite Economic Gangue 5 Ankerite Economic Gangue Mineral Record Details Site Visit Information Date: Aug 10, 1999 Geologist: G Bennett Notes: Drilling i</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -4426,23 +4418,23 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="U48" t="n">
         <v>48</v>
       </c>
       <c r="V48" t="n">
-        <v>50.04735</v>
+        <v>46.44114</v>
       </c>
       <c r="W48" t="n">
-        <v>-87.58936</v>
+        <v>-83.73430999999999</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J05NE00002</t>
         </is>
       </c>
     </row>
@@ -4452,42 +4444,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jardun Mine - No 3 Zone</t>
+          <t>Bridget Lake Occurrence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MDI41K09NE00090</t>
+          <t>MDI41N15NW00007</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Northland</t>
+          <t>Michipicoten River</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver, Zinc, Gold</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I49" t="b">
         <v>0</v>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4497,7 +4489,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>137 drill hole(s) nearby · 1951–1984 · Longbow Exploration Inc/Watson Lake Mines Ltd, Jardun Mines Ltd · tested Copper, Lead, Silver, Zinc, Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Gold Economic Ore 1 Pyrite Economic Gangue 2 Galena Economic Gangue 3 Chalcopyrite Economic Gangue 4 Sphalerite Economic Gangue 5 Arsenopyrite Economic Gangue Chlorite Alteration Chloritic 1 Weak Replacement Mineralization Comments Dec 07, 2005 (A Wilson) - The H vein averaged 0.459 oz/t Au over the 156 feet of the length of the adit. Other sections of the vein averaged 0.852 oz/t Au over 81 feet. The average grade of samp</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -4506,7 +4498,11 @@
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>abuts South Michipicoten River-Superior Shoreline Conservation Reserve boundary</t>
+        </is>
+      </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
@@ -4517,14 +4513,14 @@
         <v>48</v>
       </c>
       <c r="V49" t="n">
-        <v>46.63751</v>
+        <v>47.8998</v>
       </c>
       <c r="W49" t="n">
-        <v>-84.14293000000001</v>
+        <v>-84.85621</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K09NE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41N15NW00007</t>
         </is>
       </c>
     </row>
@@ -4534,39 +4530,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Tashota-Nipigon</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI42L04SE00005</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Auden</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9</v>
+        <v>29.3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Bismuth, Copper, Silver</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -4579,7 +4575,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1983 · Tashota Nipigon Mines Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -4590,23 +4586,23 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U50" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="V50" t="n">
-        <v>45.58868</v>
+        <v>50.04735</v>
       </c>
       <c r="W50" t="n">
-        <v>-79.70944</v>
+        <v>-87.58936</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42L04SE00005</t>
         </is>
       </c>
     </row>
@@ -4616,12 +4612,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gatling Five Acre</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MDI31C12SE00028</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4630,7 +4626,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4661,7 +4657,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -4678,17 +4674,17 @@
         <v>200</v>
       </c>
       <c r="U51" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>44.51496</v>
+        <v>44.51686</v>
       </c>
       <c r="W51" t="n">
-        <v>-77.62126000000001</v>
+        <v>-77.62098</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -4698,35 +4694,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>McManus Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41P09NW00043</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Cobalt, Copper, Nickel, Silver</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I52" t="b">
@@ -4740,10 +4736,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Ag 171g/t</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>A 90 pound sample submitted in 1956 assayed: Cu-trace, Ni - 23.4%, Co - 4.45%, Fe - 1.35%, As-37.62%, S-2.52%, Ag-trace.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -4754,23 +4754,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="V52" t="n">
-        <v>49.71016</v>
+        <v>47.72286</v>
       </c>
       <c r="W52" t="n">
-        <v>-94.40097</v>
+        <v>-80.28064000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41P09NW00043</t>
         </is>
       </c>
     </row>
@@ -4780,39 +4780,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -4825,7 +4825,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4836,23 +4836,23 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T53" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U53" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="V53" t="n">
-        <v>44.5143</v>
+        <v>45.58868</v>
       </c>
       <c r="W53" t="n">
-        <v>-77.61444</v>
+        <v>-79.70944</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -4862,21 +4862,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
+          <t>Gatling Five Acre</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00028</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Deloro</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>MDI31C12SE00039</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
       <c r="E54" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I54" t="b">
@@ -4907,7 +4907,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper, Gold</t>
+          <t>11 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -4918,23 +4918,23 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U54" t="n">
         <v>41</v>
       </c>
       <c r="V54" t="n">
-        <v>44.51231</v>
+        <v>44.51496</v>
       </c>
       <c r="W54" t="n">
-        <v>-77.62011</v>
+        <v>-77.62126000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00028</t>
         </is>
       </c>
     </row>
@@ -4944,35 +4944,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MDI52H09NE00021</t>
+          <t>MDI31C12SE00039</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Poplar Lodge</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>0.3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Molybdenum, Copper, Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I55" t="b">
@@ -4986,14 +4986,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Mo 2.00%</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Nortoba Mines · tested Gold</t>
+          <t>15 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5004,23 +5000,23 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T55" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U55" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V55" t="n">
-        <v>49.69198</v>
+        <v>44.51231</v>
       </c>
       <c r="W55" t="n">
-        <v>-88.04716999999999</v>
+        <v>-77.62011</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00039</t>
         </is>
       </c>
     </row>
@@ -5030,30 +5026,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Springer-Lavergne Rare Earth Project</t>
+          <t>Nortoba-Tyson Prospect (No. 3 Vein)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MDI31L05NW00002</t>
+          <t>MDI52H09NE00021</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Crystal Falls</t>
+          <t>Poplar Lodge</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rare earths</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
+          <t>Molybdenum, Copper, Gold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5072,10 +5068,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Mo 2.00%</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
+          <t>64 drill hole(s) nearby · 1958–2008 · Candore Expl Ltd, Nortoba Mines · tested Gold</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -5092,17 +5092,17 @@
         <v>25</v>
       </c>
       <c r="U56" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="V56" t="n">
-        <v>46.44231</v>
+        <v>49.69198</v>
       </c>
       <c r="W56" t="n">
-        <v>-79.94853999999999</v>
+        <v>-88.04716999999999</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52H09NE00021</t>
         </is>
       </c>
     </row>
@@ -5112,35 +5112,35 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Empire B Zone</t>
+          <t>Kam Kotia Mine</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDI31D16NE00146</t>
+          <t>MDI42A12SE00005</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>South Wilberforce</t>
+          <t>Kamiskotia</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Uranium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Uranium, Yttrium, Fluorite, Thorium</t>
+          <t>Copper, Zinc, Gold, Silver</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I57" t="b">
@@ -5154,10 +5154,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Cu 1.10%, Zn 1.17%</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
+          <t>8 drill hole(s) nearby · 1954–1993 · Falconbridge Ltd, Pleno Mines Ltd</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -5174,17 +5178,17 @@
         <v>25</v>
       </c>
       <c r="U57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="V57" t="n">
-        <v>44.99427</v>
+        <v>48.59125</v>
       </c>
       <c r="W57" t="n">
-        <v>-78.19589999999999</v>
+        <v>-81.60500999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A12SE00005</t>
         </is>
       </c>
     </row>
@@ -5194,30 +5198,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bannockburn Gold Project</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MDI31C12NE00195</t>
+          <t>MDI42A09SW00163</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Holtyre</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
+          <t>Copper, Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5239,7 +5243,7 @@
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
+          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons  · tested Gold</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -5250,23 +5254,23 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="U58" t="n">
         <v>32</v>
       </c>
       <c r="V58" t="n">
-        <v>44.64988</v>
+        <v>48.50619</v>
       </c>
       <c r="W58" t="n">
-        <v>-77.54698</v>
+        <v>-80.31543000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
         </is>
       </c>
     </row>
@@ -5276,30 +5280,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abbican</t>
+          <t>Springer-Lavergne Rare Earth Project</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MDI41J06NE00044</t>
+          <t>MDI31L05NW00002</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Crystal Falls</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10.3</v>
+        <v>5.1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rare earths</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Cerium, Gallium, Lanthanum, Neodymium, Rare Earth Elements, Yttrium, Thorium</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5311,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5321,7 +5325,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Bastnaesite Economic Ore 2 Chalcopyrite Economic Ore 3 Pyrite Economic Ore 4 Fluorite Economic Ore 5 Hematite Economic Ore Mineralization Comments Nov 15, 2011 (A Wilson) - Partial results from Rare Earth Metals original 4 hole drill program included 0.98% REO over 112.7 m which included a higher-grade section of 1.22% REO over 63.3 m (DDH-L-69-1). DDH-L-69-4, completed 180 m north of DDH-L-69-1 intersected two separate mi</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -5330,11 +5334,7 @@
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
         <v>1</v>
       </c>
@@ -5345,14 +5345,14 @@
         <v>32</v>
       </c>
       <c r="V59" t="n">
-        <v>46.47973</v>
+        <v>46.44231</v>
       </c>
       <c r="W59" t="n">
-        <v>-83.15055</v>
+        <v>-79.94853999999999</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31L05NW00002</t>
         </is>
       </c>
     </row>
@@ -5362,21 +5362,21 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Macassa</t>
+          <t>Lakemount Property</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MDI31C13SE00099</t>
+          <t>MDI42C02SE00090</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ormsby</t>
+          <t>Hawk Junction</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
+          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5407,7 +5407,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
+          <t>98 drill hole(s) nearby · 1952–1982 · Firespur Expl Ltd, Kelore Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -5418,23 +5418,23 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="U60" t="n">
         <v>32</v>
       </c>
       <c r="V60" t="n">
-        <v>44.868</v>
+        <v>48.06318</v>
       </c>
       <c r="W60" t="n">
-        <v>-77.72254</v>
+        <v>-84.62636999999999</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
         </is>
       </c>
     </row>
@@ -5444,30 +5444,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Band-Ore Mattagami Zone 4</t>
+          <t>Abbican</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MDI52B09SE00024</t>
+          <t>MDI41J06NE00044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Shebandowan</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.2</v>
+        <v>10.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
+          <t>30 drill hole(s) nearby · 1955–1968 · Abbican Mines Ltd, Milgate Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -5498,7 +5498,11 @@
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>abuts Little White River Provincial Park (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
@@ -5509,14 +5513,14 @@
         <v>32</v>
       </c>
       <c r="V61" t="n">
-        <v>48.62462</v>
+        <v>46.47973</v>
       </c>
       <c r="W61" t="n">
-        <v>-90.12229000000001</v>
+        <v>-83.15055</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00044</t>
         </is>
       </c>
     </row>
@@ -5526,30 +5530,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Scramble Mine</t>
+          <t>Empire B Zone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MDI52E16SW00091</t>
+          <t>MDI31D16NE00146</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Pelletier Bridge</t>
+          <t>South Wilberforce</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Uranium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Uranium, Yttrium, Fluorite, Thorium</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5571,7 +5575,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Uranothorite Economic Ore 2 Uraninite Economic Ore 3 Zircon Economic Ore 4 Allanite Economic Ore 5 Thorite Economic Ore 6 Molybdenite Economic Ore 7 Fluorite Economic Ore Mineralization Comments Jan 26, 2017 (A Wilson) - Assays from drilling returned values ranging from 0.035% U3O8 over 4 ft. to 0.489% U3O8 over 1.25 ft. Ytrrium assays ranged from 201 ppm to 1459 ppm.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -5591,14 +5595,14 @@
         <v>32</v>
       </c>
       <c r="V62" t="n">
-        <v>49.78399</v>
+        <v>44.99427</v>
       </c>
       <c r="W62" t="n">
-        <v>-94.37701</v>
+        <v>-78.19589999999999</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NE00146</t>
         </is>
       </c>
     </row>
@@ -5608,21 +5612,21 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Simon Copper Property</t>
+          <t>Macassa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MDI31F03NW00044</t>
+          <t>MDI31C13SE00099</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Slate Falls</t>
+          <t>Ormsby</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Iron, Selenium</t>
+          <t>Copper, Nickel, Cobalt, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5653,7 +5657,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
+          <t>6 drill hole(s) nearby · 1961–2004 · Macassa Gold Mines Ltd, Limerick Mines Ltd · tested Copper, Nickel</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -5664,23 +5668,23 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T63" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="U63" t="n">
         <v>32</v>
       </c>
       <c r="V63" t="n">
-        <v>45.20807</v>
+        <v>44.868</v>
       </c>
       <c r="W63" t="n">
-        <v>-77.31331</v>
+        <v>-77.72254</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C13SE00099</t>
         </is>
       </c>
     </row>
@@ -5690,30 +5694,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hermina</t>
+          <t>Band-Ore Mattagami Zone 4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MDI41J01NE00007</t>
+          <t>MDI52B09SE00024</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Shebandowan</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Copper, Silver, Zinc</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5735,7 +5739,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
+          <t>33 drill hole(s) nearby · 1981–2022 · Mattagami Lake Expl Ltd, E2 Gold Inc · tested Gold</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -5746,23 +5750,23 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U64" t="n">
         <v>32</v>
       </c>
       <c r="V64" t="n">
-        <v>46.23918</v>
+        <v>48.62462</v>
       </c>
       <c r="W64" t="n">
-        <v>-82.15586</v>
+        <v>-90.12229000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52B09SE00024</t>
         </is>
       </c>
     </row>
@@ -5772,21 +5776,21 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shoot Zone Deposit</t>
+          <t>Bannockburn Gold Project</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MDI42A10SE00065</t>
+          <t>MDI31C12NE00195</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5795,7 +5799,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold, Copper</t>
+          <t>Gold, Silver, Arsenic, Bismuth, Copper, Tellurium, Zinc</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5817,7 +5821,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
+          <t>100 drill hole(s) nearby · 1985–1987 · Mono Gold Mines Inc · tested Gold, Silver</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -5828,23 +5832,23 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T65" t="n">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="U65" t="n">
         <v>32</v>
       </c>
       <c r="V65" t="n">
-        <v>48.56426</v>
+        <v>44.64988</v>
       </c>
       <c r="W65" t="n">
-        <v>-80.63866</v>
+        <v>-77.54698</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00195</t>
         </is>
       </c>
     </row>
@@ -5854,21 +5858,21 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scadding Gold Property</t>
+          <t>Scramble Mine</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MDI41I10NE00012</t>
+          <t>MDI52E16SW00091</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Basin Mines</t>
+          <t>Pelletier Bridge</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Palladium, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5899,7 +5903,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
+          <t>6 drill hole(s) nearby · 1985–1988 · Scramble Mining Ltd, Boise Cascade Canada Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -5919,14 +5923,14 @@
         <v>32</v>
       </c>
       <c r="V66" t="n">
-        <v>46.65087</v>
+        <v>49.78399</v>
       </c>
       <c r="W66" t="n">
-        <v>-80.61375</v>
+        <v>-94.37701</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E16SW00091</t>
         </is>
       </c>
     </row>
@@ -5936,30 +5940,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Geneva Lake Mine</t>
+          <t>Simon Copper Property</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MDI41I13SE00002</t>
+          <t>MDI31F03NW00044</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Slate Falls</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
+          <t>Copper, Zinc, Iron, Selenium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5981,7 +5985,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
+          <t>49 drill hole(s) nearby · 1956–2008 · Noranda Exploration Co Ltd, Malcolm Property · tested Copper, Zinc, Gold, Nickel</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -6001,14 +6005,14 @@
         <v>32</v>
       </c>
       <c r="V67" t="n">
-        <v>46.7905</v>
+        <v>45.20807</v>
       </c>
       <c r="W67" t="n">
-        <v>-81.51521</v>
+        <v>-77.31331</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F03NW00044</t>
         </is>
       </c>
     </row>
@@ -6018,30 +6022,30 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Shoot Zone Deposit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MDI42A09SW00163</t>
+          <t>MDI42A10SE00065</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Holtyre</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Copper, Gold, Molybdenum, Silver</t>
+          <t>Gold, Copper</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6063,7 +6067,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>91 drill hole(s) nearby · 1946–2021 · Armco-Geddes Resc Ltd, G E Parsons  · tested Gold</t>
+          <t>25 drill hole(s) nearby · 1984–2016 · St Andrew Goldfields Ltd, Hollinger Argus Ltd · tested Gold</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -6074,23 +6078,23 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U68" t="n">
         <v>32</v>
       </c>
       <c r="V68" t="n">
-        <v>48.50619</v>
+        <v>48.56426</v>
       </c>
       <c r="W68" t="n">
-        <v>-80.31543000000001</v>
+        <v>-80.63866</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A09SW00163</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42A10SE00065</t>
         </is>
       </c>
     </row>
@@ -6100,30 +6104,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lakemount Property</t>
+          <t>Scadding Gold Property</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MDI42C02SE00090</t>
+          <t>MDI41I10NE00012</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hawk Junction</t>
+          <t>Basin Mines</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Copper, Nickel, Platinum, Gold, Palladium</t>
+          <t>Gold, Palladium, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6145,7 +6149,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>98 drill hole(s) nearby · 1952–1982 · Firespur Expl Ltd, Kelore Mines Ltd · tested Copper, Nickel</t>
+          <t>375 drill hole(s) nearby · 1970–2025 · Macdonald Mines Exploration Ltd, Currie Rose Resc Inc · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -6165,14 +6169,14 @@
         <v>32</v>
       </c>
       <c r="V69" t="n">
-        <v>48.06318</v>
+        <v>46.65087</v>
       </c>
       <c r="W69" t="n">
-        <v>-84.62636999999999</v>
+        <v>-80.61375</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42C02SE00090</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10NE00012</t>
         </is>
       </c>
     </row>
@@ -6182,30 +6186,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Reserve Creek Occurrences</t>
+          <t>Hermina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MDI42M12SE00008</t>
+          <t>MDI41J01NE00007</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Eabametoong First Nation</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>12</v>
+        <v>6.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6224,14 +6228,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Mo 0.45%</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Pricemore Resources Inc · tested Gold</t>
+          <t>8 drill hole(s) nearby · 1967–2005 · J Gutcher, G H Babcock</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -6242,23 +6242,23 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V70" t="n">
-        <v>51.57743</v>
+        <v>46.23918</v>
       </c>
       <c r="W70" t="n">
-        <v>-87.73681999999999</v>
+        <v>-82.15586</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00007</t>
         </is>
       </c>
     </row>
@@ -6268,30 +6268,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eagle Copper Mine</t>
+          <t>Methuen Township Ilmenite</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MDI41K16SW00002</t>
+          <t>MDI31C12NW00114</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bourdages Corner</t>
+          <t>Oak Lake</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Titanium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Lead, Silver</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6310,14 +6310,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Cu 1.15%</t>
-        </is>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
+          <t>62 drill hole(s) nearby · 1969–2008 · Canadian Nickel Co Ltd, M R Tripp</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -6328,23 +6324,23 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U71" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V71" t="n">
-        <v>46.75901</v>
+        <v>44.62955</v>
       </c>
       <c r="W71" t="n">
-        <v>-84.26090000000001</v>
+        <v>-77.87374</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NW00114</t>
         </is>
       </c>
     </row>
@@ -6354,30 +6350,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Northern Kyanite</t>
+          <t>Geneva Lake Mine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MDI41I10SE00004</t>
+          <t>MDI41I13SE00002</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wahnapitae</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
+          <t>Lead, Silver, Zinc, Copper, Gold, Uranium</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6399,7 +6395,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Galena Economic Ore 4 Sphalerite Economic Ore 6 Chalcopyrite Economic Ore 2 Pyrite Economic Gangue 3 Arsenopyrite Economic Gangue 5 Magnetite Economic Gangue Mineralization Comments May 25, 2010 (A Wilson) - An assay from Towgamac's drill hole No-11 returned 5.48%Pb, 16.35% Zn, 1.06 oz/t Ag, $0.40 gold over 4.5 feet.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -6410,23 +6406,23 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="U72" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="V72" t="n">
-        <v>46.50103</v>
+        <v>46.7905</v>
       </c>
       <c r="W72" t="n">
-        <v>-80.73585</v>
+        <v>-81.51521</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I13SE00002</t>
         </is>
       </c>
     </row>
@@ -6436,30 +6432,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stanleyville Vermiculite</t>
+          <t>Reserve Creek Occurrences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MDI31C16SW00030</t>
+          <t>MDI42M12SE00008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Eabametoong First Nation</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Vermiculite</t>
+          <t>Gold, Copper, Molybdenum, Silver, Tungsten</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6478,10 +6474,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Mo 0.45%</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+          <t>136 drill hole(s) nearby · 1942–2011 · Lun-Echo Gold Mines Ltd, Pricemore Resources Inc · tested Gold</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -6492,23 +6492,23 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="U73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V73" t="n">
-        <v>44.79726</v>
+        <v>51.57743</v>
       </c>
       <c r="W73" t="n">
-        <v>-76.32017999999999</v>
+        <v>-87.73681999999999</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI42M12SE00008</t>
         </is>
       </c>
     </row>
@@ -6518,30 +6518,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jayfran-Pipawa</t>
+          <t>Eagle Copper Mine</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MDI31F04SE00036</t>
+          <t>MDI41K16SW00002</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Vardy</t>
+          <t>Bourdages Corner</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nepheline Syenite, Uranium</t>
+          <t>Copper, Lead, Silver</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6553,17 +6553,21 @@
         <v>0</v>
       </c>
       <c r="J74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Cu 1.15%</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
+          <t>Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 1 Chalcopyrite Economic Ore 2 Galena Economic Ore 1 Pyrite Economic Gangue 2 Magnetite Economic Gangue 3 Graphite Economic Gangue 4 Carbonate Economic Gangue 5 Pyrrhotite Economic Gangue 6 Quartz Economic Gangue Mineralization Comments Jun 23, 2011 (A Pace) - The mineralization was observed in coarse grained andesite units but drill core from the Airnorth drilling program indicated several weakly mineralized zones in 0.4% Cu</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
@@ -6572,29 +6576,25 @@
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U74" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V74" t="n">
-        <v>45.09484</v>
+        <v>46.75901</v>
       </c>
       <c r="W74" t="n">
-        <v>-77.76734999999999</v>
+        <v>-84.26090000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41K16SW00002</t>
         </is>
       </c>
     </row>
@@ -6604,21 +6604,21 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>95-2</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MDI31M12SW00017</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Diamond, Kimberlite</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Pipawa Expl Ltd, Jayfran Enterprises Ltd</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -6658,25 +6658,361 @@
       </c>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T75" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="U75" t="n">
         <v>27</v>
       </c>
       <c r="V75" t="n">
+        <v>45.09484</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-77.76734999999999</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Northern Kyanite</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MDI41I10SE00004</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Wahnapitae</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Kyanite (Nonmetals), Garnet (Nonmetals), Sillimanite</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>10 drill hole(s) nearby · 1953–1955 · Hoyle Mining Company</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="n">
+        <v>50</v>
+      </c>
+      <c r="U76" t="n">
+        <v>27</v>
+      </c>
+      <c r="V76" t="n">
+        <v>46.50103</v>
+      </c>
+      <c r="W76" t="n">
+        <v>-80.73585</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I10SE00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Stanleyville Vermiculite</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MDI31C16SW00030</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Stanleyville</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Vermiculite</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Comments Sep 11, 2015 (A Wilson) - Drill results concluded that this deposit could support a 270 tonnes (300ton)/day operation for 10 years, with the mill-feed grading 20% vermiculite.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>100</v>
+      </c>
+      <c r="U77" t="n">
+        <v>27</v>
+      </c>
+      <c r="V77" t="n">
+        <v>44.79726</v>
+      </c>
+      <c r="W77" t="n">
+        <v>-76.32017999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SW00030</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>95-2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MDI31M12SW00017</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Hudson</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Diamond, Kimberlite</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>29 drill hole(s) nearby · 1995–2005 · Sudbury Contact Mines Ltd, Contact Diamond Corp</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>25</v>
+      </c>
+      <c r="U78" t="n">
+        <v>27</v>
+      </c>
+      <c r="V78" t="n">
         <v>47.52342</v>
       </c>
-      <c r="W75" t="n">
+      <c r="W78" t="n">
         <v>-79.89148</v>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31M12SW00017</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>West Graham</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MDI41I06NW00072</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Crean Hill</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Copper, Nickel, Cobalt, Gold, Palladium, Platinum, Silver</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Ni 0.30%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1961 · Mcvittie-Graham Mining Co Ltd · tested Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>25</v>
+      </c>
+      <c r="U79" t="n">
+        <v>22</v>
+      </c>
+      <c r="V79" t="n">
+        <v>46.43504</v>
+      </c>
+      <c r="W79" t="n">
+        <v>-81.30689</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I06NW00072</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,10 +698,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +716,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V3" t="n">
-        <v>45.30338</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.90682</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -783,7 +787,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -803,14 +807,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>45.29002</v>
+        <v>48.24876</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.94167</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -885,14 +889,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.85917</v>
+        <v>45.28947</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.15956</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -902,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -925,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>44.85917</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1049,14 +1053,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.21442</v>
+        <v>45.30338</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.8742</v>
+        <v>-76.90682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1066,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.49976</v>
+        <v>45.29002</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.94167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1148,30 +1152,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T9" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U9" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.5021</v>
+        <v>44.55104</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.61301</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.52895</v>
+        <v>45.21442</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.78169</v>
+        <v>-77.8742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1394,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>44.63956</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.55477999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>46.30402</v>
+        <v>44.51686</v>
       </c>
       <c r="W13" t="n">
-        <v>-81.53989</v>
+        <v>-77.62098</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1600,10 +1604,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="V14" t="n">
-        <v>46.29559</v>
+        <v>44.99932</v>
       </c>
       <c r="W14" t="n">
-        <v>-83.20277</v>
+        <v>-78.32907</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1648,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>44.73856</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.32056</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1730,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1784,17 +1792,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>44.55883</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.57349000000001</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1804,30 +1812,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1849,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1869,14 +1877,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.62168</v>
+        <v>44.63956</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.56963</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1886,30 +1894,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1931,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1942,23 +1950,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.47438</v>
+        <v>46.29559</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.51861</v>
+        <v>-83.20277</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1968,21 +1976,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1991,12 +1999,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2013,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2033,14 +2041,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>48.69799</v>
+        <v>46.30402</v>
       </c>
       <c r="W19" t="n">
-        <v>-93.27513999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2050,30 +2058,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2095,7 +2103,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2112,15 +2120,425 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
+        <v>48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>44.55883</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-76.57349000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timmins Mine</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MDI31C09NW00013</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stanleyville</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>11</v>
+      </c>
+      <c r="T21" t="n">
+        <v>275</v>
+      </c>
+      <c r="U21" t="n">
+        <v>48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>44.73856</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-76.32056</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Frontenac</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MDI31C07NE00036</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Perth Road</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lead, Gold, Silver, Zinc</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>44.47438</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-76.51861</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Meadow Lake Zone</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MDI31C10SE00205</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bedford</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
+        <v>48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>44.62168</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-76.56963</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="n">
+        <v>300</v>
+      </c>
+      <c r="U24" t="n">
+        <v>48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
         <v>43</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V25" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W25" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>45.39062</v>
+        <v>44.55039</v>
       </c>
       <c r="W2" t="n">
-        <v>-76.70397</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,14 +698,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -716,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>45.30338</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-76.90682</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -742,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -787,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -807,14 +803,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>48.24876</v>
+        <v>45.29002</v>
       </c>
       <c r="W4" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -824,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +885,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.28947</v>
+        <v>44.85917</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -906,21 +902,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +925,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.85917</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.15956</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1049,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.30338</v>
+        <v>45.21442</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.90682</v>
+        <v>-77.8742</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.29002</v>
+        <v>44.49976</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94167</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1152,30 +1148,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55104</v>
+        <v>44.5021</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.61301</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V10" t="n">
-        <v>45.21442</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.8742</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1394,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1426,7 +1422,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>44.63956</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="V13" t="n">
-        <v>44.51686</v>
+        <v>46.30402</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.62098</v>
+        <v>-81.53989</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1558,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1604,14 +1600,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="V14" t="n">
-        <v>44.99932</v>
+        <v>46.29559</v>
       </c>
       <c r="W14" t="n">
-        <v>-78.32907</v>
+        <v>-83.20277</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1648,35 +1640,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1693,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.73856</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-76.32056</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1730,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1775,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1792,17 +1784,17 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>44.55883</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1804,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1857,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1877,14 +1869,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.63956</v>
+        <v>44.62168</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.56963</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1886,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1931,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,23 +1942,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>46.29559</v>
+        <v>44.47438</v>
       </c>
       <c r="W18" t="n">
-        <v>-83.20277</v>
+        <v>-76.51861</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -1976,21 +1968,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1999,12 +1991,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2021,7 +2013,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2041,14 +2033,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>46.30402</v>
+        <v>48.69799</v>
       </c>
       <c r="W19" t="n">
-        <v>-81.53989</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -2058,30 +2050,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2103,7 +2095,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2120,425 +2112,15 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V20" t="n">
-        <v>44.55883</v>
+        <v>45.58868</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.57349000000001</v>
+        <v>-79.70944</v>
       </c>
       <c r="X20" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Timmins Mine</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MDI31C09NW00013</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Stanleyville</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>275</v>
-      </c>
-      <c r="U21" t="n">
-        <v>48</v>
-      </c>
-      <c r="V21" t="n">
-        <v>44.73856</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-76.32056</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Frontenac</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MDI31C07NE00036</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Perth Road</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Lead, Gold, Silver, Zinc</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>44.47438</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-76.51861</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Meadow Lake Zone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MDI31C10SE00205</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bedford</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>44.62168</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-76.56963</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>12</v>
-      </c>
-      <c r="T24" t="n">
-        <v>300</v>
-      </c>
-      <c r="U24" t="n">
-        <v>48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>13</v>
-      </c>
-      <c r="T25" t="n">
-        <v>325</v>
-      </c>
-      <c r="U25" t="n">
-        <v>43</v>
-      </c>
-      <c r="V25" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X25" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -656,21 +656,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,10 +698,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mo 5.00%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -718,17 +722,17 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>45.30338</v>
+        <v>45.39062</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.90682</v>
+        <v>-76.70397</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -738,30 +742,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -780,10 +784,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +802,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V4" t="n">
-        <v>45.29002</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.94167</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -820,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.85917</v>
+        <v>44.49976</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.15956</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -902,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>45.29002</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -984,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1049,14 +1057,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.21442</v>
+        <v>45.28947</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.8742</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1066,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1130,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.49976</v>
+        <v>44.55104</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1148,30 +1156,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1212,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.5021</v>
+        <v>44.85917</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.61301</v>
+        <v>-76.15956</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1230,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>71.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1253,12 +1261,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.52895</v>
+        <v>54.51539</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.78169</v>
+        <v>-91.40791</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,12 +1343,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1394,21 +1402,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,12 +1425,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V12" t="n">
-        <v>44.63956</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.55477999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V13" t="n">
-        <v>46.30402</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-81.53989</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1640,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1705,14 +1713,14 @@
         <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.73856</v>
+        <v>44.63956</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.32056</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1804,30 +1812,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1849,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1869,14 +1877,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.62168</v>
+        <v>46.30402</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.56963</v>
+        <v>-81.53989</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1886,30 +1894,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1931,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1951,14 +1959,14 @@
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.47438</v>
+        <v>44.62168</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.51861</v>
+        <v>-76.56963</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1968,35 +1976,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2013,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2033,14 +2041,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>48.69799</v>
+        <v>44.47438</v>
       </c>
       <c r="W19" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.51861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2050,30 +2058,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2095,7 +2103,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2106,21 +2114,185 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
+        <v>11</v>
+      </c>
+      <c r="T20" t="n">
+        <v>275</v>
+      </c>
+      <c r="U20" t="n">
+        <v>48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>44.73856</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-76.32056</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>13</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>325</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
+        <v>48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
         <v>43</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V22" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W22" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -784,14 +784,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -802,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>48.24876</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -828,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.49976</v>
+        <v>45.21442</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.8742</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -910,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -955,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -975,14 +971,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.29002</v>
+        <v>45.30338</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94167</v>
+        <v>-76.90682</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -992,12 +988,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1006,7 +1002,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1037,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1057,14 +1053,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.28947</v>
+        <v>45.29002</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55104</v>
+        <v>44.49976</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1152,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U9" t="n">
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.85917</v>
+        <v>46.23809</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.15956</v>
+        <v>-82.11991</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1299,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>54.51539</v>
+        <v>45.28947</v>
       </c>
       <c r="W10" t="n">
-        <v>-91.40791</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>71.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1343,12 +1339,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>54.51539</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-91.40791</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1402,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1425,12 +1421,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>44.51686</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-77.62098</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1540,10 +1536,10 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>57</v>
@@ -1566,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1611,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>46.29559</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-83.20277</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
         <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1808,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1857,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1877,14 +1873,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>46.30402</v>
+        <v>44.62168</v>
       </c>
       <c r="W17" t="n">
-        <v>-81.53989</v>
+        <v>-76.56963</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1890,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1959,14 +1955,14 @@
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.62168</v>
+        <v>46.30402</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.56963</v>
+        <v>-81.53989</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1976,30 +1972,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2021,7 +2017,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2041,14 +2037,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.47438</v>
+        <v>44.63956</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.51861</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2058,30 +2054,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2103,7 +2099,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2114,23 +2110,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.73856</v>
+        <v>44.47438</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.32056</v>
+        <v>-76.51861</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2140,35 +2136,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2185,7 +2181,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2196,23 +2192,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U21" t="n">
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>48.69799</v>
+        <v>44.73856</v>
       </c>
       <c r="W21" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.32056</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2222,35 +2218,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2267,7 +2263,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2284,15 +2280,97 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
+        <v>48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
         <v>43</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -787,7 +787,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -807,14 +807,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>48.24876</v>
+        <v>44.85917</v>
       </c>
       <c r="W4" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +889,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.21442</v>
+        <v>45.30338</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.8742</v>
+        <v>-76.90682</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -971,14 +971,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.30338</v>
+        <v>45.29002</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.90682</v>
+        <v>-76.94167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.29002</v>
+        <v>45.28947</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.94167</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.49976</v>
+        <v>45.21442</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.8742</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U10" t="n">
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>45.28947</v>
+        <v>44.55104</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71.8</v>
+        <v>2.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1381,14 +1381,14 @@
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>54.51539</v>
+        <v>48.24876</v>
       </c>
       <c r="W11" t="n">
-        <v>-91.40791</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>71.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>44.51686</v>
+        <v>54.51539</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.62098</v>
+        <v>-91.40791</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>T. Horscroft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31D10NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Norland</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum, Iron, Uranium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>44.72488</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-78.80319</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1604,10 +1604,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>44.99932</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-78.32907</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1644,35 +1648,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>46.29559</v>
+        <v>44.5021</v>
       </c>
       <c r="W15" t="n">
-        <v>-83.20277</v>
+        <v>-77.61301</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1730,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1786,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>44.55883</v>
+        <v>44.5143</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.57349000000001</v>
+        <v>-77.61444</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1812,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1868,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>44.62168</v>
+        <v>44.52895</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.56963</v>
+        <v>-77.78169</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1890,35 +1894,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1950,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U18" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V18" t="n">
-        <v>46.30402</v>
+        <v>49.71016</v>
       </c>
       <c r="W18" t="n">
-        <v>-81.53989</v>
+        <v>-94.40097</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1972,30 +1976,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2017,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2037,14 +2041,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.63956</v>
+        <v>44.47438</v>
       </c>
       <c r="W19" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.51861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2054,30 +2058,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2099,7 +2103,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2119,14 +2123,14 @@
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.47438</v>
+        <v>44.63956</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.51861</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2136,30 +2140,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2181,7 +2185,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2192,23 +2196,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>44.73856</v>
+        <v>46.30402</v>
       </c>
       <c r="W21" t="n">
-        <v>-76.32056</v>
+        <v>-81.53989</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2218,21 +2222,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,12 +2245,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2263,7 +2267,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2274,23 +2278,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U22" t="n">
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>48.69799</v>
+        <v>46.29559</v>
       </c>
       <c r="W22" t="n">
-        <v>-93.27513999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -2300,30 +2304,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2345,7 +2349,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2356,21 +2360,267 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="n">
+        <v>250</v>
+      </c>
+      <c r="U23" t="n">
+        <v>48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>44.73856</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-76.32056</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kirkham Graphite Property</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MDI31C10SE00023</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Glendower</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>13</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>325</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
+        <v>48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>44.55883</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-76.57349000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Meadow Lake Zone</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MDI31C10SE00205</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bedford</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>13</v>
+      </c>
+      <c r="T25" t="n">
+        <v>325</v>
+      </c>
+      <c r="U25" t="n">
+        <v>48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>44.62168</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-76.56963</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
         <v>43</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,30 +742,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -784,10 +784,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +802,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V4" t="n">
-        <v>44.85917</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.15956</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -824,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +893,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.30338</v>
+        <v>44.85917</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.90682</v>
+        <v>-76.15956</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -906,12 +910,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -920,7 +924,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -951,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -971,14 +975,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.29002</v>
+        <v>45.28947</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94167</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -988,21 +992,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1033,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1057,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.28947</v>
+        <v>45.30338</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1139,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.21442</v>
+        <v>45.29002</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.8742</v>
+        <v>-76.94167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1261,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55104</v>
+        <v>45.21442</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.8742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>48.24876</v>
+        <v>44.55104</v>
       </c>
       <c r="W11" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1402,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71.8</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1463,14 +1467,14 @@
         <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>54.51539</v>
+        <v>48.24876</v>
       </c>
       <c r="W12" t="n">
-        <v>-91.40791</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1484,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T. Horscroft</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31D10NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Norland</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum, Iron, Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8 drill hole(s) nearby · 1955–1969 · Rio Can Expl Ltd/Adair Knight Option, R Adair</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>44.72488</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.80319</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D10NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1566,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.8</v>
+        <v>71.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1604,14 +1608,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1628,17 +1628,17 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V14" t="n">
-        <v>44.99932</v>
+        <v>54.51539</v>
       </c>
       <c r="W14" t="n">
-        <v>-78.32907</v>
+        <v>-91.40791</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1690,10 +1690,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1710,17 +1714,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V15" t="n">
-        <v>44.5021</v>
+        <v>44.99932</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61301</v>
+        <v>-78.32907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1734,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1744,7 +1748,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1753,7 +1757,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1775,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1786,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5143</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61444</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1868,10 +1872,10 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
         <v>57</v>
@@ -1894,35 +1898,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1939,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>49.71016</v>
+        <v>44.62168</v>
       </c>
       <c r="W18" t="n">
-        <v>-94.40097</v>
+        <v>-76.56963</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1976,30 +1980,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2021,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2041,14 +2045,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.47438</v>
+        <v>46.30402</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.51861</v>
+        <v>-81.53989</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2058,30 +2062,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2103,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2114,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -2140,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2185,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2196,23 +2200,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U21" t="n">
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W21" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2222,30 +2226,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2267,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2278,23 +2282,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U22" t="n">
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>46.29559</v>
+        <v>44.73856</v>
       </c>
       <c r="W22" t="n">
-        <v>-83.20277</v>
+        <v>-76.32056</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2304,21 +2308,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2349,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2360,23 +2364,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -2386,30 +2390,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2431,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2451,14 +2455,14 @@
         <v>48</v>
       </c>
       <c r="V24" t="n">
-        <v>44.55883</v>
+        <v>44.47438</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.51861</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2468,30 +2472,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2513,7 +2517,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2530,97 +2534,15 @@
         <v>325</v>
       </c>
       <c r="U25" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V25" t="n">
-        <v>44.62168</v>
+        <v>45.58868</v>
       </c>
       <c r="W25" t="n">
-        <v>-76.56963</v>
+        <v>-79.70944</v>
       </c>
       <c r="X25" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>43</v>
-      </c>
-      <c r="V26" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X26" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -828,21 +828,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -893,14 +893,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.85917</v>
+        <v>45.21442</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.15956</v>
+        <v>-77.8742</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -910,35 +910,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -975,14 +975,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.28947</v>
+        <v>48.24876</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94428000000001</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -992,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.30338</v>
+        <v>44.55104</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.90682</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1130,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.29002</v>
+        <v>46.23809</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94167</v>
+        <v>-82.11991</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1212,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>46.23809</v>
+        <v>45.28947</v>
       </c>
       <c r="W9" t="n">
-        <v>-82.11991</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1238,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>71.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1303,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>45.21442</v>
+        <v>54.51539</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.8742</v>
+        <v>-91.40791</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1320,30 +1320,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>44.55104</v>
+        <v>45.29002</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1402,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
         <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>48.24876</v>
+        <v>45.30338</v>
       </c>
       <c r="W12" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1484,30 +1484,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1529,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>44.85917</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.15956</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1566,21 +1566,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71.8</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1611,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V14" t="n">
-        <v>54.51539</v>
+        <v>44.51686</v>
       </c>
       <c r="W14" t="n">
-        <v>-91.40791</v>
+        <v>-77.62098</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1980,30 +1980,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2025,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2036,23 +2036,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W19" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2062,30 +2062,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2107,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>46.29559</v>
+        <v>44.47438</v>
       </c>
       <c r="W20" t="n">
-        <v>-83.20277</v>
+        <v>-76.51861</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2144,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2189,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2200,23 +2200,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2226,21 +2226,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2282,23 +2282,23 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U22" t="n">
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W22" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -2308,30 +2308,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2353,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2364,23 +2364,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T23" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U23" t="n">
         <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>44.55883</v>
+        <v>46.29559</v>
       </c>
       <c r="W23" t="n">
-        <v>-76.57349000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -2390,30 +2390,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2435,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2446,23 +2446,23 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T24" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U24" t="n">
         <v>48</v>
       </c>
       <c r="V24" t="n">
-        <v>44.47438</v>
+        <v>44.73856</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.51861</v>
+        <v>-76.32056</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2472,35 +2472,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2517,7 +2517,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2528,21 +2528,103 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>300</v>
+      </c>
+      <c r="U25" t="n">
+        <v>48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>13</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>325</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>43</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V26" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -828,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.21442</v>
+        <v>44.49976</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.8742</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -910,35 +910,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>48.24876</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -992,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55104</v>
+        <v>46.23809</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.54891000000001</v>
+        <v>-82.11991</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1130,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>46.23809</v>
+        <v>45.28947</v>
       </c>
       <c r="W8" t="n">
-        <v>-82.11991</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1156,21 +1156,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1221,14 +1221,14 @@
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>45.28947</v>
+        <v>45.30338</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1238,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71.8</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1303,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>54.51539</v>
+        <v>45.29002</v>
       </c>
       <c r="W10" t="n">
-        <v>-91.40791</v>
+        <v>-76.94167</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>71.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1385,14 +1385,14 @@
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>45.29002</v>
+        <v>54.51539</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.94167</v>
+        <v>-91.40791</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1402,30 +1402,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
         <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>45.30338</v>
+        <v>44.85917</v>
       </c>
       <c r="W12" t="n">
-        <v>-76.90682</v>
+        <v>-76.15956</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1484,30 +1484,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1526,10 +1526,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1546,17 +1550,17 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="V13" t="n">
-        <v>44.85917</v>
+        <v>44.99932</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.15956</v>
+        <v>-78.32907</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1566,21 +1570,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,12 +1593,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1611,7 +1615,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>44.51686</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.62098</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1652,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1690,14 +1694,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>44.99932</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-78.32907</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1734,35 +1734,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1779,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1790,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>44.55883</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1816,21 +1816,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1861,7 +1861,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,23 +1872,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>44.63956</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1898,30 +1898,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1943,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1954,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.62168</v>
+        <v>46.29559</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.56963</v>
+        <v>-83.20277</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1980,30 +1980,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2025,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2036,23 +2036,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.63956</v>
+        <v>44.47438</v>
       </c>
       <c r="W19" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.51861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2062,30 +2062,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2107,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.47438</v>
+        <v>44.73856</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.51861</v>
+        <v>-76.32056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2144,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2189,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2209,14 +2209,14 @@
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>46.30402</v>
+        <v>44.62168</v>
       </c>
       <c r="W21" t="n">
-        <v>-81.53989</v>
+        <v>-76.56963</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -2226,17 +2226,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2291,14 +2291,14 @@
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>44.55883</v>
+        <v>46.30402</v>
       </c>
       <c r="W22" t="n">
-        <v>-76.57349000000001</v>
+        <v>-81.53989</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2308,21 +2308,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2353,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2364,23 +2364,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>46.29559</v>
+        <v>48.69799</v>
       </c>
       <c r="W23" t="n">
-        <v>-83.20277</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -2390,30 +2390,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2435,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2446,185 +2446,21 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V24" t="n">
-        <v>44.73856</v>
+        <v>45.58868</v>
       </c>
       <c r="W24" t="n">
-        <v>-76.32056</v>
+        <v>-79.70944</v>
       </c>
       <c r="X24" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>12</v>
-      </c>
-      <c r="T25" t="n">
-        <v>300</v>
-      </c>
-      <c r="U25" t="n">
-        <v>48</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>43</v>
-      </c>
-      <c r="V26" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X26" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,30 +742,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -784,14 +784,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -802,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.85917</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-76.15956</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -828,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.49976</v>
+        <v>44.55104</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -910,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>44.49976</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -992,35 +988,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1037,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>46.23809</v>
+        <v>48.24876</v>
       </c>
       <c r="W7" t="n">
-        <v>-82.11991</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1139,14 +1135,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.28947</v>
+        <v>45.21442</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94428000000001</v>
+        <v>-77.8742</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1152,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V9" t="n">
-        <v>45.30338</v>
+        <v>44.51686</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.90682</v>
+        <v>-77.62098</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1238,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1280,10 +1276,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1300,17 +1300,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="V10" t="n">
-        <v>45.29002</v>
+        <v>44.99932</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.94167</v>
+        <v>-78.32907</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71.8</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>54.51539</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-91.40791</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1402,30 +1402,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V12" t="n">
-        <v>44.85917</v>
+        <v>44.52895</v>
       </c>
       <c r="W12" t="n">
-        <v>-76.15956</v>
+        <v>-77.78169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1526,14 +1526,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1544,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U13" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="V13" t="n">
-        <v>44.99932</v>
+        <v>44.73856</v>
       </c>
       <c r="W13" t="n">
-        <v>-78.32907</v>
+        <v>-76.32056</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1570,21 +1566,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1593,12 +1589,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1615,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>44.63956</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1652,35 +1648,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1697,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.47438</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-76.51861</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -1734,21 +1730,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1779,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1799,14 +1795,14 @@
         <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1816,30 +1812,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1861,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,23 +1868,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.63956</v>
+        <v>44.55883</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1898,21 +1894,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1921,7 +1917,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1943,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1954,23 +1950,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W18" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1980,30 +1976,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2025,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2036,23 +2032,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U19" t="n">
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.47438</v>
+        <v>46.29559</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.51861</v>
+        <v>-83.20277</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -2062,35 +2058,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2107,7 +2103,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2114,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.73856</v>
+        <v>48.69799</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.32056</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -2144,30 +2140,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2189,7 +2185,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2206,261 +2202,15 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V21" t="n">
-        <v>44.62168</v>
+        <v>45.58868</v>
       </c>
       <c r="W21" t="n">
-        <v>-76.56963</v>
+        <v>-79.70944</v>
       </c>
       <c r="X21" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Fensom</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MDI41I05SE00067</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nairn Centre</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>46.30402</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-81.53989</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>43</v>
-      </c>
-      <c r="V24" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X24" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -725,14 +725,14 @@
         <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>45.39062</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.70397</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -742,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.7</v>
+        <v>71.8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -787,7 +787,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -807,14 +807,14 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>44.85917</v>
+        <v>54.51539</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.15956</v>
+        <v>-91.40791</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -880,10 +880,10 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -971,14 +971,14 @@
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.49976</v>
+        <v>45.28947</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.61284999999999</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -988,35 +988,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>48.24876</v>
+        <v>45.30338</v>
       </c>
       <c r="W7" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.90682</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1070,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1135,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.21442</v>
+        <v>45.29002</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.8742</v>
+        <v>-76.94167</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1152,35 +1152,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.51686</v>
+        <v>48.24876</v>
       </c>
       <c r="W9" t="n">
-        <v>-77.62098</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1276,14 +1276,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1300,17 +1296,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.99932</v>
+        <v>45.21442</v>
       </c>
       <c r="W10" t="n">
-        <v>-78.32907</v>
+        <v>-77.8742</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1362,10 +1358,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>44.99932</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-78.32907</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1402,21 +1402,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>57</v>
       </c>
       <c r="V12" t="n">
-        <v>44.52895</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.78169</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1529,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V13" t="n">
-        <v>44.73856</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.32056</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1566,21 +1566,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1611,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>44.63956</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.55477999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1713,14 +1713,14 @@
         <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.47438</v>
+        <v>44.62168</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.51861</v>
+        <v>-76.56963</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1730,30 +1730,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1795,14 +1795,14 @@
         <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>44.62168</v>
+        <v>46.30402</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.56963</v>
+        <v>-81.53989</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1812,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1857,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1868,23 +1868,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U17" t="n">
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.55883</v>
+        <v>46.29559</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.57349000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1894,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1959,14 +1959,14 @@
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>46.30402</v>
+        <v>44.47438</v>
       </c>
       <c r="W18" t="n">
-        <v>-81.53989</v>
+        <v>-76.51861</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -1976,30 +1976,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2021,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2032,23 +2032,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T19" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U19" t="n">
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W19" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2058,35 +2058,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2103,7 +2103,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2123,14 +2123,14 @@
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>48.69799</v>
+        <v>44.73856</v>
       </c>
       <c r="W20" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.32056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2140,30 +2140,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2185,7 +2185,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2202,15 +2202,179 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
+        <v>48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>44.55883</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-76.57349000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>13</v>
+      </c>
+      <c r="T23" t="n">
+        <v>325</v>
+      </c>
+      <c r="U23" t="n">
         <v>43</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V23" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W23" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>45.39062</v>
+        <v>44.55039</v>
       </c>
       <c r="W2" t="n">
-        <v>-76.70397</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -725,14 +725,14 @@
         <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -742,35 +742,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71.8</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -784,10 +784,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +802,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V4" t="n">
-        <v>54.51539</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-91.40791</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -824,21 +828,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +851,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>44.55104</v>
+        <v>45.21442</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.54891000000001</v>
+        <v>-77.8742</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -906,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.28947</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -988,35 +992,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>71.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1033,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1057,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>45.30338</v>
+        <v>54.51539</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.90682</v>
+        <v>-91.40791</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1070,35 +1074,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1115,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1139,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>45.29002</v>
+        <v>48.24876</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.94167</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1152,35 +1156,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1197,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1221,14 @@
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>48.24876</v>
+        <v>44.85917</v>
       </c>
       <c r="W9" t="n">
-        <v>-89.86754000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1238,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1303,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>45.21442</v>
+        <v>45.29002</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.8742</v>
+        <v>-76.94167</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1358,14 +1362,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1382,17 +1382,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>44.99932</v>
+        <v>45.30338</v>
       </c>
       <c r="W11" t="n">
-        <v>-78.32907</v>
+        <v>-76.90682</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1402,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1444,10 +1444,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1462,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>44.99932</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-78.32907</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1484,21 +1488,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1529,7 +1533,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1544,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>57</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1566,21 +1570,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1589,12 +1593,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1611,7 +1615,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1648,35 +1652,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1693,7 +1697,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>44.62168</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-76.56963</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1816,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1857,7 +1861,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1868,23 +1872,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>46.29559</v>
+        <v>44.47438</v>
       </c>
       <c r="W17" t="n">
-        <v>-83.20277</v>
+        <v>-76.51861</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1898,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.47438</v>
+        <v>44.73856</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.51861</v>
+        <v>-76.32056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1976,30 +1980,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2021,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2032,23 +2036,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.63956</v>
+        <v>44.62168</v>
       </c>
       <c r="W19" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.56963</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -2058,30 +2062,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2103,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2123,14 +2127,14 @@
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.73856</v>
+        <v>44.63956</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.32056</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2140,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2185,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2196,23 +2200,23 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U21" t="n">
         <v>48</v>
       </c>
       <c r="V21" t="n">
-        <v>44.55883</v>
+        <v>46.29559</v>
       </c>
       <c r="W21" t="n">
-        <v>-76.57349000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -2222,35 +2226,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2267,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2287,14 +2291,14 @@
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>48.69799</v>
+        <v>44.55883</v>
       </c>
       <c r="W22" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -2304,35 +2308,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2349,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2360,21 +2364,103 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>300</v>
+      </c>
+      <c r="U23" t="n">
+        <v>48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>13</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>325</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>43</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,21 +570,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -612,14 +612,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -630,23 +626,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T2" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V2" t="n">
-        <v>44.55039</v>
+        <v>46.23809</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.36235000000001</v>
+        <v>-82.11991</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -656,30 +652,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,14 +694,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Mo 5.00%</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -716,23 +708,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="U3" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V3" t="n">
-        <v>45.39062</v>
+        <v>44.55104</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.70397</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -742,30 +734,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -784,14 +776,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -802,23 +790,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>45.28947</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -828,30 +816,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +861,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -893,14 +881,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.21442</v>
+        <v>45.30338</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.8742</v>
+        <v>-76.90682</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -910,30 +898,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +943,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +954,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>45.29002</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.94167</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -992,35 +980,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71.8</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1037,7 +1025,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1057,14 +1045,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>54.51539</v>
+        <v>44.85917</v>
       </c>
       <c r="W7" t="n">
-        <v>-91.40791</v>
+        <v>-76.15956</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1074,35 +1062,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1119,7 +1107,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1118,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>48.24876</v>
+        <v>44.49976</v>
       </c>
       <c r="W8" t="n">
-        <v>-89.86754000000001</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1144,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1198,10 +1186,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1218,17 +1210,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="V9" t="n">
-        <v>44.85917</v>
+        <v>44.99932</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.15956</v>
+        <v>-78.32907</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1238,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V10" t="n">
-        <v>45.29002</v>
+        <v>44.5021</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.94167</v>
+        <v>-77.61301</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="V11" t="n">
-        <v>45.30338</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.90682</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1402,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1444,14 +1436,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1462,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U12" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="V12" t="n">
-        <v>44.99932</v>
+        <v>44.52895</v>
       </c>
       <c r="W12" t="n">
-        <v>-78.32907</v>
+        <v>-77.78169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1488,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1533,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1544,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>44.62168</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-76.56963</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1570,21 +1558,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1593,12 +1581,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1615,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>44.63956</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1652,35 +1640,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1697,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>46.29559</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-83.20277</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1734,30 +1722,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1779,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1790,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>46.30402</v>
+        <v>44.73856</v>
       </c>
       <c r="W16" t="n">
-        <v>-81.53989</v>
+        <v>-76.32056</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1816,30 +1804,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1861,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1881,14 +1869,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>44.47438</v>
+        <v>46.30402</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.51861</v>
+        <v>-81.53989</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1898,21 +1886,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1921,7 +1909,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1943,7 +1931,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1954,23 +1942,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1980,30 +1968,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2025,7 +2013,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2045,14 +2033,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.62168</v>
+        <v>44.47438</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.56963</v>
+        <v>-76.51861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2062,35 +2050,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2107,7 +2095,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2106,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.63956</v>
+        <v>48.69799</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.55477999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -2144,30 +2132,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2189,7 +2177,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2200,267 +2188,21 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T21" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V21" t="n">
-        <v>46.29559</v>
+        <v>45.58868</v>
       </c>
       <c r="W21" t="n">
-        <v>-83.20277</v>
+        <v>-79.70944</v>
       </c>
       <c r="X21" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Kirkham Graphite Property</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MDI31C10SE00023</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Glendower</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>44.55883</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-76.57349000000001</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>12</v>
-      </c>
-      <c r="T23" t="n">
-        <v>300</v>
-      </c>
-      <c r="U23" t="n">
-        <v>48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>43</v>
-      </c>
-      <c r="V24" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X24" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,21 +570,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -612,10 +612,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -626,23 +630,23 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>46.23809</v>
+        <v>44.55039</v>
       </c>
       <c r="W2" t="n">
-        <v>-82.11991</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -652,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -694,10 +698,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mo 5.00%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -708,23 +716,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>150</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55104</v>
+        <v>45.39062</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -734,30 +742,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -776,10 +784,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -790,23 +802,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="V4" t="n">
-        <v>45.28947</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-76.94428000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -816,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -861,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -881,14 +893,14 @@
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.30338</v>
+        <v>45.21442</v>
       </c>
       <c r="W5" t="n">
-        <v>-76.90682</v>
+        <v>-77.8742</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -898,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -943,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -954,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>45.29002</v>
+        <v>44.55104</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.94167</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -980,35 +992,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.7</v>
+        <v>71.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1025,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1045,14 +1057,14 @@
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>44.85917</v>
+        <v>54.51539</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.15956</v>
+        <v>-91.40791</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1062,35 +1074,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1107,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1118,23 +1130,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>44.49976</v>
+        <v>48.24876</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.61284999999999</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1144,30 +1156,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1186,14 +1198,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1210,17 +1218,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.99932</v>
+        <v>44.85917</v>
       </c>
       <c r="W9" t="n">
-        <v>-78.32907</v>
+        <v>-76.15956</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1238,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>44.5021</v>
+        <v>45.29002</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.61301</v>
+        <v>-76.94167</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>45.30338</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-76.90682</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1402,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1436,10 +1444,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1462,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V12" t="n">
-        <v>44.52895</v>
+        <v>44.99932</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.78169</v>
+        <v>-78.32907</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1488,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1533,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1544,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V13" t="n">
-        <v>44.62168</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.56963</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1558,21 +1570,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1581,12 +1593,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1615,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1626,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V14" t="n">
-        <v>44.63956</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.55477999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1652,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1697,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V15" t="n">
-        <v>46.29559</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-83.20277</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1734,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>44.73856</v>
+        <v>46.30402</v>
       </c>
       <c r="W16" t="n">
-        <v>-76.32056</v>
+        <v>-81.53989</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1804,30 +1816,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1849,7 +1861,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1869,14 +1881,14 @@
         <v>48</v>
       </c>
       <c r="V17" t="n">
-        <v>46.30402</v>
+        <v>44.47438</v>
       </c>
       <c r="W17" t="n">
-        <v>-81.53989</v>
+        <v>-76.51861</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -1886,21 +1898,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1909,7 +1921,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1931,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1942,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1968,30 +1980,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2013,7 +2025,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2033,14 +2045,14 @@
         <v>48</v>
       </c>
       <c r="V19" t="n">
-        <v>44.47438</v>
+        <v>44.62168</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.51861</v>
+        <v>-76.56963</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -2050,35 +2062,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2095,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2106,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T20" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>48.69799</v>
+        <v>44.63956</v>
       </c>
       <c r="W20" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2132,30 +2144,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2177,7 +2189,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2188,21 +2200,267 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
+        <v>11</v>
+      </c>
+      <c r="T21" t="n">
+        <v>275</v>
+      </c>
+      <c r="U21" t="n">
+        <v>48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>46.29559</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-83.20277</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kirkham Graphite Property</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MDI31C10SE00023</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Glendower</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>325</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
+        <v>48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>44.55883</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-76.57349000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>300</v>
+      </c>
+      <c r="U23" t="n">
+        <v>48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>325</v>
+      </c>
+      <c r="U24" t="n">
         <v>43</v>
       </c>
-      <c r="V21" t="n">
+      <c r="V24" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W21" t="n">
+      <c r="W24" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,30 +570,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Zenith Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31F07NE00019</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Belangers Corner</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Molybdenum, Thorium, Uranium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Mo 5.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,14 +639,14 @@
         <v>70</v>
       </c>
       <c r="V2" t="n">
-        <v>44.55039</v>
+        <v>45.39062</v>
       </c>
       <c r="W2" t="n">
-        <v>-77.36235000000001</v>
+        <v>-76.70397</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
         </is>
       </c>
     </row>
@@ -656,30 +656,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Mo 5.00%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -725,14 +725,14 @@
         <v>70</v>
       </c>
       <c r="V3" t="n">
-        <v>45.39062</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-76.70397</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -828,30 +828,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -873,7 +873,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>66</v>
       </c>
       <c r="V5" t="n">
-        <v>45.21442</v>
+        <v>44.49976</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.8742</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -910,21 +910,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Globe Graphite Mine</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C16SE00016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Rideau Ferry</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Mineral Specimen, Tourmaline</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>66</v>
       </c>
       <c r="V6" t="n">
-        <v>44.55104</v>
+        <v>44.85917</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.15956</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
         </is>
       </c>
     </row>
@@ -992,35 +992,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Bawden Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31C10SE00024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Desert Lake</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71.8</v>
+        <v>5.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>66</v>
       </c>
       <c r="V7" t="n">
-        <v>54.51539</v>
+        <v>44.55104</v>
       </c>
       <c r="W7" t="n">
-        <v>-91.40791</v>
+        <v>-76.54891000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2.8</v>
+        <v>71.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1139,14 +1139,14 @@
         <v>66</v>
       </c>
       <c r="V8" t="n">
-        <v>48.24876</v>
+        <v>54.51539</v>
       </c>
       <c r="W8" t="n">
-        <v>-89.86754000000001</v>
+        <v>-91.40791</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>O'Brien Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI31F07SW00018</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.7</v>
+        <v>7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1221,14 +1221,14 @@
         <v>66</v>
       </c>
       <c r="V9" t="n">
-        <v>44.85917</v>
+        <v>45.28947</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.15956</v>
+        <v>-76.94428000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1238,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1303,14 @@
         <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>45.29002</v>
+        <v>48.24876</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.94167</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>
@@ -1320,30 +1320,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>National Graphite Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31F04NW00017</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1385,14 +1385,14 @@
         <v>66</v>
       </c>
       <c r="V11" t="n">
-        <v>45.30338</v>
+        <v>45.21442</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.90682</v>
+        <v>-77.8742</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
         </is>
       </c>
     </row>
@@ -1402,21 +1402,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Ross Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31F07SW00017</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Greater Madawaska</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>6.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1444,14 +1444,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1468,17 +1464,17 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V12" t="n">
-        <v>44.99932</v>
+        <v>45.29002</v>
       </c>
       <c r="W12" t="n">
-        <v>-78.32907</v>
+        <v>-76.94167</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
         </is>
       </c>
     </row>
@@ -1488,30 +1484,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Hunt Mine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31F07SW00016</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Mount St. Patrick</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1533,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1544,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>45.30338</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-76.90682</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
         </is>
       </c>
     </row>
@@ -1570,21 +1566,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1593,12 +1589,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1615,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1626,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>44.51686</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-77.62098</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1652,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>G. Padwell Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31D16NW00208</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Essonville</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1694,10 +1690,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Mo 1.00%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1708,23 +1708,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.99932</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-78.32907</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
         </is>
       </c>
     </row>
@@ -1734,35 +1734,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1779,7 +1779,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1790,23 +1790,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V16" t="n">
-        <v>46.30402</v>
+        <v>44.52895</v>
       </c>
       <c r="W16" t="n">
-        <v>-81.53989</v>
+        <v>-77.78169</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1816,35 +1816,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frontenac</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C07NE00036</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Perth Road</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Gold, Silver, Zinc</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1861,7 +1861,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,23 +1872,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="V17" t="n">
-        <v>44.47438</v>
+        <v>44.5021</v>
       </c>
       <c r="W17" t="n">
-        <v>-76.51861</v>
+        <v>-77.61301</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1898,30 +1898,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1943,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1954,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>48</v>
       </c>
       <c r="V18" t="n">
-        <v>44.73856</v>
+        <v>46.30402</v>
       </c>
       <c r="W18" t="n">
-        <v>-76.32056</v>
+        <v>-81.53989</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -2062,30 +2062,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2107,7 +2107,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2118,23 +2118,23 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T20" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U20" t="n">
         <v>48</v>
       </c>
       <c r="V20" t="n">
-        <v>44.63956</v>
+        <v>44.73856</v>
       </c>
       <c r="W20" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.32056</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -2226,30 +2226,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Frontenac</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C07NE00036</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Perth Road</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Lead, Gold, Silver, Zinc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2291,14 +2291,14 @@
         <v>48</v>
       </c>
       <c r="V22" t="n">
-        <v>44.55883</v>
+        <v>44.47438</v>
       </c>
       <c r="W22" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.51861</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
         </is>
       </c>
     </row>
@@ -2308,35 +2308,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2353,7 +2353,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2364,23 +2364,23 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T23" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U23" t="n">
         <v>48</v>
       </c>
       <c r="V23" t="n">
-        <v>48.69799</v>
+        <v>44.63956</v>
       </c>
       <c r="W23" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -2390,30 +2390,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2435,7 +2435,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2452,15 +2452,179 @@
         <v>325</v>
       </c>
       <c r="U24" t="n">
+        <v>48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>44.55883</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-76.57349000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>300</v>
+      </c>
+      <c r="U25" t="n">
+        <v>48</v>
+      </c>
+      <c r="V25" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>325</v>
+      </c>
+      <c r="U26" t="n">
         <v>43</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>45.58868</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>-79.70944</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +570,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zenith Mine</t>
+          <t>Sachigo River Mine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDI31F07NE00019</t>
+          <t>MDI53J11SW00002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Belangers Corner</t>
+          <t>Bearskin Lake</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.6</v>
+        <v>71.8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Molybdenum, Thorium, Uranium</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -612,14 +612,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Mo 5.00%</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Two samples of granite pegmatite taken from the rock dump averaged 7 ppm U3O8 and 23 ppm Th.</t>
+          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -636,17 +632,17 @@
         <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="V2" t="n">
-        <v>45.39062</v>
+        <v>54.51539</v>
       </c>
       <c r="W2" t="n">
-        <v>-76.70397</v>
+        <v>-91.40791</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07NE00019</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
         </is>
       </c>
     </row>
@@ -722,7 +718,7 @@
         <v>325</v>
       </c>
       <c r="U3" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="V3" t="n">
         <v>44.55039</v>
@@ -742,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -765,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -784,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -802,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -828,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -856,7 +848,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -873,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -890,17 +882,17 @@
         <v>300</v>
       </c>
       <c r="U5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.49976</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -910,35 +902,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Globe Graphite Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C16SE00016</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rideau Ferry</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Graphite, Mineral Specimen, Tourmaline</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -955,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>On the basis of the present drill results, it is provisionally estimated that perhaps 50,000 tons grading in the region of 7% graphite might remain in the deposit below the mined-out portion, to the 300 ft.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.85917</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-76.15956</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C16SE00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -992,21 +984,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bawden Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00024</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Desert Lake</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1020,7 +1012,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1037,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1987 · Stewart L Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55104</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.54891000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1074,35 +1066,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sachigo River Mine</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI53J11SW00002</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bearskin Lake</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71.8</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1119,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Comments Nov 21, 2014 (A Wilson) - A 2 foot thick section of a drill hole completed on the No 2 vein in 1936 intersected 28 oz/t Au. Diamond drilling by Lac Minerals in 1983 returned a best drill intersection of 0.1 oz/t Au from DDH SA-83-4. The best assay from diamond drilling completed by Inco in 1990 returned 4.05 g/t Au over 2.16 m at 81.78 m. 1 Vein 1979 Possible 5443 Hawkins (2009) 6000 tons of 10 g/t Au Production Data Year Tonnes Commodities Reference Comment 1942 42145 Silver 6127 Ounces Gold 52560 Ounces MDC013 The mine produced 52,560 oz Au and 6127 oz Ag from 42145 tonnes of ore mi</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>54.51539</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-91.40791</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI53J11SW00002</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1156,35 +1148,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>O'Brien Property</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31F07SW00018</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1201,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Howe and Associates Limited in 1965 returned the following assays: 0.122% MoS2 from a 15 lb sample of wasterock;</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1218,17 +1210,17 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>45.28947</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.94428000000001</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1238,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U10" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>48.24876</v>
+        <v>49.71016</v>
       </c>
       <c r="W10" t="n">
-        <v>-89.86754000000001</v>
+        <v>-94.40097</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1320,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>National Graphite Mine</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F04NW00017</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite, Feldspar (Gemstones), Molybdenum</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The average grade was reportedly 7%. Grab samples collected from the pits by the OGS in 1943 returned: 12.6% Cg over 13.5 ft and 10.37% Cg over 16 ft. 13 where an ore intersection between 89 and 105 ft was estimated to run 15-20% 1/8 to inch graphite flake Dec 07, 2005 (D Laidlaw) - Variety: Sunstone. Average of 7% graphite flakes 1.5-3 mm, locally 15-20%.</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.21442</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.8742</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04NW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1402,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ross Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31F07SW00017</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Greater Madawaska</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.8</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1447,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>153 150 tons grading 0.91% Mo were reportedly shipped from this site in 1917; An additional 96.8 tons of fines grading between 1.57 and 1.84% Mo also were shipped in 1917 References Publication - Molybdenum metallurgy and uses and the occurrence, mining and concentr</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>45.29002</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-76.94167</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00017</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1484,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hunt Mine</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31F07SW00016</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mount St. Patrick</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1529,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1962–1964 · R Rinaldi</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.30338</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-76.90682</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F07SW00016</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1566,30 +1558,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1611,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.51686</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.62098</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1648,35 +1640,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>G. Padwell Property</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31D16NW00208</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Essonville</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1690,14 +1682,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Mo 1.00%</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mineral Record Details Production Data Year Tonnes Commodities Reference Comment 1917 56 shipped 62 tons grading 1.0% MoS2; 1916 50 shipped 50.43 tonness of hand-picked ore grading 1.4% MoS2.</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1714,17 +1702,17 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.99932</v>
+        <v>45.58868</v>
       </c>
       <c r="W15" t="n">
-        <v>-78.32907</v>
+        <v>-79.70944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31D16NW00208</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1784,7 @@
         <v>250</v>
       </c>
       <c r="U16" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="V16" t="n">
         <v>44.52895</v>
@@ -1816,35 +1804,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1861,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1872,761 +1860,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>44.5021</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61301</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Fensom</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI41I05SE00067</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nairn Centre</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>48</v>
-      </c>
-      <c r="V18" t="n">
-        <v>46.30402</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-81.53989</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Meadow Lake Zone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI31C10SE00205</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Bedford</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>48</v>
-      </c>
-      <c r="V19" t="n">
-        <v>44.62168</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-76.56963</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Timmins Mine</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MDI31C09NW00013</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stanleyville</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>11</v>
-      </c>
-      <c r="T20" t="n">
-        <v>275</v>
-      </c>
-      <c r="U20" t="n">
-        <v>48</v>
-      </c>
-      <c r="V20" t="n">
-        <v>44.73856</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-76.32056</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Principle Strategic Minerals Prospect</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MDI41J06SE00050</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Patton</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Copper, Silver</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>11</v>
-      </c>
-      <c r="T21" t="n">
-        <v>275</v>
-      </c>
-      <c r="U21" t="n">
-        <v>48</v>
-      </c>
-      <c r="V21" t="n">
-        <v>46.29559</v>
-      </c>
-      <c r="W21" t="n">
-        <v>-83.20277</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Frontenac</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MDI31C07NE00036</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Perth Road</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Lead</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Lead, Gold, Silver, Zinc</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Bulk sampling on surface over a length of 400 feet and an average width of 12 feet gave 4.20% Pb, 0.30% Zn, 0.22 oz./ton Ag.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>48</v>
-      </c>
-      <c r="V22" t="n">
-        <v>44.47438</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-76.51861</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C07NE00036</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bannockburn</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MDI31C12NE00021</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Bannockburn</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>13</v>
-      </c>
-      <c r="T23" t="n">
-        <v>325</v>
-      </c>
-      <c r="U23" t="n">
-        <v>48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>44.63956</v>
-      </c>
-      <c r="W23" t="n">
-        <v>-77.55477999999999</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Kirkham Graphite Property</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MDI31C10SE00023</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Glendower</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="n">
-        <v>13</v>
-      </c>
-      <c r="T24" t="n">
-        <v>325</v>
-      </c>
-      <c r="U24" t="n">
-        <v>48</v>
-      </c>
-      <c r="V24" t="n">
-        <v>44.55883</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-76.57349000000001</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>12</v>
-      </c>
-      <c r="T25" t="n">
-        <v>300</v>
-      </c>
-      <c r="U25" t="n">
-        <v>48</v>
-      </c>
-      <c r="V25" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W25" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="n">
-        <v>13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>325</v>
-      </c>
-      <c r="U26" t="n">
-        <v>43</v>
-      </c>
-      <c r="V26" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W26" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>49.71016</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-94.40097</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1394,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,7 +1421,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1476,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1558,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1726,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1804,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,21 +1864,185 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>200</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.5143</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.61444</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ackerman</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C05NE00018</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>300</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.49976</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.61284999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>13</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T19" t="n">
         <v>325</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -824,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>49.71016</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-94.40097</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1394,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,7 +1417,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1558,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,30 +1722,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W16" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1804,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,185 +1860,21 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>44.5143</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61444</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ackerman</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI31C05NE00018</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>300</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>44.49976</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-77.61284999999999</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -902,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -925,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1046,17 +1050,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>49.71016</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-94.40097</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1398,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1408,7 +1412,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,7 +1421,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>45.58868</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-79.70944</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.52895</v>
+        <v>44.5143</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.78169</v>
+        <v>-77.61444</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1804,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,21 +1864,185 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.52895</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.78169</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>300</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1050,17 +1046,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.5021</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-77.61301</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1312,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1394,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1463,14 +1459,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1558,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1644,21 +1640,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,21 +1722,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1749,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5143</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61444</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1804,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,185 +1860,21 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>300</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>300</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1046,17 +1050,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.5021</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.61301</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1394,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1459,14 +1463,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1640,21 +1644,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1663,7 +1667,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,12 +1749,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>44.5143</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-77.61444</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1804,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,21 +1864,185 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>225</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.52895</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.78169</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>12</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>300</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>44.5143</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61444</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1545,14 +1545,14 @@
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5143</v>
+        <v>45.58868</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61444</v>
+        <v>-79.70944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,187 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>300</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>300</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
